--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,16 +35,16 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,22 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -536,139 +550,163 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0189</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MATANG</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>5597300</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>28.35</v>
-      </c>
-      <c r="H2" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2691800</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>59.98</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>现价0.60高于50日均线0.529，SAR转多信号获均线支撑；RSI 59.98处中性偏上区间，未超买，信号可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7120</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AXTERIA</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0.0256</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>3073700</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>87.61</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1307400</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="J3" s="3" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 57.44处中性偏上，未超买；现价0.63高于50日均线0.585约7.7%，技术面信号可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CEB</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>-0.0377</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>2706200</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H4" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1036000</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>66.13</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号可靠，现价高于50日均线约27%，RSI 66.13接近超买区，需留意动能。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,42 +716,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0299</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2371300</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.03</v>
+          <t>AXTERIA</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>16906000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>3.3</v>
       </c>
       <c r="H5" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.269</v>
+        <v>89.54000000000001</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.118</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -723,42 +761,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>-0.0135</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1170400</v>
-      </c>
-      <c r="G6" s="5" t="n">
+          <t>ASTRO</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
         <v>0.05</v>
       </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.09089999999999999</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>14552900</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>3.96</v>
+      </c>
       <c r="H6" t="n">
-        <v>78.62</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.5679999999999999</v>
+        <v>41.01</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.057</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,42 +806,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>850000</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.41</v>
+          <t>DATAPRP</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>10150200</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.97</v>
       </c>
       <c r="H7" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.629</v>
+        <v>37.48</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -813,42 +851,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GDB</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.0388</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>641000</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.17</v>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0667</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>8968200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.15</v>
       </c>
       <c r="H8" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>51.28</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0.438</v>
+      <c r="J8" s="9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.148</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -858,45 +896,2822 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>8526100</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H9" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>8254700</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>7583900</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H11" t="n">
+        <v>72.56999999999999</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0189</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MATANG</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>7497700</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="H12" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>6857400</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>62.24</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>1.808</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>-0.0667</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>6708300</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H14" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>6283200</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>6232500</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>5438700</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>4963300</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>4700100</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H19" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>4090000</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H20" t="n">
+        <v>44.11</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>4029700</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>3721600</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.0857</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>3664100</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H23" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>3438700</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H24" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>2731000</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>54.16</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>2587000</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>5.369</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>5.515</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>2576300</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>2235900</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H28" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>2161000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>60.49</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0266</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>2131300</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1866400</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H31" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>4.877</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>4.772</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1843000</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0278</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EDELTEQ</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1705600</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H33" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1667500</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H34" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1655900</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>0146</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>JFTECH</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="D36" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1628500</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H36" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MMSV</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1559800</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="H37" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1532400</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H38" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>2.593</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>2.563</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1420200</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H39" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7155</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SKPRES</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1409700</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H40" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1405500</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H41" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1390100</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H42" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>1325100</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>46.34</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>1265200</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H44" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E45" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>501700</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H9" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="F45" s="11" t="n">
+        <v>1171300</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1155300</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H46" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>1046000</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H47" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>1043600</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1032700</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H49" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K49" s="9" t="n"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1017200</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H50" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>3.005</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>973100</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H51" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>885300</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H52" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>3.081</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>878300</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H53" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>851500</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H54" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>840800</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H55" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>835100</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H56" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>1.209</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>804500</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H57" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>3.827</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>784500</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H58" t="n">
+        <v>63.72</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>704400</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H59" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>704000</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H60" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>661200</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H61" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>633400</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H62" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>632900</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H63" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>624100</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H64" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>590300</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H65" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>572700</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H66" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>2.726</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>568300</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H67" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>5.537</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>565600</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H68" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>561100</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H69" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0391</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>523600</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H70" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>6.369</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>6.026</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0142</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>517300</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H71" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>4.014</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>3.666</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M9"/>
+  <autoFilter ref="A1:M71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -89,14 +89,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0619</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2691800</v>
+        <v>3749600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>59.98</v>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.05</v>
+        <v>0.0417</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1307400</v>
+        <v>1884800</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.44</v>
+        <v>56.61</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.44处中性偏上，未超买；现价0.63高于50日均线0.585约7.7%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 56.61处中性区间未超买，现价高于50日均线约6.8%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0508</v>
+        <v>0.0254</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1036000</v>
+        <v>1320600</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.13</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.106</v>
+        <v>1.103</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.974</v>
+        <v>0.973</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号可靠，现价高于50日均线约27%，RSI 66.13接近超买区，需留意动能。</t>
+          <t>SAR转多信号，RSI 64.18未超买，现价高于50日均线约24%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -716,28 +716,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.1282</v>
+        <v>-0.0667</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>16906000</v>
+        <v>37068100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>3.3</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>89.54000000000001</v>
+        <v>32.57</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.13</v>
+        <v>0.096</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.118</v>
+        <v>0.247</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -761,39 +761,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.05</v>
+        <v>0.215</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.1026</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>14552900</v>
+        <v>24017500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>3.96</v>
+        <v>4.69</v>
       </c>
       <c r="H6" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.11</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.055</v>
+        <v>0.129</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.057</v>
+        <v>0.118</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -806,28 +806,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
         <v>0.05</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.1111</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>10150200</v>
+        <v>14552900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.97</v>
+        <v>3.96</v>
       </c>
       <c r="H7" t="n">
-        <v>37.48</v>
+        <v>41.01</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>13697000</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>0.16</v>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0667</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>8968200</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.15</v>
-      </c>
       <c r="H8" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.92</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.159</v>
+        <v>0.319</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.148</v>
+        <v>0.269</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -905,19 +905,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0105</v>
+        <v>0.485</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8526100</v>
+        <v>12481600</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H9" t="n">
-        <v>73.34</v>
+        <v>74.08</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -941,39 +941,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.345</v>
+        <v>0.735</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.0299</v>
+        <v>-0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8254700</v>
+        <v>10713700</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="H10" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.18000000000001</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.319</v>
+        <v>0.667</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.269</v>
+        <v>0.569</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -986,28 +986,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7583900</v>
+        <v>10641900</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.95</v>
+        <v>0.18</v>
       </c>
       <c r="H11" t="n">
-        <v>72.56999999999999</v>
+        <v>51.28</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.079</v>
+        <v>0.159</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.076</v>
+        <v>0.148</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1031,39 +1031,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>10545200</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>37.48</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K12" s="9" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>7497700</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="H12" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>0.074</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1087,14 +1087,14 @@
       <c r="D13" s="9" t="n">
         <v>2.14</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="15" t="n">
         <v>0.0338</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6857400</v>
+        <v>8000900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H13" t="n">
         <v>62.24</v>
@@ -1121,28 +1121,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>-0.0667</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6708300</v>
+        <v>7953900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.02</v>
+        <v>2.04</v>
       </c>
       <c r="H14" t="n">
-        <v>32.57</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.096</v>
+        <v>0.079</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.247</v>
+        <v>0.076</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.735</v>
+        <v>0.435</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.0068</v>
+        <v>0.0357</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6283200</v>
+        <v>7655200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H15" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.79</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.667</v>
+        <v>0.453</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.569</v>
+        <v>0.473</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1211,28 +1211,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.295</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6232500</v>
+        <v>7497700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.86</v>
+        <v>37.97</v>
       </c>
       <c r="H16" t="n">
-        <v>49.06</v>
+        <v>44.67</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.295</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.295</v>
+        <v>0.074</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1256,40 +1256,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0054</v>
+        <v>0.225</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5438700</v>
+        <v>7482800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H17" t="n">
-        <v>64.87</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0.768</v>
-      </c>
+        <v>51.42</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1301,28 +1297,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>4963300</v>
+        <v>7231400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.33</v>
+        <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>83.7</v>
+        <v>66.61</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1330,10 +1326,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.459</v>
+        <v>0.867</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.439</v>
+        <v>0.769</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1346,28 +1342,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0929</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4700100</v>
+        <v>6638600</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.42</v>
+        <v>1.34</v>
       </c>
       <c r="H19" t="n">
-        <v>41.24</v>
+        <v>49.05</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1375,10 +1371,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.284</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.279</v>
+        <v>0.637</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1391,28 +1387,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.18</v>
+        <v>0.295</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4090000</v>
+        <v>6232500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.21</v>
+        <v>1.86</v>
       </c>
       <c r="H20" t="n">
-        <v>44.11</v>
+        <v>49.06</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1420,10 +1416,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.185</v>
+        <v>0.295</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.187</v>
+        <v>0.295</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1445,16 +1441,16 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0441</v>
+        <v>0.735</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0809</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>4029700</v>
+        <v>5824000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1474,39 +1470,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.54</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.04849999999999999</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3721600</v>
+        <v>5448500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.1</v>
+        <v>1.46</v>
       </c>
       <c r="H22" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.7</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.453</v>
+        <v>0.459</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.473</v>
+        <v>0.439</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1519,28 +1515,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.0857</v>
+        <v>0.595</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.04389999999999999</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3664100</v>
+        <v>5331900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="H23" t="n">
-        <v>48.73</v>
+        <v>55.89</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1548,10 +1544,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.637</v>
+        <v>0.548</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1564,36 +1560,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.225</v>
+        <v>0.265</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3438700</v>
+        <v>5267300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
       <c r="H24" t="n">
-        <v>51.42</v>
+        <v>41.24</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.279</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1605,28 +1605,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0263</v>
+        <v>0.475</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2731000</v>
+        <v>4769500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H25" t="n">
-        <v>54.16</v>
+        <v>63.76</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.57</v>
+        <v>0.438</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.548</v>
+        <v>0.389</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1650,28 +1650,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0282</v>
+        <v>0.18</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2587000</v>
+        <v>4141400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H26" t="n">
-        <v>39.18</v>
+        <v>44.11</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>5.369</v>
+        <v>0.185</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>5.515</v>
+        <v>0.187</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1695,39 +1695,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.95</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2576300</v>
+        <v>3804900</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.87</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.774</v>
+        <v>1</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.776</v>
+        <v>0.985</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1740,28 +1740,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0241</v>
+        <v>0.775</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2235900</v>
+        <v>3772600</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H28" t="n">
-        <v>59.01</v>
+        <v>50.65</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.404</v>
+        <v>0.774</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.384</v>
+        <v>0.776</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1785,28 +1785,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.465</v>
+        <v>5.06</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.0211</v>
+        <v>0.0202</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2161000</v>
+        <v>3713900</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="H29" t="n">
-        <v>60.49</v>
+        <v>37.48</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.437</v>
+        <v>5.366</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.389</v>
+        <v>5.514</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1830,39 +1830,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0266</v>
+        <v>0.475</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2131300</v>
+        <v>3469600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.2</v>
+        <v>38.93</v>
       </c>
       <c r="H30" t="n">
-        <v>45.01</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.28</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.002</v>
+        <v>0.46</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.986</v>
+        <v>0.478</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1875,39 +1875,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.002</v>
+        <v>0.82</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1866400</v>
+        <v>3275000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.877</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.772</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1920,28 +1920,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0</v>
+        <v>0.875</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1843000</v>
+        <v>3175100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.12</v>
+        <v>0.51</v>
       </c>
       <c r="H32" t="n">
-        <v>54.27</v>
+        <v>48.44</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.886</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1965,39 +1965,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.0118</v>
+        <v>0.135</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1705600</v>
+        <v>3097500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.27</v>
+        <v>23.37</v>
       </c>
       <c r="H33" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.72</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.402</v>
+        <v>0.131</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.367</v>
+        <v>0.137</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2021,14 +2021,14 @@
       <c r="D34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="15" t="n">
         <v>0.0204</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1667500</v>
+        <v>3039200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H34" t="n">
         <v>36.89</v>
@@ -2055,28 +2055,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0175</v>
+        <v>0.155</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1655900</v>
+        <v>3019000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.27</v>
+        <v>0.08</v>
       </c>
       <c r="H35" t="n">
-        <v>47.8</v>
+        <v>47.73</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.886</v>
+        <v>0.156</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.862</v>
+        <v>0.156</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2100,28 +2100,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.43</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1628500</v>
+        <v>2920100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H36" t="n">
-        <v>54.5</v>
+        <v>58.37</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.745</v>
+        <v>0.402</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.708</v>
+        <v>0.367</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2145,28 +2145,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0345</v>
+        <v>4.89</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.002</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1559800</v>
+        <v>2871400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2.81</v>
+        <v>0.12</v>
       </c>
       <c r="H37" t="n">
-        <v>54.53</v>
+        <v>52.01</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.291</v>
+        <v>4.877</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.295</v>
+        <v>4.772</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2190,28 +2190,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0198</v>
+        <v>0.575</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.036</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1532400</v>
+        <v>2824900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.09</v>
+        <v>0.32</v>
       </c>
       <c r="H38" t="n">
-        <v>48.62</v>
+        <v>43.3</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.593</v>
+        <v>0.605</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.563</v>
+        <v>0.617</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2235,39 +2235,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0105</v>
+        <v>0.415</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1420200</v>
+        <v>2802800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H39" t="n">
-        <v>43.36</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.493</v>
+        <v>0.403</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.514</v>
+        <v>0.384</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2280,39 +2280,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.0152</v>
+        <v>0.38</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1409700</v>
+        <v>2627100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H40" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.95</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.347</v>
+        <v>0.46</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.33</v>
+        <v>0.577</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2325,40 +2325,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.0197</v>
+        <v>0.385</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0405</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1405500</v>
+        <v>2534500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.52</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0.771</v>
-      </c>
+        <v>0.342</v>
+      </c>
+      <c r="K41" s="9" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2370,39 +2368,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0225</v>
+        <v>2.56</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1390100</v>
+        <v>2531800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.79</v>
+        <v>0.15</v>
       </c>
       <c r="H42" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.98</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.905</v>
+        <v>2.593</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.895</v>
+        <v>2.563</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2415,39 +2413,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.47</v>
+        <v>2.09</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.0217</v>
+        <v>-0.0048</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1325100</v>
+        <v>2502600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H43" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.3</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.49</v>
+        <v>2.104</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.47</v>
+        <v>2.111</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2460,28 +2458,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.78</v>
+        <v>1.14</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>0.013</v>
+        <v>-0.0172</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1265200</v>
+        <v>2411900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="H44" t="n">
-        <v>57.5</v>
+        <v>24.71</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2489,10 +2487,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.745</v>
+        <v>1.287</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2505,28 +2503,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="E45" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1171300</v>
+        <v>2278900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="H45" t="n">
-        <v>47.41</v>
+        <v>44.37</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2534,10 +2532,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.337</v>
+        <v>0.49</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.337</v>
+        <v>0.47</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2550,28 +2548,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.018</v>
+        <v>0.76</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1155300</v>
+        <v>2244700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.13</v>
+        <v>0.73</v>
       </c>
       <c r="H46" t="n">
-        <v>41.29</v>
+        <v>54.5</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2579,10 +2577,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.604</v>
+        <v>0.745</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.616</v>
+        <v>0.708</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2595,39 +2593,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.775</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1046000</v>
+        <v>2129000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="H47" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.83</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.43</v>
+        <v>0.745</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.417</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2640,28 +2638,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>-0.008</v>
+        <v>0.89</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1043600</v>
+        <v>2126100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.29</v>
+        <v>1.2</v>
       </c>
       <c r="H48" t="n">
-        <v>53.48</v>
+        <v>47.64</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2669,10 +2667,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.62</v>
+        <v>0.904</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.611</v>
+        <v>0.895</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2685,28 +2683,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0405</v>
+        <v>1.43</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1032700</v>
+        <v>2106600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H49" t="n">
-        <v>64.52</v>
+        <v>29.85</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2714,9 +2712,11 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="K49" s="9" t="n"/>
+        <v>1.564</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>1.852</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
     </row>
@@ -2728,28 +2728,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0503</v>
+        <v>0.485</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1017200</v>
+        <v>2051600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="H50" t="n">
-        <v>57.15</v>
+        <v>45.27</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>3.005</v>
+        <v>0.493</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.87</v>
+        <v>0.514</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2773,39 +2773,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0048</v>
+        <v>0.305</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.0517</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>973100</v>
+        <v>1813600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.09</v>
+        <v>3.27</v>
       </c>
       <c r="H51" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.106</v>
+        <v>0.292</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.111</v>
+        <v>0.295</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2818,28 +2818,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>885300</v>
+        <v>1754500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H52" t="n">
-        <v>89.08</v>
+        <v>66.22</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>3.081</v>
+        <v>0.626</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.61</v>
+        <v>0.619</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0.0167</v>
+        <v>3.16</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0604</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>878300</v>
+        <v>1705200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="H53" t="n">
-        <v>57.18</v>
+        <v>58.26</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.58</v>
+        <v>3.008</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.489</v>
+        <v>2.87</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2908,39 +2908,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0197</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>851500</v>
+        <v>1568000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H54" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.94</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.641</v>
+        <v>0.768</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.629</v>
+        <v>0.771</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2953,28 +2953,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0174</v>
+        <v>3.97</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0232</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>840800</v>
+        <v>1552200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
       <c r="H55" t="n">
-        <v>61.28</v>
+        <v>57.07</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.1</v>
+        <v>3.828</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.059</v>
+        <v>3.755</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2998,28 +2998,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.24</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>835100</v>
+        <v>1525600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="H56" t="n">
-        <v>58.6</v>
+        <v>43.17</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.234</v>
+        <v>1.271</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.209</v>
+        <v>1.317</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3043,39 +3043,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0206</v>
+        <v>0.33</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>804500</v>
+        <v>1502700</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H57" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.827</v>
+        <v>0.337</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>3.755</v>
+        <v>0.337</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3088,28 +3088,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.44</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>784500</v>
+        <v>1491800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="H58" t="n">
-        <v>63.72</v>
+        <v>53.62</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.626</v>
+        <v>0.43</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.619</v>
+        <v>0.417</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3133,39 +3133,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.0915</v>
+        <v>0.265</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>704400</v>
+        <v>1450500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.95</v>
+        <v>0.21</v>
       </c>
       <c r="H59" t="n">
-        <v>55.05</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.15</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.601</v>
+        <v>0.28</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.65</v>
+        <v>0.282</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3178,39 +3178,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.465</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>704000</v>
+        <v>1441300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="n">
-        <v>61.09</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.02</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.836</v>
+        <v>0.481</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.802</v>
+        <v>0.536</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3223,39 +3223,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.965</v>
+        <v>0.335</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.0052</v>
+        <v>0.0152</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>661200</v>
+        <v>1440200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H61" t="n">
-        <v>61.68</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.945</v>
+        <v>0.347</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.895</v>
+        <v>0.33</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3268,39 +3268,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0167</v>
+        <v>3.43</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>633400</v>
+        <v>1432500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
       <c r="H62" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.26000000000001</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.644</v>
+        <v>3.082</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.681</v>
+        <v>2.61</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3313,39 +3313,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0.0153</v>
+        <v>1.18</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0261</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>632900</v>
+        <v>1388400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H63" t="n">
-        <v>43.42</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.3</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.711</v>
+        <v>1.101</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3358,28 +3358,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.23</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>624100</v>
+        <v>1318400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="H64" t="n">
-        <v>56.33</v>
+        <v>14.67</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3387,11 +3387,9 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.273</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>1.189</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K64" s="9" t="n"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3403,28 +3401,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>-0.0049</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>590300</v>
+        <v>1276500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="H65" t="n">
-        <v>31.15</v>
+        <v>46.65</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3432,10 +3430,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.565</v>
+        <v>2.038</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.852</v>
+        <v>2.063</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3448,39 +3446,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.0038</v>
+        <v>0.305</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>572700</v>
+        <v>1226600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="H66" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.54</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.726</v>
+        <v>0.314</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.747</v>
+        <v>0.357</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3493,39 +3491,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0.0516</v>
+        <v>0.91</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>568300</v>
+        <v>1225900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="H67" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.65</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>5.537</v>
+        <v>0.898</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>5.39</v>
+        <v>0.956</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3538,39 +3536,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0166</v>
+        <v>0.61</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>565600</v>
+        <v>1224300</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H68" t="n">
-        <v>52.46</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.18</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.899</v>
+        <v>0.58</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.956</v>
+        <v>0.489</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3583,39 +3581,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.515</v>
+        <v>4.21</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0.0198</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>561100</v>
+        <v>1210500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="H69" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.24</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.528</v>
+        <v>4.007</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>3.664</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3628,39 +3626,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0391</v>
+        <v>1.29</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>523600</v>
+        <v>1177000</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H70" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>6.369</v>
+        <v>1.235</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>6.026</v>
+        <v>1.209</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3673,28 +3671,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4.29</v>
+        <v>4.72</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>0.0142</v>
+        <v>-0.0021</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>517300</v>
+        <v>1138200</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="H71" t="n">
-        <v>62.78</v>
+        <v>47.78</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3702,16 +3700,1636 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>4.014</v>
+        <v>4.728</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>3.666</v>
+        <v>4.805</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>1131900</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H72" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>1115400</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H73" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>10.106</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0395</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OGX</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>1089900</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H74" t="n">
+        <v>58.83</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>1048300</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>41.32</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>2.427</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>1043600</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H76" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>1012300</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H77" t="n">
+        <v>41.76</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>1010600</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H78" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1.652</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>994100</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H79" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>956600</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H80" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>951700</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H81" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>2.603</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>910800</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H82" t="n">
+        <v>61.09</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0784</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>889300</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>885800</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H84" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>884400</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H85" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>5.535</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>866200</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H86" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>856900</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H87" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>2.725</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>2.747</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>851500</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H88" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>834300</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H89" t="n">
+        <v>29.83</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>799800</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H90" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>2.081</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>770800</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>6.364</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>6.025</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>767600</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H92" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>732800</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H93" t="n">
+        <v>31.47</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>7.335</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>7.611</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>709700</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H94" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>687900</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H95" t="n">
+        <v>58.01</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>2.699</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>678100</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H96" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>670200</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H97" t="n">
+        <v>56.52</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>665400</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H98" t="n">
+        <v>62.29</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>10.528</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>9.907</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>656500</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H99" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>643800</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H100" t="n">
+        <v>64.84</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>638700</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H101" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>3.827</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>631400</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H102" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>2.822</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>624800</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H103" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>609000</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H104" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>7.027</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>7.471</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>599300</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H105" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>564500</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H106" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>513300</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H107" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>7.308</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>6.968</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M71"/>
+  <autoFilter ref="A1:M107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0619</v>
+        <v>0.0708</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3749600</v>
+        <v>4009700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98</v>
+        <v>60.71</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.60高于50日均线0.529，SAR转多信号获均线支撑；RSI 59.98处中性偏上区间，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.605高于50日均线0.529约14%，RSI 60.71处中性偏强区间，未超买，信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0417</v>
+        <v>0.0583</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1884800</v>
+        <v>3032200</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>56.61</v>
+        <v>58.24</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.596</v>
+        <v>0.597</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.585</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 56.61处中性区间未超买，现价高于50日均线约6.8%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，RSI 58.24处中性偏上，未超买；现价0.635高于50日均线0.585约8.5%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0339</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1320600</v>
+        <v>1539200</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.18000000000001</v>
+        <v>64.86</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.103</v>
+        <v>1.104</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.973</v>
+        <v>0.974</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.18未超买，现价高于50日均线约24%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号，RSI 64.86接近超买区，现价高于50日均线约25%，技术面信号偏强但需留意RSI高位。</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>37068100</v>
+        <v>42958500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="H5" t="n">
         <v>32.57</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.215</v>
+        <v>0.21</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.1026</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>24017500</v>
+        <v>27041900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4.69</v>
+        <v>5.28</v>
       </c>
       <c r="H6" t="n">
-        <v>89.11</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -806,28 +806,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.345</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0299</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14552900</v>
+        <v>18098000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>3.96</v>
+        <v>0.21</v>
       </c>
       <c r="H7" t="n">
-        <v>41.01</v>
+        <v>64.92</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.055</v>
+        <v>0.319</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.057</v>
+        <v>0.269</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.345</v>
+        <v>0.485</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.0211</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13697000</v>
+        <v>17813100</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.08</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.319</v>
+        <v>0.426</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.269</v>
+        <v>0.326</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -896,39 +896,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.055</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12481600</v>
+        <v>14553000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.34</v>
+        <v>3.96</v>
       </c>
       <c r="H9" t="n">
-        <v>74.08</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.65</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.426</v>
+        <v>0.055</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.326</v>
+        <v>0.058</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -956,10 +956,10 @@
         <v>-0.0068</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10713700</v>
+        <v>12969600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="H10" t="n">
         <v>81.18000000000001</v>
@@ -1001,7 +1001,7 @@
         <v>0.0667</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10641900</v>
+        <v>10738600</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0.18</v>
@@ -1046,10 +1046,10 @@
         <v>0.1111</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10545200</v>
+        <v>10560600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="H12" t="n">
         <v>37.48</v>
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.0338</v>
+        <v>0.0386</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8000900</v>
+        <v>9511200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="H13" t="n">
-        <v>62.24</v>
+        <v>62.67</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.988</v>
+        <v>1.989</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>1.808</v>
@@ -1136,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7953900</v>
+        <v>9312300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="H14" t="n">
         <v>72.56999999999999</v>
@@ -1166,39 +1166,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.93</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7655200</v>
+        <v>8386000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="H15" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.02</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.453</v>
+        <v>0.867</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.473</v>
+        <v>0.769</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1211,28 +1211,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7497700</v>
+        <v>7967700</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>37.97</v>
+        <v>0.22</v>
       </c>
       <c r="H16" t="n">
-        <v>44.67</v>
+        <v>42.79</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.453</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.074</v>
+        <v>0.473</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1256,36 +1256,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0929</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7482800</v>
+        <v>7875300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.38</v>
+        <v>1.59</v>
       </c>
       <c r="H17" t="n">
-        <v>51.42</v>
+        <v>49.05</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="J17" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.637</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1297,40 +1301,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0054</v>
+        <v>0.22</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7231400</v>
+        <v>7508000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H18" t="n">
-        <v>66.61</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0.769</v>
-      </c>
+        <v>48.42</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1342,28 +1342,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0929</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>6638600</v>
+        <v>7497700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.34</v>
+        <v>37.97</v>
       </c>
       <c r="H19" t="n">
-        <v>49.05</v>
+        <v>44.67</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.637</v>
+        <v>0.074</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1387,28 +1387,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.295</v>
+        <v>0.18</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6232500</v>
+        <v>7210000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.86</v>
+        <v>0.37</v>
       </c>
       <c r="H20" t="n">
-        <v>49.06</v>
+        <v>44.11</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.295</v>
+        <v>0.185</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.295</v>
+        <v>0.187</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1432,33 +1432,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.0809</v>
+        <v>0.47</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5824000</v>
+        <v>6870100</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+        <v>77.09</v>
+      </c>
+      <c r="H21" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.478</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1470,40 +1477,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5448500</v>
+        <v>6321500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="H22" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.439</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1515,28 +1515,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.265</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5331900</v>
+        <v>6293400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="H23" t="n">
-        <v>55.89</v>
+        <v>41.24</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.571</v>
+        <v>0.284</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.548</v>
+        <v>0.279</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1560,28 +1560,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.04389999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5267300</v>
+        <v>6280900</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="H24" t="n">
-        <v>41.24</v>
+        <v>55.89</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.284</v>
+        <v>0.571</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.279</v>
+        <v>0.548</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1605,28 +1605,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.475</v>
+        <v>0.295</v>
       </c>
       <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4769500</v>
+        <v>6232500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.23</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
-        <v>63.76</v>
+        <v>49.06</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.438</v>
+        <v>0.295</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.389</v>
+        <v>0.295</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1650,40 +1650,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.18</v>
+        <v>0.005</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4141400</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H26" t="n">
-        <v>44.11</v>
-      </c>
+        <v>6131900</v>
+      </c>
+      <c r="G26" s="12" t="n"/>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.187</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1695,39 +1686,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3804900</v>
+        <v>5805100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.35</v>
+        <v>1.56</v>
       </c>
       <c r="H27" t="n">
-        <v>42.87</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.7</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1</v>
+        <v>0.459</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.985</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1740,39 +1731,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.775</v>
+        <v>5.11</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0302</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3772600</v>
+        <v>5121700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.59</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.774</v>
+        <v>5.37</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.776</v>
+        <v>5.515</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1785,39 +1776,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.0202</v>
+        <v>0.82</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3713900</v>
+        <v>5074000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>5.366</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>5.514</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1830,28 +1821,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HARNLEN</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.475</v>
+        <v>0.775</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3469600</v>
+        <v>4972600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>38.93</v>
+        <v>0.32</v>
       </c>
       <c r="H30" t="n">
-        <v>53.28</v>
+        <v>50.65</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1859,10 +1850,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.46</v>
+        <v>0.774</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.478</v>
+        <v>0.776</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1875,39 +1866,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.82</v>
+        <v>0.475</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3275000</v>
+        <v>4893700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H31" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.76</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.438</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.389</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1920,39 +1911,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.875</v>
+        <v>0.945</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.0234</v>
+        <v>0.0053</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3175100</v>
+        <v>4819100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H32" t="n">
-        <v>48.44</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.12</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.886</v>
+        <v>1</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.862</v>
+        <v>0.985</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1965,39 +1956,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INNATURE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.135</v>
+        <v>2.02</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.0385</v>
+        <v>0.0306</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3097500</v>
+        <v>4414200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>23.37</v>
+        <v>0.37</v>
       </c>
       <c r="H33" t="n">
-        <v>58.72</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.42</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.131</v>
+        <v>2.095</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.137</v>
+        <v>2.227</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2010,28 +2001,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0204</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3039200</v>
+        <v>4354700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H34" t="n">
-        <v>36.89</v>
+        <v>52.61</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2039,10 +2030,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.094</v>
+        <v>4.878</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.227</v>
+        <v>4.772</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2070,10 +2061,10 @@
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3019000</v>
+        <v>4219000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H35" t="n">
         <v>47.73</v>
@@ -2100,39 +2091,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.415</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2920100</v>
+        <v>4068200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.46</v>
+        <v>0.34</v>
       </c>
       <c r="H36" t="n">
-        <v>58.37</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.402</v>
+        <v>0.403</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.367</v>
+        <v>0.384</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2145,39 +2136,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>4.89</v>
+        <v>0.39</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0.002</v>
+        <v>0.04</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2871400</v>
+        <v>3926500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H37" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.45</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>4.877</v>
+        <v>0.461</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>4.772</v>
+        <v>0.577</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2190,28 +2181,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.575</v>
+        <v>2.57</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.036</v>
+        <v>0.0198</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2824900</v>
+        <v>3852500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H38" t="n">
-        <v>43.3</v>
+        <v>48.62</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2219,10 +2210,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.605</v>
+        <v>2.593</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.617</v>
+        <v>2.563</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2235,28 +2226,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2802800</v>
+        <v>3812200</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.24</v>
+        <v>12.43</v>
       </c>
       <c r="H39" t="n">
-        <v>56.17</v>
+        <v>74.02</v>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
@@ -2264,10 +2255,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.403</v>
+        <v>0.185</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.384</v>
+        <v>0.192</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2280,39 +2271,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.305</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2627100</v>
+        <v>3812000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="n">
-        <v>28.95</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.46</v>
+        <v>0.307</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.577</v>
+        <v>0.303</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2325,28 +2316,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.385</v>
+        <v>0.86</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.0405</v>
+        <v>0.0058</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2534500</v>
+        <v>3585100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="H41" t="n">
-        <v>64.52</v>
+        <v>46.47</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2354,9 +2345,11 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>0.885</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.862</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2368,28 +2361,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.56</v>
+        <v>0.575</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.036</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2531800</v>
+        <v>3434900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="H42" t="n">
-        <v>47.98</v>
+        <v>43.3</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2397,10 +2390,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.593</v>
+        <v>0.605</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.563</v>
+        <v>0.617</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2413,28 +2406,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.0048</v>
+        <v>0.385</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0405</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2502600</v>
+        <v>3264000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.24</v>
+        <v>0.49</v>
       </c>
       <c r="H43" t="n">
-        <v>47.3</v>
+        <v>61.86</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2442,10 +2435,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.104</v>
+        <v>0.374</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.111</v>
+        <v>0.37</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2458,28 +2451,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0172</v>
+        <v>0.265</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2411900</v>
+        <v>3147400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H44" t="n">
-        <v>24.71</v>
+        <v>42.15</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2487,10 +2480,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.287</v>
+        <v>0.28</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.49</v>
+        <v>0.282</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2503,28 +2496,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2278900</v>
+        <v>3128900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H45" t="n">
-        <v>44.37</v>
+        <v>58.37</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2532,10 +2525,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.49</v>
+        <v>0.402</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.47</v>
+        <v>0.367</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2548,39 +2541,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.76</v>
+        <v>0.135</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.0385</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2244700</v>
+        <v>3098100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.73</v>
+        <v>23.37</v>
       </c>
       <c r="H46" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.72</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.745</v>
+        <v>0.131</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.708</v>
+        <v>0.137</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2593,40 +2586,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.775</v>
+        <v>0.38</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2129000</v>
+        <v>3046800</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="H47" t="n">
-        <v>56.83</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.49</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="K47" s="9" t="n">
-        <v>0.6929999999999999</v>
-      </c>
+        <v>0.341</v>
+      </c>
+      <c r="K47" s="9" t="n"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
     </row>
@@ -2638,28 +2629,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2126100</v>
+        <v>2916200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1.2</v>
+        <v>0.28</v>
       </c>
       <c r="H48" t="n">
-        <v>47.64</v>
+        <v>63.72</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2667,10 +2658,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.904</v>
+        <v>0.626</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.895</v>
+        <v>0.619</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2683,39 +2674,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2106600</v>
+        <v>2900300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H49" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.33</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.564</v>
+        <v>1.288</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.852</v>
+        <v>1.49</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2728,39 +2719,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.485</v>
+        <v>1.45</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.014</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2051600</v>
+        <v>2623800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="H50" t="n">
-        <v>45.27</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.41</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.493</v>
+        <v>1.566</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.514</v>
+        <v>1.852</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2773,28 +2764,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.305</v>
+        <v>0.775</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0.0517</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1813600</v>
+        <v>2564800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>3.27</v>
+        <v>0.47</v>
       </c>
       <c r="H51" t="n">
-        <v>56.71</v>
+        <v>56.83</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2802,10 +2793,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.292</v>
+        <v>0.745</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.295</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2818,28 +2809,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.0157</v>
+        <v>2.09</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1754500</v>
+        <v>2534300</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H52" t="n">
-        <v>66.22</v>
+        <v>47.3</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2847,10 +2838,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.626</v>
+        <v>2.104</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.619</v>
+        <v>2.111</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2863,28 +2854,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>3.16</v>
+        <v>0.465</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0604</v>
+        <v>0.0109</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1705200</v>
+        <v>2513800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="H53" t="n">
-        <v>58.26</v>
+        <v>45.37</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2892,10 +2883,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.008</v>
+        <v>0.49</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.87</v>
+        <v>0.47</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2908,28 +2899,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.775</v>
+        <v>0.755</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0197</v>
+        <v>0.0067</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1568000</v>
+        <v>2490800</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>51.94</v>
+        <v>53.69</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2937,10 +2928,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.768</v>
+        <v>0.744</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.771</v>
+        <v>0.708</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2953,39 +2944,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>3.97</v>
+        <v>3.22</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>0.0232</v>
+        <v>0.0805</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1552200</v>
+        <v>2471800</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="H55" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.33</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>3.828</v>
+        <v>3.014</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>3.755</v>
+        <v>2.872</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2998,39 +2989,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.008</v>
+        <v>0.485</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1525600</v>
+        <v>2210300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="H56" t="n">
-        <v>43.17</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.27</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.271</v>
+        <v>0.493</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>1.317</v>
+        <v>0.514</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3043,39 +3034,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.33</v>
+        <v>0.89</v>
       </c>
       <c r="E57" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1502700</v>
+        <v>2196100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.15</v>
+        <v>1.24</v>
       </c>
       <c r="H57" t="n">
-        <v>47.41</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.337</v>
+        <v>0.904</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.337</v>
+        <v>0.895</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3103,10 +3094,10 @@
         <v>0.0115</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1491800</v>
+        <v>2095300</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H58" t="n">
         <v>53.62</v>
@@ -3133,39 +3124,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.865</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1450500</v>
+        <v>2028200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="H59" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.28</v>
+        <v>0.868</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.282</v>
+        <v>0.869</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3178,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0517</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1441300</v>
+        <v>2002600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.2</v>
+        <v>3.61</v>
       </c>
       <c r="H60" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.481</v>
+        <v>0.292</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.536</v>
+        <v>0.295</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3223,39 +3214,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0152</v>
+        <v>1.25</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1440200</v>
+        <v>1868100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H61" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.347</v>
+        <v>1.272</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.33</v>
+        <v>1.317</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3268,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>3.43</v>
+        <v>0.335</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0029</v>
+        <v>0.0152</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1432500</v>
+        <v>1858200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="H62" t="n">
-        <v>89.26000000000001</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>3.082</v>
+        <v>0.347</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.61</v>
+        <v>0.33</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3313,28 +3304,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.18</v>
+        <v>3.96</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0261</v>
+        <v>0.0206</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1388400</v>
+        <v>1851800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="H63" t="n">
-        <v>62.3</v>
+        <v>56.72</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3342,10 +3333,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.101</v>
+        <v>3.827</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.06</v>
+        <v>3.755</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3358,28 +3349,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0</v>
+        <v>2.65</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0271</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1318400</v>
+        <v>1851600</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="H64" t="n">
-        <v>14.67</v>
+        <v>54.41</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3387,9 +3378,11 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K64" s="9" t="n"/>
+        <v>2.602</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>2.603</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3401,39 +3394,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0049</v>
+        <v>3.45</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1276500</v>
+        <v>1783500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.59</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.038</v>
+        <v>3.084</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.063</v>
+        <v>2.61</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3446,39 +3439,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.305</v>
+        <v>1.16</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1226600</v>
+        <v>1756700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H66" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.54</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.314</v>
+        <v>1.2</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.357</v>
+        <v>1.284</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3491,39 +3484,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.33</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1225900</v>
+        <v>1744500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="H67" t="n">
-        <v>49.65</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.898</v>
+        <v>0.337</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.956</v>
+        <v>0.337</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3536,39 +3529,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.9</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1224300</v>
+        <v>1683900</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="H68" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.7</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.58</v>
+        <v>0.897</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.489</v>
+        <v>0.956</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3581,28 +3574,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1210500</v>
+        <v>1649200</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H69" t="n">
-        <v>60.24</v>
+        <v>41.54</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3610,10 +3603,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>4.007</v>
+        <v>0.314</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.664</v>
+        <v>0.357</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3626,39 +3619,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1177000</v>
+        <v>1600800</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H70" t="n">
-        <v>60.23</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.46</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.235</v>
+        <v>0.768</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.209</v>
+        <v>0.771</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3671,28 +3664,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>-0.0021</v>
+        <v>1.18</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0261</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1138200</v>
+        <v>1597700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="H71" t="n">
-        <v>47.78</v>
+        <v>62.3</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3700,10 +3693,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>4.728</v>
+        <v>1.101</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>4.805</v>
+        <v>1.06</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3716,39 +3709,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.46</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1131900</v>
+        <v>1545400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="H72" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.51</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.273</v>
+        <v>0.48</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.189</v>
+        <v>0.536</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3761,39 +3754,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>9.99</v>
+        <v>0.675</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>0.001</v>
+        <v>0.0305</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1115400</v>
+        <v>1534200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="H73" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.88</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>9.994</v>
+        <v>0.712</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>10.106</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3806,28 +3799,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.475</v>
+        <v>9.99</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0326</v>
+        <v>0.001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1089900</v>
+        <v>1533800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.49</v>
+        <v>0.12</v>
       </c>
       <c r="H74" t="n">
-        <v>58.83</v>
+        <v>48.1</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3835,10 +3828,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.454</v>
+        <v>9.994</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.45</v>
+        <v>10.106</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3851,39 +3844,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.37</v>
+        <v>4.2</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0071</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1048300</v>
+        <v>1492900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="H75" t="n">
-        <v>41.32</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.8</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.427</v>
+        <v>4.006</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.417</v>
+        <v>3.664</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3896,39 +3889,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.008</v>
+        <v>0.865</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1043600</v>
+        <v>1479700</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
       <c r="H76" t="n">
-        <v>53.48</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.62</v>
+        <v>0.865</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.611</v>
+        <v>0.861</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3941,39 +3934,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.945</v>
+        <v>0.26</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>0.0053</v>
+        <v>0.04</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1012300</v>
+        <v>1442000</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="H77" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.39</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.952</v>
+        <v>0.264</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.03</v>
+        <v>0.282</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3986,39 +3979,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0063</v>
+        <v>1.29</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1010600</v>
+        <v>1424600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H78" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.652</v>
+        <v>1.235</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.737</v>
+        <v>1.209</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4031,28 +4024,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.23</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>994100</v>
+        <v>1403400</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.13</v>
+        <v>0.53</v>
       </c>
       <c r="H79" t="n">
-        <v>41.4</v>
+        <v>14.67</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4060,11 +4053,9 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="K79" s="9" t="n">
-        <v>0.681</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K79" s="9" t="n"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4076,39 +4067,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0073</v>
+        <v>0.95</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>956600</v>
+        <v>1403300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H80" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.98</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.655</v>
+        <v>0.952</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.583</v>
+        <v>1.03</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4121,28 +4112,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.62</v>
+        <v>5.94</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0155</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>951700</v>
+        <v>1393900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.18</v>
+        <v>0.34</v>
       </c>
       <c r="H81" t="n">
-        <v>52.03</v>
+        <v>61.2</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4150,10 +4141,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.599</v>
+        <v>5.54</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.603</v>
+        <v>5.391</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4166,28 +4157,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.0172</v>
+        <v>2.02</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>910800</v>
+        <v>1355500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H82" t="n">
-        <v>61.09</v>
+        <v>44.59</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4195,10 +4186,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.836</v>
+        <v>2.037</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.802</v>
+        <v>2.062</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4211,28 +4202,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0784</v>
+        <v>4.72</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>889300</v>
+        <v>1336500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1.2</v>
+        <v>0.06</v>
       </c>
       <c r="H83" t="n">
-        <v>53.5</v>
+        <v>47.78</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4240,10 +4231,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.599</v>
+        <v>4.728</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.65</v>
+        <v>4.805</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4256,28 +4247,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.665</v>
+        <v>0.345</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0153</v>
+        <v>0.0147</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>885800</v>
+        <v>1314900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.18</v>
+        <v>1.54</v>
       </c>
       <c r="H84" t="n">
-        <v>43.42</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4285,10 +4276,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.711</v>
+        <v>0.331</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.317</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4301,39 +4292,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>5.89</v>
+        <v>0.475</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.048</v>
+        <v>0.0326</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>884400</v>
+        <v>1310700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.21</v>
+        <v>0.59</v>
       </c>
       <c r="H85" t="n">
-        <v>60.24</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.83</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>5.535</v>
+        <v>0.454</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>5.39</v>
+        <v>0.45</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4346,28 +4337,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0</v>
+        <v>2.23</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0276</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>866200</v>
+        <v>1293700</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.04</v>
+        <v>0.55</v>
       </c>
       <c r="H86" t="n">
-        <v>46.13</v>
+        <v>65.3</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4375,10 +4366,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.868</v>
+        <v>2.128</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.869</v>
+        <v>2.082</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4391,28 +4382,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>0</v>
+        <v>1.32</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>856900</v>
+        <v>1286100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.08</v>
+        <v>0.49</v>
       </c>
       <c r="H87" t="n">
-        <v>43.55</v>
+        <v>56.33</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4420,10 +4411,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.725</v>
+        <v>1.273</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.747</v>
+        <v>1.189</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4436,39 +4427,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>0</v>
+        <v>2.67</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>851500</v>
+        <v>1261700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
       <c r="H88" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.641</v>
+        <v>2.726</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.629</v>
+        <v>2.747</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4481,28 +4472,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.025</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>834300</v>
+        <v>1232700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
-        <v>29.83</v>
+        <v>57.76</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4510,10 +4501,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.527</v>
+        <v>0.58</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.489</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4526,39 +4517,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0184</v>
+        <v>0.265</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>799800</v>
+        <v>1184700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H90" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2.126</v>
+        <v>0.267</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.081</v>
+        <v>0.269</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4571,28 +4562,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>6.86</v>
+        <v>7.11</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.0316</v>
+        <v>0.0014</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>770800</v>
+        <v>1183300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>60.6</v>
+        <v>32.25</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4600,10 +4591,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>6.364</v>
+        <v>7.336</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>6.025</v>
+        <v>7.612</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4625,19 +4616,19 @@
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0156</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>767600</v>
+        <v>1122800</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H92" t="n">
-        <v>39.69</v>
+        <v>39.03</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4645,10 +4636,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.678</v>
+        <v>0.677</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4661,28 +4652,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>732800</v>
+        <v>1118000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="H93" t="n">
-        <v>31.47</v>
+        <v>41.4</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4690,10 +4681,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>7.335</v>
+        <v>0.644</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>7.611</v>
+        <v>0.681</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4706,39 +4697,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.96</v>
+        <v>0.43</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>-0.0103</v>
+        <v>-0.0227</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>709700</v>
+        <v>1114300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.89</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.945</v>
+        <v>0.475</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.895</v>
+        <v>0.607</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4751,28 +4742,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>0.0069</v>
+        <v>2.36</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>687900</v>
+        <v>1111800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H95" t="n">
-        <v>58.01</v>
+        <v>40.15</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4780,10 +4771,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.809</v>
+        <v>2.426</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.699</v>
+        <v>2.417</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4796,28 +4787,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.15</v>
+        <v>0.605</v>
       </c>
       <c r="E96" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>678100</v>
+        <v>1099600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="H96" t="n">
-        <v>33.75</v>
+        <v>64.84</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4825,10 +4816,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.199</v>
+        <v>0.548</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.284</v>
+        <v>0.489</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4841,39 +4832,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0076</v>
+        <v>1.58</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>670200</v>
+        <v>1089900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H97" t="n">
-        <v>56.52</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.17</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.255</v>
+        <v>1.651</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.123</v>
+        <v>1.737</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4886,39 +4877,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>11.06</v>
+        <v>0.28</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.0317</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>665400</v>
+        <v>1082500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H98" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>10.528</v>
+        <v>0.295</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>9.907</v>
+        <v>0.32</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4931,28 +4922,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.505</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>656500</v>
+        <v>1059700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
-        <v>36.42</v>
+        <v>29.83</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4960,10 +4951,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.865</v>
+        <v>0.527</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.927</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4976,28 +4967,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0</v>
+        <v>2.91</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>643800</v>
+        <v>1057300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H100" t="n">
-        <v>64.84</v>
+        <v>57.54</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -5005,10 +4996,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.548</v>
+        <v>2.808</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.489</v>
+        <v>2.699</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5021,28 +5012,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0</v>
+        <v>11.1</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0354</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>638700</v>
+        <v>1055800</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="H101" t="n">
-        <v>64.31999999999999</v>
+        <v>62.81</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5050,10 +5041,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>3.827</v>
+        <v>10.532</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>3.294</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5066,28 +5057,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.72</v>
+        <v>6.82</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.0074</v>
+        <v>0.0104</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>631400</v>
+        <v>1055800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="H102" t="n">
-        <v>39.02</v>
+        <v>38.87</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5095,10 +5086,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.822</v>
+        <v>7.027</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.959</v>
+        <v>7.471</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5111,39 +5102,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.62</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>624800</v>
+        <v>1043600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="H103" t="n">
-        <v>63.93</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.48</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.846</v>
+        <v>0.62</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.378</v>
+        <v>0.611</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5156,28 +5147,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6.82</v>
+        <v>6.94</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.0104</v>
+        <v>0.0436</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>609000</v>
+        <v>1040500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H104" t="n">
-        <v>38.87</v>
+        <v>61.61</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5185,10 +5176,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>7.027</v>
+        <v>6.371</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>7.471</v>
+        <v>6.026</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5201,39 +5192,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>1.06</v>
+        <v>4.1</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0073</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>599300</v>
+        <v>1037900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H105" t="n">
-        <v>39.53</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.1</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>1.123</v>
+        <v>3.824</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>1.249</v>
+        <v>3.294</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5246,39 +5237,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>564500</v>
+        <v>1004900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="H106" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.78</v>
+        <v>0.583</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5291,45 +5282,1305 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>7.49</v>
+        <v>0.88</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0317</v>
+        <v>0.0115</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>513300</v>
+        <v>981200</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="H107" t="n">
-        <v>55.78</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.38</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>7.308</v>
+        <v>0.835</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>6.968</v>
+        <v>0.802</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PIE</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0.07190000000000001</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>957000</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H108" t="n">
+        <v>52.69</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>851500</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H109" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>850500</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H110" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>832000</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H111" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>6.969</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>813300</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H112" t="n">
+        <v>36.42</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>802500</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H113" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>797600</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H114" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>791800</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H115" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>2.846</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>785400</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>1.631</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1.673</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>772100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H117" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>2.822</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>2.959</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>717900</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H118" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>KEEMING</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0766</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>698000</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H119" t="n">
+        <v>57.24</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>2.563</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>2.522</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>668000</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H120" t="n">
+        <v>50.79</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>641300</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H121" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>640700</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H122" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>7.405</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>7.796</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>640500</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H123" t="n">
+        <v>47.01</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>626200</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H124" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>6.819</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>613800</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H125" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>610200</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H126" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>574200</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H127" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>6.626</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>566500</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H128" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>565000</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H129" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>564500</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H130" t="n">
+        <v>49.18</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>7.556</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>551700</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H131" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>541500</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H132" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>529000</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H133" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>525100</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H134" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>5.065</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>5.036</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>517700</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>5.726</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M107"/>
+  <autoFilter ref="A1:M135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0708</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4009700</v>
+        <v>4162200</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>60.71</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.605高于50日均线0.529约14%，RSI 60.71处中性偏强区间，未超买，信号技术面可靠性尚可。</t>
+          <t>SAR转多信号，RSI 60.71未超买，现价高于50日均线约14%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0583</v>
+        <v>0.0667</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3032200</v>
+        <v>3819300</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.77</v>
+        <v>0.97</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>58.24</v>
+        <v>59.01</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.24处中性偏上，未超买；现价0.635高于50日均线0.585约8.5%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 59.01未超买，现价高于50日均线约9.4%，技术面信号可靠性偏正面。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0339</v>
+        <v>0.0678</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1539200</v>
+        <v>3054900</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.86</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.104</v>
+        <v>1.108</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.974</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.86接近超买区，现价高于50日均线约25%，技术面信号偏强但需留意RSI高位。</t>
+          <t>SAR转多信号，现价1.26高于50日均线0.974约29%，RSI 67.32接近超买区，信号偏强但需留意短线过热。</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>42958500</v>
+        <v>45971900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H5" t="n">
         <v>32.57</v>
@@ -761,40 +761,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.21</v>
+        <v>0.005</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.07690000000000001</v>
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>27041900</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="H6" t="n">
-        <v>88.65000000000001</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.118</v>
-      </c>
+        <v>30603100</v>
+      </c>
+      <c r="G6" s="12" t="n"/>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="9" t="n"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -806,39 +797,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.215</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0.1026</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18098000</v>
+        <v>27744100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.21</v>
+        <v>5.42</v>
       </c>
       <c r="H7" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.11</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.319</v>
+        <v>0.129</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.269</v>
+        <v>0.118</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -862,14 +853,14 @@
       <c r="D8" s="9" t="n">
         <v>0.485</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="17" t="n">
         <v>0.0211</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>17813100</v>
+        <v>20167400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="H8" t="n">
         <v>74.08</v>
@@ -896,28 +887,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.055</v>
+        <v>0.345</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0</v>
+        <v>0.0299</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>14553000</v>
+        <v>19610700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>3.96</v>
+        <v>0.23</v>
       </c>
       <c r="H9" t="n">
-        <v>48.65</v>
+        <v>64.92</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -925,10 +916,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.055</v>
+        <v>0.319</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.058</v>
+        <v>0.269</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -941,28 +932,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.155</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12969600</v>
+        <v>16369500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="H10" t="n">
-        <v>81.18000000000001</v>
+        <v>47.73</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -970,10 +961,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.667</v>
+        <v>0.156</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.569</v>
+        <v>0.156</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -986,39 +977,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.16</v>
+        <v>0.055</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10738600</v>
+        <v>14553000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.18</v>
+        <v>3.96</v>
       </c>
       <c r="H11" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.65</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.159</v>
+        <v>0.055</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.148</v>
+        <v>0.058</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1031,39 +1022,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.1111</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10560600</v>
+        <v>14237200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="H12" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.17</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.06</v>
+        <v>0.159</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.148</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1076,39 +1067,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.0386</v>
+        <v>0.735</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9511200</v>
+        <v>13569000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="H13" t="n">
-        <v>62.67</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.18000000000001</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.989</v>
+        <v>0.667</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.808</v>
+        <v>0.569</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1121,39 +1112,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0</v>
+        <v>0.0278</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9312300</v>
+        <v>13172400</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2.39</v>
+        <v>0.67</v>
       </c>
       <c r="H14" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.98</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.079</v>
+        <v>0.185</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.076</v>
+        <v>0.187</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1166,39 +1157,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.93</v>
+        <v>2.16</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8386000</v>
+        <v>11761400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H15" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.867</v>
+        <v>1.99</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.769</v>
+        <v>1.808</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1211,28 +1202,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0.1111</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7967700</v>
+        <v>11575600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.22</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="n">
-        <v>42.79</v>
+        <v>37.48</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1240,10 +1231,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.453</v>
+        <v>0.06</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.473</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1256,39 +1247,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0929</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7875300</v>
+        <v>10595800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.59</v>
+        <v>0.14</v>
       </c>
       <c r="H17" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.61</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.637</v>
+        <v>0.769</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1301,36 +1292,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7508000</v>
+        <v>9373000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.38</v>
+        <v>2.41</v>
       </c>
       <c r="H18" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.076</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1342,28 +1337,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0</v>
+        <v>0.1143</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7497700</v>
+        <v>8264200</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>37.97</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>44.67</v>
+        <v>49.99</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1371,10 +1366,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.074</v>
+        <v>0.637</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1387,28 +1382,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7210000</v>
+        <v>8067800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="H20" t="n">
-        <v>44.11</v>
+        <v>41.09</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1416,10 +1411,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.185</v>
+        <v>0.453</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.187</v>
+        <v>0.473</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1432,39 +1427,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HARNLEN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E21" s="17" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6870100</v>
+        <v>7608900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>77.09</v>
+        <v>0.39</v>
       </c>
       <c r="H21" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.459</v>
+        <v>0.307</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.478</v>
+        <v>0.303</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1477,33 +1472,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.72</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6321500</v>
+        <v>7547900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.2</v>
+        <v>38.22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>44.67</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="J22" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.074</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1515,40 +1517,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6293400</v>
+        <v>7546500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="H23" t="n">
-        <v>41.24</v>
+        <v>48.42</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0.279</v>
-      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1560,28 +1558,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.595</v>
+        <v>0.265</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.04389999999999999</v>
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6280900</v>
+        <v>7056200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="H24" t="n">
-        <v>55.89</v>
+        <v>41.24</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1589,10 +1587,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.571</v>
+        <v>0.284</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.548</v>
+        <v>0.279</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1605,28 +1603,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.595</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>0</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6232500</v>
+        <v>7000700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.86</v>
+        <v>0.34</v>
       </c>
       <c r="H25" t="n">
-        <v>49.06</v>
+        <v>55.89</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1634,10 +1632,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.571</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.295</v>
+        <v>0.548</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1650,31 +1648,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E26" s="17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6131900</v>
-      </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+        <v>6870100</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="H26" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.478</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1686,28 +1693,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5805100</v>
+        <v>6552600</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.56</v>
+        <v>0.42</v>
       </c>
       <c r="H27" t="n">
-        <v>83.7</v>
+        <v>50.65</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1715,10 +1722,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.459</v>
+        <v>0.774</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.439</v>
+        <v>0.776</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1731,40 +1738,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0302</v>
+        <v>0.72</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5121700</v>
+        <v>6500600</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H28" t="n">
-        <v>39.59</v>
+        <v>0.2</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>5.515</v>
-      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1776,39 +1776,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.82</v>
+        <v>5.11</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.0302</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5074000</v>
+        <v>6379200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.32</v>
+        <v>0.43</v>
       </c>
       <c r="H29" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.59</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>5.515</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1821,28 +1821,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.775</v>
+        <v>0.82</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4972600</v>
+        <v>6233700</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H30" t="n">
-        <v>50.65</v>
+        <v>54.27</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.776</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1866,28 +1866,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E31" s="17" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E31" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4893700</v>
+        <v>6232500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.24</v>
+        <v>1.86</v>
       </c>
       <c r="H31" t="n">
-        <v>63.76</v>
+        <v>49.06</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.438</v>
+        <v>0.295</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.389</v>
+        <v>0.295</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1922,14 +1922,14 @@
       <c r="D32" s="9" t="n">
         <v>0.945</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" s="17" t="n">
         <v>0.0053</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4819100</v>
+        <v>6144800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H32" t="n">
         <v>42.12</v>
@@ -1956,39 +1956,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0306</v>
+        <v>0.535</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4414200</v>
+        <v>6045600</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.37</v>
+        <v>1.62</v>
       </c>
       <c r="H33" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.095</v>
+        <v>0.458</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.227</v>
+        <v>0.438</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -2001,28 +2001,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.9</v>
+        <v>0.475</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.004099999999999999</v>
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4354700</v>
+        <v>5924300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H34" t="n">
-        <v>52.61</v>
+        <v>63.76</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>4.878</v>
+        <v>0.438</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>4.772</v>
+        <v>0.389</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2046,28 +2046,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.155</v>
+        <v>0.38</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4219000</v>
+        <v>5407400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.11</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>47.73</v>
+        <v>58.17</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.156</v>
+        <v>0.373</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.156</v>
+        <v>0.37</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2091,28 +2091,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.415</v>
+        <v>0.39</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4068200</v>
+        <v>5171100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="H36" t="n">
-        <v>56.17</v>
+        <v>31.45</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.403</v>
+        <v>0.461</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.384</v>
+        <v>0.577</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2136,28 +2136,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.39</v>
+        <v>0.415</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3926500</v>
+        <v>5138100</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="H37" t="n">
-        <v>31.45</v>
+        <v>56.17</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.461</v>
+        <v>0.403</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.577</v>
+        <v>0.384</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2181,28 +2181,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.0198</v>
+        <v>4.9</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3852500</v>
+        <v>5136200</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H38" t="n">
-        <v>48.62</v>
+        <v>52.61</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.593</v>
+        <v>4.878</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.563</v>
+        <v>4.772</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2226,39 +2226,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.1351</v>
+        <v>2.02</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0.0306</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3812200</v>
+        <v>4816700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>12.43</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="n">
-        <v>74.02</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.42</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.185</v>
+        <v>2.095</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.192</v>
+        <v>2.227</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2271,28 +2271,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3812000</v>
+        <v>4787600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H40" t="n">
-        <v>47.42</v>
+        <v>39.09</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.307</v>
+        <v>0.208</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.303</v>
+        <v>0.227</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2316,39 +2316,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0058</v>
+        <v>2.56</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3585100</v>
+        <v>4550900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.98</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.885</v>
+        <v>2.593</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.862</v>
+        <v>2.563</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2361,39 +2361,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.036</v>
+        <v>0.21</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3434900</v>
+        <v>4271400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.39</v>
+        <v>13.93</v>
       </c>
       <c r="H42" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.02</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.605</v>
+        <v>0.185</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.617</v>
+        <v>0.192</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2406,28 +2406,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0405</v>
+        <v>0.64</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3264000</v>
+        <v>3978700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H43" t="n">
-        <v>61.86</v>
+        <v>63.72</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.374</v>
+        <v>0.626</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.37</v>
+        <v>0.619</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2451,39 +2451,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.145</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0.1154</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3147400</v>
+        <v>3916000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.46</v>
+        <v>29.54</v>
       </c>
       <c r="H44" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.91</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.28</v>
+        <v>0.132</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.282</v>
+        <v>0.137</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2496,28 +2496,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>3844800</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>0.43</v>
       </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>3128900</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H45" t="n">
-        <v>58.37</v>
+        <v>43.3</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.402</v>
+        <v>0.605</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.367</v>
+        <v>0.617</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2541,39 +2541,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INNATURE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.135</v>
+        <v>0.26</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3098100</v>
+        <v>3834200</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>23.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>58.72</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.131</v>
+        <v>0.28</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.137</v>
+        <v>0.282</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2597,14 +2597,14 @@
       <c r="D47" s="9" t="n">
         <v>0.38</v>
       </c>
-      <c r="E47" s="15" t="n">
+      <c r="E47" s="17" t="n">
         <v>0.027</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3046800</v>
+        <v>3726000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="H47" t="n">
         <v>63.49</v>
@@ -2629,28 +2629,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.86</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2916200</v>
+        <v>3685100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H48" t="n">
-        <v>63.72</v>
+        <v>46.47</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.626</v>
+        <v>0.885</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.619</v>
+        <v>0.862</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2674,28 +2674,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.0086</v>
+        <v>0.425</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2900300</v>
+        <v>3574000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="H49" t="n">
-        <v>25.33</v>
+        <v>57.47</v>
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.288</v>
+        <v>0.401</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.49</v>
+        <v>0.367</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2719,28 +2719,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>1.45</v>
+        <v>0.865</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2623800</v>
+        <v>3438100</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H50" t="n">
-        <v>32.41</v>
+        <v>46.13</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1.566</v>
+        <v>0.868</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1.852</v>
+        <v>0.869</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2775,14 +2775,14 @@
       <c r="D51" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="17" t="n">
         <v>0.006500000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2564800</v>
+        <v>3164400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="H51" t="n">
         <v>56.83</v>
@@ -2809,39 +2809,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.09</v>
+        <v>1.15</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>-0.0048</v>
+        <v>-0.0086</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2534300</v>
+        <v>3042500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H52" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.33</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.104</v>
+        <v>1.288</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.111</v>
+        <v>1.49</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2854,39 +2854,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>0.0109</v>
+        <v>3.97</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0.0232</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2513800</v>
+        <v>2994600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.28</v>
+        <v>0.87</v>
       </c>
       <c r="H53" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.07</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.49</v>
+        <v>3.828</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.47</v>
+        <v>3.755</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2899,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.755</v>
+        <v>0.435</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.0067</v>
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2490800</v>
+        <v>2889300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="H54" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.744</v>
+        <v>0.43</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.708</v>
+        <v>0.417</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,39 +2944,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0805</v>
+        <v>1.45</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0.014</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2471800</v>
+        <v>2864400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.93</v>
+        <v>0.21</v>
       </c>
       <c r="H55" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.41</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>3.014</v>
+        <v>1.566</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2.872</v>
+        <v>1.852</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,28 +2989,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.465</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2210300</v>
+        <v>2817600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H56" t="n">
-        <v>45.27</v>
+        <v>45.37</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.493</v>
+        <v>0.49</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.514</v>
+        <v>0.47</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,39 +3034,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.89</v>
+        <v>3.23</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>0</v>
+        <v>0.0839</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2196100</v>
+        <v>2702200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="H57" t="n">
-        <v>47.64</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.66</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.904</v>
+        <v>3.015</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.895</v>
+        <v>2.872</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,39 +3079,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0115</v>
+        <v>0.485</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2095300</v>
+        <v>2671900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H58" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.27</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.43</v>
+        <v>0.493</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.417</v>
+        <v>0.514</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3124,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.865</v>
+        <v>0.755</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>0.0067</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2028200</v>
+        <v>2597400</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.1</v>
+        <v>0.85</v>
       </c>
       <c r="H59" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.69</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.868</v>
+        <v>0.744</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.869</v>
+        <v>0.708</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0517</v>
+        <v>2.09</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2002600</v>
+        <v>2593600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>3.61</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.3</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.292</v>
+        <v>2.104</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.295</v>
+        <v>2.111</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,28 +3214,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.25</v>
+        <v>9.99</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1868100</v>
+        <v>2583000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H61" t="n">
-        <v>44.58</v>
+        <v>48.1</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.272</v>
+        <v>9.994</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.317</v>
+        <v>10.106</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,39 +3259,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.335</v>
+        <v>0.89</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0152</v>
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1858200</v>
+        <v>2548200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.23</v>
+        <v>1.44</v>
       </c>
       <c r="H62" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.347</v>
+        <v>0.904</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.33</v>
+        <v>0.895</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,39 +3304,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0206</v>
+        <v>1.16</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1851800</v>
+        <v>2527500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="H63" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.54</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>3.827</v>
+        <v>1.2</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>3.755</v>
+        <v>1.284</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,28 +3349,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0271</v>
+        <v>1.57</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1851600</v>
+        <v>2200500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H64" t="n">
-        <v>54.41</v>
+        <v>37.28</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>2.602</v>
+        <v>1.65</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.603</v>
+        <v>1.737</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,39 +3394,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>3.45</v>
+        <v>0.33</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.008800000000000001</v>
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1783500</v>
+        <v>2158100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="H65" t="n">
-        <v>89.59</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.41</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>3.084</v>
+        <v>0.337</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.61</v>
+        <v>0.337</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3439,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.17</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1756700</v>
+        <v>2095700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H66" t="n">
-        <v>36.54</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.28</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.284</v>
+        <v>1.059</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,28 +3484,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E67" s="17" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E67" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1744500</v>
+        <v>2057000</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="H67" t="n">
-        <v>47.41</v>
+        <v>50.44</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.337</v>
+        <v>0.865</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.337</v>
+        <v>0.861</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,39 +3529,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.665</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0.0153</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1683900</v>
+        <v>2044800</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>0.41</v>
       </c>
       <c r="H68" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.42</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.897</v>
+        <v>0.711</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.956</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,39 +3574,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.0167</v>
+        <v>2.62</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1649200</v>
+        <v>2040800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H69" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.03</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.314</v>
+        <v>2.599</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.357</v>
+        <v>2.603</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,39 +3619,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.77</v>
+        <v>0.3</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1600800</v>
+        <v>2029500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H70" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.96</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.768</v>
+        <v>0.313</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.771</v>
+        <v>0.357</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,28 +3664,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0261</v>
+        <v>1.67</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1597700</v>
+        <v>2019000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H71" t="n">
-        <v>62.3</v>
+        <v>54.74</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.101</v>
+        <v>1.631</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1.06</v>
+        <v>1.673</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,39 +3709,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0108</v>
+        <v>0.3</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1545400</v>
+        <v>2002700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.22</v>
+        <v>3.61</v>
       </c>
       <c r="H72" t="n">
-        <v>36.51</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.48</v>
+        <v>0.291</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.536</v>
+        <v>0.295</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,39 +3754,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0305</v>
+        <v>3.46</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1534200</v>
+        <v>1980400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="H73" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.75</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.712</v>
+        <v>3.085</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.6909999999999999</v>
+        <v>2.611</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,28 +3799,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.001</v>
+        <v>0.95</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1533800</v>
+        <v>1955700</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.12</v>
+        <v>0.48</v>
       </c>
       <c r="H74" t="n">
-        <v>48.1</v>
+        <v>43.98</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>9.994</v>
+        <v>0.952</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>10.106</v>
+        <v>1.03</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,39 +3844,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0071</v>
+        <v>5.85</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0.0409</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1492900</v>
+        <v>1938100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H75" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.45</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>4.006</v>
+        <v>5.532</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>3.664</v>
+        <v>5.389</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,28 +3889,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.865</v>
+        <v>0.335</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>0.0152</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1479700</v>
+        <v>1887800</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="H76" t="n">
-        <v>50.44</v>
+        <v>45.4</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.865</v>
+        <v>0.347</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.861</v>
+        <v>0.33</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,39 +3934,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>1883500</v>
+      </c>
+      <c r="G77" s="12" t="n">
         <v>0.26</v>
       </c>
-      <c r="E77" s="15" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F77" s="11" t="n">
-        <v>1442000</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>0.25</v>
-      </c>
       <c r="H77" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.264</v>
+        <v>1.272</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.282</v>
+        <v>1.317</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,28 +3979,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.29</v>
+        <v>0.63</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1424600</v>
+        <v>1859600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.21</v>
+        <v>0.52</v>
       </c>
       <c r="H78" t="n">
-        <v>60.23</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.235</v>
+        <v>0.621</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.209</v>
+        <v>0.611</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,38 +4024,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>4.72</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1403400</v>
+        <v>1859100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
       <c r="H79" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.78</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K79" s="9" t="n"/>
+        <v>4.728</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>4.805</v>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
     </row>
@@ -4067,39 +4069,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0106</v>
+        <v>2.37</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1403300</v>
+        <v>1849900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H80" t="n">
-        <v>43.98</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.32</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.952</v>
+        <v>2.427</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.03</v>
+        <v>2.417</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4112,39 +4114,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.05690000000000001</v>
+        <v>4.17</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0142</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1393900</v>
+        <v>1849100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H81" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.53</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>5.54</v>
+        <v>4.003</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>5.391</v>
+        <v>3.664</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4166,19 +4168,19 @@
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.0049</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1355500</v>
+        <v>1836600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H82" t="n">
-        <v>44.59</v>
+        <v>46.65</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4186,10 +4188,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.037</v>
+        <v>2.038</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.062</v>
+        <v>2.063</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4202,28 +4204,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0021</v>
+        <v>1.31</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1336500</v>
+        <v>1819300</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="H83" t="n">
-        <v>47.78</v>
+        <v>62.34</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4231,10 +4233,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>4.728</v>
+        <v>1.237</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>4.805</v>
+        <v>1.21</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4247,39 +4249,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.345</v>
+        <v>0.905</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0147</v>
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1314900</v>
+        <v>1800200</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.54</v>
+        <v>0.44</v>
       </c>
       <c r="H84" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.331</v>
+        <v>0.898</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.317</v>
+        <v>0.956</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4292,39 +4294,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0326</v>
+        <v>0.255</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1310700</v>
+        <v>1699500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H85" t="n">
-        <v>58.83</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.93</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.454</v>
+        <v>0.264</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.45</v>
+        <v>0.282</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4337,39 +4339,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.0276</v>
+        <v>2.91</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1293700</v>
+        <v>1691100</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.55</v>
+        <v>0.22</v>
       </c>
       <c r="H86" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.54</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.128</v>
+        <v>2.808</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.082</v>
+        <v>2.699</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4391,19 +4393,19 @@
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0233</v>
+        <v>1.34</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>0.0388</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1286100</v>
+        <v>1621500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="H87" t="n">
-        <v>56.33</v>
+        <v>57.85</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4411,10 +4413,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.273</v>
+        <v>1.275</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.189</v>
+        <v>1.19</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4427,39 +4429,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.67</v>
+        <v>0.465</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.0038</v>
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1261700</v>
+        <v>1606200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="H88" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.02</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.726</v>
+        <v>0.481</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.747</v>
+        <v>0.536</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4472,28 +4474,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>0.025</v>
+        <v>0.77</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1232700</v>
+        <v>1600800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H89" t="n">
-        <v>57.76</v>
+        <v>50.46</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4501,10 +4503,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.58</v>
+        <v>0.768</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.489</v>
+        <v>0.771</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4517,39 +4519,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.0185</v>
+        <v>11.16</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0.04099999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1184700</v>
+        <v>1593900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.2</v>
+        <v>0.43</v>
       </c>
       <c r="H90" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.55</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.267</v>
+        <v>10.538</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.269</v>
+        <v>9.909000000000001</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4562,39 +4564,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0014</v>
+        <v>2.24</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1183300</v>
+        <v>1565800</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="H91" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.14</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>7.336</v>
+        <v>2.128</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>7.612</v>
+        <v>2.082</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4607,39 +4609,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0156</v>
+        <v>0.47</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1122800</v>
+        <v>1545000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="H92" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.31</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.677</v>
+        <v>0.454</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.732</v>
+        <v>0.45</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4652,28 +4654,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
         <v>0.61</v>
       </c>
-      <c r="E93" s="15" t="n">
+      <c r="E93" s="17" t="n">
         <v>0.0167</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1118000</v>
+        <v>1544600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H93" t="n">
-        <v>41.4</v>
+        <v>57.18</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4681,10 +4683,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.644</v>
+        <v>0.58</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.681</v>
+        <v>0.489</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4697,28 +4699,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>-0.0227</v>
+        <v>0.875</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1114300</v>
+        <v>1446700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>27.89</v>
+        <v>59.65</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4726,10 +4728,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.475</v>
+        <v>0.835</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.607</v>
+        <v>0.802</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4742,28 +4744,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0126</v>
+        <v>6.78</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1111800</v>
+        <v>1438600</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H95" t="n">
-        <v>40.15</v>
+        <v>37.17</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4771,10 +4773,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.426</v>
+        <v>7.023</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.417</v>
+        <v>7.47</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4787,28 +4789,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.605</v>
+        <v>6.32</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1099600</v>
+        <v>1413400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H96" t="n">
-        <v>64.84</v>
+        <v>45.83</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4816,10 +4818,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.548</v>
+        <v>6.34</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.489</v>
+        <v>6.626</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4832,28 +4834,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E97" s="17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E97" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1089900</v>
+        <v>1404100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="H97" t="n">
-        <v>38.17</v>
+        <v>14.67</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4861,11 +4863,9 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.651</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>1.737</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K97" s="9" t="n"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4877,28 +4877,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.345</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1082500</v>
+        <v>1403500</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.16</v>
+        <v>1.64</v>
       </c>
       <c r="H98" t="n">
-        <v>41.19</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.295</v>
+        <v>0.331</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.32</v>
+        <v>0.317</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4922,39 +4922,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.505</v>
+        <v>6.91</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>0.0391</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1059700</v>
+        <v>1397100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="H99" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.24</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.527</v>
+        <v>6.369</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>6.026</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4967,28 +4967,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0034</v>
+        <v>7.11</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1057300</v>
+        <v>1364200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H100" t="n">
-        <v>57.54</v>
+        <v>32.25</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.808</v>
+        <v>7.336</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.699</v>
+        <v>7.612</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5012,39 +5012,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>11.1</v>
+        <v>2.66</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1055800</v>
+        <v>1342100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="H101" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.55</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>10.532</v>
+        <v>2.725</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>9.907999999999999</v>
+        <v>2.747</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5057,28 +5057,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0.0104</v>
+        <v>0.615</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.025</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1055800</v>
+        <v>1282100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="H102" t="n">
-        <v>38.87</v>
+        <v>42.51</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5086,10 +5086,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>7.027</v>
+        <v>0.644</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>7.471</v>
+        <v>0.681</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5102,39 +5102,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.62</v>
+        <v>0.265</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.0185</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1043600</v>
+        <v>1268100</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H103" t="n">
-        <v>53.48</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.62</v>
+        <v>0.267</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.611</v>
+        <v>0.269</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5147,28 +5147,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0.0436</v>
+        <v>0.625</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1040500</v>
+        <v>1254100</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H104" t="n">
-        <v>61.61</v>
+        <v>38.39</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>6.371</v>
+        <v>0.677</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>6.026</v>
+        <v>0.732</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5192,39 +5192,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>4.1</v>
+        <v>0.435</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0073</v>
+        <v>-0.0114</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1037900</v>
+        <v>1247300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H105" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.69</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>3.824</v>
+        <v>0.476</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>3.294</v>
+        <v>0.607</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5237,28 +5237,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0073</v>
+        <v>0.61</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1004900</v>
+        <v>1229500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H106" t="n">
-        <v>58.94</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.655</v>
+        <v>0.549</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.583</v>
+        <v>0.489</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5282,39 +5282,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0.0115</v>
+        <v>4.09</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>981200</v>
+        <v>1172800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H107" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.7</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.835</v>
+        <v>3.824</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.802</v>
+        <v>3.293</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5327,39 +5327,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.28</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>957000</v>
+        <v>1163800</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>1.29</v>
+        <v>0.18</v>
       </c>
       <c r="H108" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.19</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.598</v>
+        <v>0.295</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.649</v>
+        <v>0.32</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5372,28 +5372,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>1.36</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>851500</v>
+        <v>1151000</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H109" t="n">
-        <v>54.73</v>
+        <v>46.29</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.641</v>
+        <v>1.365</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.629</v>
+        <v>1.435</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5417,39 +5417,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>1.31</v>
+        <v>2.71</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>850500</v>
+        <v>1149800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H110" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.06</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>1.256</v>
+        <v>2.821</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1.123</v>
+        <v>2.959</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5471,19 +5471,19 @@
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>7.58</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0441</v>
+        <v>7.55</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0.0399</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>832000</v>
+        <v>1128000</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>57.45</v>
+        <v>56.9</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>7.316</v>
+        <v>7.313</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>6.969</v>
@@ -5507,28 +5507,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.835</v>
+        <v>0.505</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.0121</v>
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>813300</v>
+        <v>1098300</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H112" t="n">
-        <v>36.42</v>
+        <v>29.83</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.865</v>
+        <v>0.527</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.927</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5552,28 +5552,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.96</v>
+        <v>7.34</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>-0.0103</v>
+        <v>-0.0014</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>802500</v>
+        <v>1076000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H113" t="n">
-        <v>59.52</v>
+        <v>41.58</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.945</v>
+        <v>7.405</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.895</v>
+        <v>7.796</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5597,39 +5597,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>-0.0145</v>
+        <v>0.32</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>797600</v>
+        <v>1029200</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="H114" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.79</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.365</v>
+        <v>0.323</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1.435</v>
+        <v>0.332</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5642,39 +5642,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3.05</v>
+        <v>0.205</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>791800</v>
+        <v>1028700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="H115" t="n">
-        <v>63.93</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.26000000000001</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.846</v>
+        <v>0.175</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.378</v>
+        <v>0.164</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5687,39 +5687,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.285</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>785400</v>
+        <v>1023400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
       <c r="H116" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.631</v>
+        <v>0.272</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.673</v>
+        <v>0.259</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5732,39 +5732,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0074</v>
+        <v>1.64</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0.07190000000000001</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>772100</v>
+        <v>1008100</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.22</v>
+        <v>1.36</v>
       </c>
       <c r="H117" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.69</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>2.822</v>
+        <v>1.598</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>2.959</v>
+        <v>1.649</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5777,39 +5777,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>717900</v>
+        <v>1007900</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H118" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.78</v>
+        <v>0.583</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5822,28 +5822,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0.0766</v>
+        <v>0.835</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>698000</v>
+        <v>978000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.95</v>
+        <v>0.35</v>
       </c>
       <c r="H119" t="n">
-        <v>57.24</v>
+        <v>36.42</v>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.563</v>
+        <v>0.865</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.522</v>
+        <v>0.927</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5867,39 +5867,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0.02</v>
+        <v>5.74</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>668000</v>
+        <v>970300</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="H120" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.04</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.025</v>
+        <v>5.816</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.979</v>
+        <v>6.07</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5912,39 +5912,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E121" s="17" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E121" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>641300</v>
+        <v>965000</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="H121" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.645</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.825</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5957,39 +5957,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0014</v>
+        <v>3.06</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>640700</v>
+        <v>938100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="H122" t="n">
-        <v>41.58</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.25</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>7.405</v>
+        <v>2.847</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>7.796</v>
+        <v>2.378</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6002,39 +6002,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0069</v>
+        <v>5.1</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>640500</v>
+        <v>924200</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.06</v>
+        <v>0.24</v>
       </c>
       <c r="H123" t="n">
-        <v>47.01</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.41</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.733</v>
+        <v>5.063</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.724</v>
+        <v>5.036</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6047,28 +6047,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>6.74</v>
+        <v>0.71</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0218</v>
+        <v>-0.0139</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>626200</v>
+        <v>918300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H124" t="n">
-        <v>46.9</v>
+        <v>46.3</v>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>6.8</v>
+        <v>0.732</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>6.819</v>
+        <v>0.724</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6092,39 +6092,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0</v>
+        <v>0.955</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>613800</v>
+        <v>911800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H125" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.51</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.124</v>
+        <v>0.944</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.249</v>
+        <v>0.895</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6137,28 +6137,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.0052</v>
+        <v>1.31</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>610200</v>
+        <v>904900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H126" t="n">
-        <v>52.71</v>
+        <v>57.49</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.931</v>
+        <v>1.256</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.009</v>
+        <v>1.123</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6182,39 +6182,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0016</v>
+        <v>2.68</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>574200</v>
+        <v>880700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.08</v>
+        <v>1.2</v>
       </c>
       <c r="H127" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.71</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>6.34</v>
+        <v>2.564</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>6.626</v>
+        <v>2.523</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6227,28 +6227,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.64</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>566500</v>
+        <v>852100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H128" t="n">
-        <v>59.55</v>
+        <v>51.43</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.293</v>
+        <v>0.641</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.214</v>
+        <v>0.629</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6272,28 +6272,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E129" s="17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E129" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>565000</v>
+        <v>800500</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="H129" t="n">
-        <v>63.09</v>
+        <v>46.05</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.634</v>
+        <v>2.645</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.633</v>
+        <v>2.825</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6317,39 +6317,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0.0027</v>
+        <v>1.02</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>564500</v>
+        <v>776000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H130" t="n">
-        <v>49.18</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.79</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>7.556</v>
+        <v>1.025</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>7.694</v>
+        <v>0.979</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6362,28 +6362,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0</v>
+        <v>6.75</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0203</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>551700</v>
+        <v>775800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H131" t="n">
-        <v>57.42</v>
+        <v>47.42</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.182</v>
+        <v>6.801</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.152</v>
+        <v>6.819</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6407,28 +6407,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.95</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>541500</v>
+        <v>736300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.08</v>
+        <v>0.64</v>
       </c>
       <c r="H132" t="n">
-        <v>71.13</v>
+        <v>51.21</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.984</v>
+        <v>0.93</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.965</v>
+        <v>1.009</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6452,28 +6452,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.0071</v>
+        <v>13.3</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>529000</v>
+        <v>723800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H133" t="n">
-        <v>41.04</v>
+        <v>59.15</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.711</v>
+        <v>13.104</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.766</v>
+        <v>13.297</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6497,28 +6497,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>5.12</v>
+        <v>0.83</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>0.0039</v>
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>525100</v>
+        <v>717900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H134" t="n">
-        <v>53.39</v>
+        <v>70.69</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>5.065</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>5.036</v>
+        <v>0.78</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6542,45 +6542,1035 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E135" s="15" t="n">
-        <v>0.0019</v>
+        <v>1.35</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>517700</v>
+        <v>701000</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.48</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>5.451</v>
+        <v>1.296</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>5.726</v>
+        <v>1.247</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>693500</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H136" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>5.451</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>5.726</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>677300</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H137" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>1.124</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SUNCON</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>667600</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H138" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>7.555</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>657300</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>1.965</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>645000</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H140" t="n">
+        <v>63.09</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>637200</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H141" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>603400</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H142" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>4.549</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>4.642</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AXREIT</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>602300</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H143" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>593000</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H144" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>2.294</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>2.214</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>582500</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H145" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>564300</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H146" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>558400</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H147" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>4.438</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>GASMSIA</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>556200</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H148" t="n">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>5.173</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>5.029</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>548900</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H149" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>548900</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H150" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>1.711</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.766</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>541800</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H151" t="n">
+        <v>59.59</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>2.739</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>535100</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H152" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>527500</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H153" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>4.323</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>515700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H154" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>515500</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H155" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>513700</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H156" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>513500</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H157" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M135"/>
+  <autoFilter ref="A1:M157"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0708</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4162200</v>
+        <v>4240800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>60.71</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 60.71未超买，现价高于50日均线约14%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，现价0.605高于50日均线0.529，RSI 60.71未超买，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0667</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3819300</v>
+        <v>4482300</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>59.01</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 59.01未超买，现价高于50日均线约9.4%，技术面信号可靠性偏正面。</t>
+          <t>SAR转多信号，RSI 59.01未超买，现价高于50日均线约9.4%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0678</v>
+        <v>0.07629999999999999</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3054900</v>
+        <v>3294900</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.31999999999999</v>
+        <v>67.88</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.108</v>
+        <v>1.109</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.974</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价1.26高于50日均线0.974约29%，RSI 67.32接近超买区，信号偏强但需留意短线过热。</t>
+          <t>SAR转多信号，RSI 67.88接近超买区，现价高于50日均线约30%，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>45971900</v>
+        <v>54613500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="H5" t="n">
         <v>32.57</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>30603100</v>
+        <v>30872000</v>
       </c>
       <c r="G6" s="12" t="n"/>
       <c r="I6" s="16" t="inlineStr">
@@ -812,10 +812,10 @@
         <v>0.1026</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>27744100</v>
+        <v>28185700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>5.42</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="n">
         <v>89.11</v>
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.485</v>
+        <v>0.49</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0.0211</v>
+        <v>0.0316</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>20167400</v>
+        <v>22201800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="n">
-        <v>74.08</v>
+        <v>74.78</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>0.326</v>
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.345</v>
+        <v>0.35</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>0.0299</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>19610700</v>
+        <v>21499800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>64.92</v>
+        <v>66.2</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -932,28 +932,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0</v>
+        <v>0.945</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>16369500</v>
+        <v>19115300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H10" t="n">
-        <v>47.73</v>
+        <v>67.73</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.156</v>
+        <v>0.868</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.156</v>
+        <v>0.769</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -977,39 +977,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.055</v>
+        <v>0.155</v>
       </c>
       <c r="E11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14553000</v>
+        <v>16369500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>3.96</v>
+        <v>0.45</v>
       </c>
       <c r="H11" t="n">
-        <v>48.65</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.055</v>
+        <v>0.156</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.058</v>
+        <v>0.156</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         <v>0.0333</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14237200</v>
+        <v>14756200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H12" t="n">
         <v>49.17</v>
@@ -1067,39 +1067,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.735</v>
+        <v>0.05</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13569000</v>
+        <v>14611300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.57</v>
+        <v>3.98</v>
       </c>
       <c r="H13" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.01</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.667</v>
+        <v>0.055</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.569</v>
+        <v>0.057</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1112,28 +1112,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.185</v>
+        <v>2.17</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.0278</v>
+        <v>0.0483</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13172400</v>
+        <v>13921200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>48.98</v>
+        <v>63.51</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.185</v>
+        <v>1.991</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.187</v>
+        <v>1.808</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1157,39 +1157,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0.0435</v>
+        <v>0.735</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>11761400</v>
+        <v>13619000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="H15" t="n">
-        <v>63.09</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.18000000000001</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.99</v>
+        <v>0.667</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.808</v>
+        <v>0.569</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0.1111</v>
+        <v>0.18</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11575600</v>
+        <v>13179400</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.1</v>
+        <v>0.67</v>
       </c>
       <c r="H16" t="n">
-        <v>37.48</v>
+        <v>44.11</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.06</v>
+        <v>0.185</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1247,39 +1247,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0.0054</v>
+        <v>0.0282</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10595800</v>
+        <v>12911100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.14</v>
+        <v>0.86</v>
       </c>
       <c r="H17" t="n">
-        <v>66.61</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.18</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.867</v>
+        <v>5.369</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.769</v>
+        <v>5.515</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1292,39 +1292,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="E18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>9373000</v>
+        <v>12555700</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2.41</v>
+        <v>1.2</v>
       </c>
       <c r="H18" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.77</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.079</v>
+        <v>0.059</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1337,28 +1337,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0.1143</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8264200</v>
+        <v>10644300</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.67</v>
+        <v>0.55</v>
       </c>
       <c r="H19" t="n">
-        <v>49.99</v>
+        <v>47.42</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.637</v>
+        <v>0.303</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="E20" s="17" t="n">
-        <v>0.0238</v>
+        <v>0.0105</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>8067800</v>
+        <v>9478900</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="n">
-        <v>41.09</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.453</v>
+        <v>0.438</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.473</v>
+        <v>0.389</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1427,39 +1427,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.305</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="E21" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7608900</v>
+        <v>9374000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.39</v>
+        <v>2.41</v>
       </c>
       <c r="H21" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.56999999999999</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.307</v>
+        <v>0.079</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.303</v>
+        <v>0.076</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7547900</v>
+        <v>8438900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>38.22</v>
+        <v>1.7</v>
       </c>
       <c r="H22" t="n">
-        <v>44.67</v>
+        <v>49.36</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.074</v>
+        <v>0.637</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1517,36 +1517,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7546500</v>
+        <v>8175600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="H23" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+        <v>50.65</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1558,28 +1562,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7056200</v>
+        <v>8079100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.64</v>
+        <v>0.23</v>
       </c>
       <c r="H24" t="n">
-        <v>41.24</v>
+        <v>41.09</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1587,10 +1591,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.284</v>
+        <v>0.453</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.279</v>
+        <v>0.473</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1603,39 +1607,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7000700</v>
+        <v>7909700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="H25" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.571</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.548</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1648,39 +1652,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HARNLEN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0.04389999999999999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6870100</v>
+        <v>7683400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>77.09</v>
+        <v>0.38</v>
       </c>
       <c r="H26" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.89</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.459</v>
+        <v>0.571</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.478</v>
+        <v>0.548</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1693,40 +1697,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6552600</v>
+        <v>7551300</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H27" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0.776</v>
-      </c>
+        <v>48.42</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1738,33 +1738,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0.0588</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6500600</v>
+        <v>7547900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.2</v>
+        <v>38.22</v>
+      </c>
+      <c r="H28" t="n">
+        <v>44.67</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+      <c r="J28" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.074</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1776,28 +1783,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0.0302</v>
+        <v>0.265</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6379200</v>
+        <v>7081100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H29" t="n">
-        <v>39.59</v>
+        <v>41.24</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1805,10 +1812,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>5.37</v>
+        <v>0.284</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>5.515</v>
+        <v>0.279</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1821,40 +1828,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>0</v>
+        <v>0.72</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6233700</v>
+        <v>6925100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H30" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>0.8139999999999999</v>
-      </c>
+        <v>0.21</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1866,39 +1866,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.295</v>
+        <v>0.47</v>
       </c>
       <c r="E31" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6232500</v>
+        <v>6870100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.86</v>
+        <v>77.09</v>
       </c>
       <c r="H31" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.02</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.295</v>
+        <v>0.459</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.295</v>
+        <v>0.478</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1920,19 +1920,19 @@
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6144800</v>
+        <v>6794300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H32" t="n">
-        <v>42.12</v>
+        <v>40.81</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0.985</v>
@@ -1971,10 +1971,10 @@
         <v>0.0388</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6045600</v>
+        <v>6482400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="H33" t="n">
         <v>83.09999999999999</v>
@@ -2001,28 +2001,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.475</v>
+        <v>0.295</v>
       </c>
       <c r="E34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5924300</v>
+        <v>6232500</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.29</v>
+        <v>1.86</v>
       </c>
       <c r="H34" t="n">
-        <v>63.76</v>
+        <v>49.06</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.438</v>
+        <v>0.295</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.389</v>
+        <v>0.295</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2046,28 +2046,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0.027</v>
+        <v>0.865</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5407400</v>
+        <v>6140700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="H35" t="n">
-        <v>58.17</v>
+        <v>46.13</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.373</v>
+        <v>0.868</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.37</v>
+        <v>0.869</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2091,39 +2091,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.39</v>
+        <v>4.89</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.04</v>
+        <v>0.002</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5171100</v>
+        <v>6041800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H36" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.01</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.461</v>
+        <v>4.877</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.577</v>
+        <v>4.772</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5138100</v>
+        <v>5924200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
         <v>56.17</v>
@@ -2181,39 +2181,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>4.9</v>
+        <v>0.39</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5136200</v>
+        <v>5897500</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="H38" t="n">
-        <v>52.61</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.45</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>4.878</v>
+        <v>0.461</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>4.772</v>
+        <v>0.577</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2226,39 +2226,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.02</v>
+        <v>0.38</v>
       </c>
       <c r="E39" s="17" t="n">
-        <v>0.0306</v>
+        <v>0.027</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4816700</v>
+        <v>5667700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="H39" t="n">
-        <v>39.42</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.17</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.095</v>
+        <v>0.373</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.227</v>
+        <v>0.37</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2286,10 +2286,10 @@
         <v>-0.025</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4787600</v>
+        <v>5591500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H40" t="n">
         <v>39.09</v>
@@ -2316,28 +2316,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.56</v>
+        <v>2.01</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>0.0159</v>
+        <v>0.0255</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4550900</v>
+        <v>5587800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="H41" t="n">
-        <v>47.98</v>
+        <v>38.18</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.593</v>
+        <v>2.094</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.563</v>
+        <v>2.227</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2361,28 +2361,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>0.1351</v>
+        <v>0.0217</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4271400</v>
+        <v>5366800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>13.93</v>
+        <v>2.42</v>
       </c>
       <c r="H42" t="n">
-        <v>74.02</v>
+        <v>57.31</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.185</v>
+        <v>0.454</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.192</v>
+        <v>0.45</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2406,39 +2406,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.64</v>
+        <v>0.585</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0541</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3978700</v>
+        <v>5329800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="H43" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.17</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.626</v>
+        <v>0.606</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.619</v>
+        <v>0.617</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2451,39 +2451,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INNATURE</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0.1154</v>
+        <v>1.15</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3916000</v>
+        <v>5115800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>29.54</v>
+        <v>0.64</v>
       </c>
       <c r="H44" t="n">
-        <v>73.91</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.75</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.132</v>
+        <v>1.199</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.137</v>
+        <v>1.284</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2496,39 +2496,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.575</v>
+        <v>0.64</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>0.036</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3844800</v>
+        <v>5085600</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H45" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.72</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.605</v>
+        <v>0.626</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.617</v>
+        <v>0.619</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2541,28 +2541,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.125</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3834200</v>
+        <v>5082500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="H46" t="n">
-        <v>39.48</v>
+        <v>48.22</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.28</v>
+        <v>0.037</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.282</v>
+        <v>0.034</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2586,38 +2586,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.38</v>
+        <v>2.57</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>0.027</v>
+        <v>0.0198</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3726000</v>
+        <v>5059600</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.66</v>
+        <v>0.29</v>
       </c>
       <c r="H47" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.62</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="K47" s="9" t="n"/>
+        <v>2.593</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>2.563</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
     </row>
@@ -2629,28 +2631,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="E48" s="17" t="n">
-        <v>0.0058</v>
+        <v>0.0174</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3685100</v>
+        <v>4869500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="H48" t="n">
-        <v>46.47</v>
+        <v>61.28</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2658,10 +2660,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.885</v>
+        <v>1.1</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.862</v>
+        <v>1.059</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2674,39 +2676,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3574000</v>
+        <v>4426700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.57</v>
+        <v>14.44</v>
       </c>
       <c r="H49" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.02</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.401</v>
+        <v>0.185</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.367</v>
+        <v>0.192</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2719,28 +2721,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0</v>
+        <v>0.14</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3438100</v>
+        <v>4310600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.17</v>
+        <v>32.52</v>
       </c>
       <c r="H50" t="n">
-        <v>46.13</v>
+        <v>68.03</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2748,10 +2750,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.868</v>
+        <v>0.131</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.869</v>
+        <v>0.137</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2764,28 +2766,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3164400</v>
+        <v>4260600</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="H51" t="n">
-        <v>56.83</v>
+        <v>39.48</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2793,10 +2795,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.745</v>
+        <v>0.28</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.282</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2809,40 +2811,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0086</v>
+        <v>0.38</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.027</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3042500</v>
+        <v>3989100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.47</v>
+        <v>0.71</v>
       </c>
       <c r="H52" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.49</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.288</v>
-      </c>
-      <c r="K52" s="9" t="n">
-        <v>1.49</v>
-      </c>
+        <v>0.341</v>
+      </c>
+      <c r="K52" s="9" t="n"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
     </row>
@@ -2854,39 +2854,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0.0232</v>
+        <v>1.15</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2994600</v>
+        <v>3865300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.87</v>
+        <v>0.6</v>
       </c>
       <c r="H53" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.33</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>3.828</v>
+        <v>1.288</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>3.755</v>
+        <v>1.49</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,28 +2899,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2889300</v>
+        <v>3810300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
-        <v>52.42</v>
+        <v>47.3</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.43</v>
+        <v>2.104</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.417</v>
+        <v>2.111</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2944,28 +2944,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.45</v>
+        <v>0.865</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>0.014</v>
+        <v>0.0117</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2864400</v>
+        <v>3809200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.21</v>
+        <v>0.61</v>
       </c>
       <c r="H55" t="n">
-        <v>32.41</v>
+        <v>47.14</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.566</v>
+        <v>0.885</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>1.852</v>
+        <v>0.862</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2989,28 +2989,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0.0109</v>
+        <v>0.425</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2817600</v>
+        <v>3798700</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H56" t="n">
-        <v>45.37</v>
+        <v>57.47</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.49</v>
+        <v>0.401</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.47</v>
+        <v>0.367</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,28 +3034,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>3.23</v>
+        <v>0.125</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>0.0839</v>
+        <v>0.0417</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2702200</v>
+        <v>3509000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="H57" t="n">
-        <v>60.66</v>
+        <v>54.74</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>3.015</v>
+        <v>0.122</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.872</v>
+        <v>0.123</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.485</v>
+        <v>0.78</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>0.0211</v>
+        <v>0.013</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2671900</v>
+        <v>3430800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="H58" t="n">
-        <v>45.27</v>
+        <v>57.5</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.493</v>
+        <v>0.745</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.514</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3124,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.755</v>
+        <v>3.96</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.0067</v>
+        <v>0.0206</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2597400</v>
+        <v>3381300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="H59" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.72</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.744</v>
+        <v>3.827</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.708</v>
+        <v>3.755</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3169,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0048</v>
+        <v>6.3</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2593600</v>
+        <v>3140700</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="H60" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.57</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.104</v>
+        <v>6.339</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.111</v>
+        <v>6.626</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,39 +3214,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>9.99</v>
+        <v>3.22</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>0.001</v>
+        <v>0.0805</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2583000</v>
+        <v>3087100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.21</v>
+        <v>1.16</v>
       </c>
       <c r="H61" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.33</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>9.994</v>
+        <v>3.014</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>10.106</v>
+        <v>2.872</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3259,28 +3259,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2548200</v>
+        <v>3087000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.44</v>
+        <v>0.65</v>
       </c>
       <c r="H62" t="n">
-        <v>47.64</v>
+        <v>42.77</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.904</v>
+        <v>0.172</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.895</v>
+        <v>0.19</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3304,39 +3304,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2527500</v>
+        <v>3082900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>36.54</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.41</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.2</v>
+        <v>1.566</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.284</v>
+        <v>1.852</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,39 +3349,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0063</v>
+        <v>0.435</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2200500</v>
+        <v>2908700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H64" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.65</v>
+        <v>0.43</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.737</v>
+        <v>0.417</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,28 +3394,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.33</v>
+        <v>0.865</v>
       </c>
       <c r="E65" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2158100</v>
+        <v>2877000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>47.41</v>
+        <v>50.44</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.337</v>
+        <v>0.865</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.337</v>
+        <v>0.861</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3439,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.0174</v>
+        <v>0.46</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2095700</v>
+        <v>2875700</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H66" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.37</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.1</v>
+        <v>0.49</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.059</v>
+        <v>0.47</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,39 +3484,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0</v>
+        <v>1.66</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2057000</v>
+        <v>2817700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.72</v>
+        <v>0.35</v>
       </c>
       <c r="H67" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.47</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.865</v>
+        <v>1.63</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.861</v>
+        <v>1.673</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,39 +3529,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.665</v>
+        <v>0.895</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>0.0153</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2044800</v>
+        <v>2778700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.41</v>
+        <v>1.57</v>
       </c>
       <c r="H68" t="n">
-        <v>43.42</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.68</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.711</v>
+        <v>0.904</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.895</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,39 +3574,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.62</v>
+        <v>9.99</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>0.0155</v>
+        <v>0.001</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2040800</v>
+        <v>2761700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>52.03</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.1</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.599</v>
+        <v>9.994</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.603</v>
+        <v>10.106</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,39 +3619,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0.0316</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2029500</v>
+        <v>2743400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="H70" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.313</v>
+        <v>0.494</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.357</v>
+        <v>0.514</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,39 +3664,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.67</v>
+        <v>0.755</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>0.0121</v>
+        <v>0.0067</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2019000</v>
+        <v>2656000</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.25</v>
+        <v>0.87</v>
       </c>
       <c r="H71" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.69</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.631</v>
+        <v>0.744</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1.673</v>
+        <v>0.708</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,28 +3709,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>0.0345</v>
+        <v>1.57</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2002700</v>
+        <v>2623800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>3.61</v>
+        <v>0.42</v>
       </c>
       <c r="H72" t="n">
-        <v>54.53</v>
+        <v>37.28</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.291</v>
+        <v>1.65</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.295</v>
+        <v>1.737</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,28 +3754,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>0.0117</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1980400</v>
+        <v>2596500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H73" t="n">
-        <v>89.75</v>
+        <v>39.36</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>3.085</v>
+        <v>0.951</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.611</v>
+        <v>1.03</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3799,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0.0106</v>
+        <v>0.555</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1955700</v>
+        <v>2549400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.48</v>
+        <v>1.25</v>
       </c>
       <c r="H74" t="n">
-        <v>43.98</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.18</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.952</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.03</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,39 +3844,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0.0409</v>
+        <v>4.13</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.0236</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1938100</v>
+        <v>2410900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="H75" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.92</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>5.532</v>
+        <v>3.999</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>5.389</v>
+        <v>3.663</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,28 +3889,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.335</v>
+        <v>2.64</v>
       </c>
       <c r="E76" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.0233</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1887800</v>
+        <v>2358600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H76" t="n">
-        <v>45.4</v>
+        <v>53.65</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.347</v>
+        <v>2.601</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.33</v>
+        <v>2.603</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,28 +3934,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0.008</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1883500</v>
+        <v>2341600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.26</v>
+        <v>0.66</v>
       </c>
       <c r="H77" t="n">
-        <v>44.58</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.272</v>
+        <v>0.621</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.317</v>
+        <v>0.611</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,39 +3979,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.63</v>
+        <v>5.84</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>0.008</v>
+        <v>0.0391</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1859600</v>
+        <v>2308700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.24</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.621</v>
+        <v>5.531</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.611</v>
+        <v>5.389</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         <v>-0.0021</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1859100</v>
+        <v>2299300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H79" t="n">
         <v>47.78</v>
@@ -4069,28 +4069,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.67</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0.0229</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1849900</v>
+        <v>2244300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H80" t="n">
-        <v>41.32</v>
+        <v>44.16</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.427</v>
+        <v>0.712</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.417</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,39 +4114,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>4.17</v>
+        <v>0.325</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>-0.0142</v>
+        <v>-0.0152</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1849100</v>
+        <v>2183800</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H81" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.66</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>4.003</v>
+        <v>0.337</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>3.664</v>
+        <v>0.337</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,39 +4159,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0049</v>
+        <v>11.1</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0.0354</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1836600</v>
+        <v>2174800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H82" t="n">
-        <v>46.65</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.038</v>
+        <v>10.532</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.063</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4204,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>0.0155</v>
+        <v>2.37</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1819300</v>
+        <v>2106900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H83" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.32</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.237</v>
+        <v>2.427</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.21</v>
+        <v>2.417</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,28 +4249,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1800200</v>
+        <v>2105900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H84" t="n">
-        <v>48.12</v>
+        <v>41.54</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.898</v>
+        <v>0.314</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.956</v>
+        <v>0.357</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.255</v>
+        <v>1.3</v>
       </c>
       <c r="E85" s="17" t="n">
-        <v>0.02</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1699500</v>
+        <v>2033300</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.31</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.264</v>
+        <v>1.236</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.282</v>
+        <v>1.209</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,39 +4339,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.91</v>
+        <v>3.46</v>
       </c>
       <c r="E86" s="17" t="n">
-        <v>0.0034</v>
+        <v>0.0117</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1691100</v>
+        <v>2029200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
       </c>
       <c r="H86" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.75</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.808</v>
+        <v>3.085</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.699</v>
+        <v>2.611</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,39 +4384,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>0.0388</v>
+        <v>1.25</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1621500</v>
+        <v>2020900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.62</v>
+        <v>0.28</v>
       </c>
       <c r="H87" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.275</v>
+        <v>1.272</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.19</v>
+        <v>1.317</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,39 +4429,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1606200</v>
+        <v>2007400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.69</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.481</v>
+        <v>0.476</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.536</v>
+        <v>0.607</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,28 +4474,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.77</v>
+        <v>0.3</v>
       </c>
       <c r="E89" s="17" t="n">
-        <v>0.0132</v>
+        <v>0.0345</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1600800</v>
+        <v>2004600</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.21</v>
+        <v>3.62</v>
       </c>
       <c r="H89" t="n">
-        <v>50.46</v>
+        <v>54.53</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4503,10 +4503,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.768</v>
+        <v>0.291</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.771</v>
+        <v>0.295</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,28 +4519,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>11.16</v>
+        <v>6.95</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0451</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1593900</v>
+        <v>1973200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.43</v>
+        <v>0.34</v>
       </c>
       <c r="H90" t="n">
-        <v>63.55</v>
+        <v>61.74</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>10.538</v>
+        <v>6.372</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>9.909000000000001</v>
+        <v>6.027</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,39 +4564,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.24</v>
+        <v>0.335</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>0.0323</v>
+        <v>0.0152</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1565800</v>
+        <v>1942300</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.66</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.4</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.128</v>
+        <v>0.347</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.082</v>
+        <v>0.33</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4609,40 +4609,38 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.47</v>
+        <v>0.235</v>
       </c>
       <c r="E92" s="17" t="n">
         <v>0.0217</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1545000</v>
+        <v>1937200</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H92" t="n">
-        <v>57.31</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.87</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="K92" s="9" t="n">
-        <v>0.45</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4654,28 +4652,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.61</v>
+        <v>6.78</v>
       </c>
       <c r="E93" s="17" t="n">
-        <v>0.0167</v>
+        <v>0.0044</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1544600</v>
+        <v>1914600</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H93" t="n">
-        <v>57.18</v>
+        <v>37.17</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4683,10 +4681,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.58</v>
+        <v>7.023</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.489</v>
+        <v>7.47</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4699,28 +4697,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0.005699999999999999</v>
+        <v>2.02</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1446700</v>
+        <v>1910700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H94" t="n">
-        <v>59.65</v>
+        <v>44.59</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4728,10 +4726,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.835</v>
+        <v>2.037</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.802</v>
+        <v>2.062</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4744,39 +4742,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>0.0044</v>
+        <v>0.905</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1438600</v>
+        <v>1880000</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="H95" t="n">
-        <v>37.17</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>7.023</v>
+        <v>0.898</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>7.47</v>
+        <v>0.956</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4789,39 +4787,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>6.32</v>
+        <v>2.91</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>0.0032</v>
+        <v>0.0034</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1413400</v>
+        <v>1836800</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H96" t="n">
-        <v>45.83</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.54</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>6.34</v>
+        <v>2.808</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>6.626</v>
+        <v>2.699</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4834,38 +4832,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0</v>
+        <v>1.36</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1404100</v>
+        <v>1817000</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="H97" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K97" s="9" t="n"/>
+        <v>1.365</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1.435</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4877,28 +4877,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.345</v>
+        <v>0.26</v>
       </c>
       <c r="E98" s="17" t="n">
-        <v>0.0147</v>
+        <v>0.04</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1403500</v>
+        <v>1763900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>1.64</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>67.54000000000001</v>
+        <v>46.39</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.331</v>
+        <v>0.264</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.317</v>
+        <v>0.282</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4922,39 +4922,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.265</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1397100</v>
+        <v>1740600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="H99" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>6.369</v>
+        <v>0.267</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>6.026</v>
+        <v>0.269</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0.0014</v>
+        <v>4.06</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1364200</v>
+        <v>1728500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="H100" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.54</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>7.336</v>
+        <v>3.821</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>7.612</v>
+        <v>3.293</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5012,28 +5012,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>0</v>
+        <v>1.33</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0.031</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1342100</v>
+        <v>1703000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="H101" t="n">
-        <v>43.55</v>
+        <v>57.1</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5041,10 +5041,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.725</v>
+        <v>1.274</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.747</v>
+        <v>1.19</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5057,39 +5057,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.615</v>
+        <v>2.23</v>
       </c>
       <c r="E102" s="17" t="n">
-        <v>0.025</v>
+        <v>0.0276</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1282100</v>
+        <v>1694600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="H102" t="n">
-        <v>42.51</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.644</v>
+        <v>2.128</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.681</v>
+        <v>2.082</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5102,39 +5102,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.265</v>
+        <v>0.46</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0185</v>
+        <v>-0.0108</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1268100</v>
+        <v>1647800</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.51</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.267</v>
+        <v>0.48</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.269</v>
+        <v>0.536</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5147,28 +5147,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.0234</v>
+        <v>2.67</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1254100</v>
+        <v>1634600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.4</v>
+        <v>0.16</v>
       </c>
       <c r="H104" t="n">
-        <v>38.39</v>
+        <v>44.52</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.677</v>
+        <v>2.726</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.732</v>
+        <v>2.747</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5192,28 +5192,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.0114</v>
+        <v>0.61</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1247300</v>
+        <v>1627700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H105" t="n">
-        <v>28.69</v>
+        <v>57.18</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.476</v>
+        <v>0.58</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.607</v>
+        <v>0.489</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5237,28 +5237,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.0132</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1229500</v>
+        <v>1626800</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H106" t="n">
-        <v>65.48999999999999</v>
+        <v>50.46</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5266,10 +5266,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.549</v>
+        <v>0.768</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.489</v>
+        <v>0.771</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5282,39 +5282,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>-0.0097</v>
+        <v>0.88</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1172800</v>
+        <v>1623600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="H107" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.38</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>3.824</v>
+        <v>0.835</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>3.293</v>
+        <v>0.802</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5327,39 +5327,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.83</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1163800</v>
+        <v>1608200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="H108" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.69</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.295</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.32</v>
+        <v>0.78</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5372,39 +5372,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.36</v>
+        <v>0.625</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0145</v>
+        <v>-0.0234</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1151000</v>
+        <v>1578900</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="H109" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.39</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>1.365</v>
+        <v>0.677</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.435</v>
+        <v>0.732</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5417,28 +5417,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.71</v>
+        <v>7.11</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>0.0037</v>
+        <v>0.0014</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1149800</v>
+        <v>1553800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="H110" t="n">
-        <v>38.06</v>
+        <v>32.25</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.821</v>
+        <v>7.336</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.959</v>
+        <v>7.612</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5462,39 +5462,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0.0399</v>
+        <v>1.12</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1128000</v>
+        <v>1488800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.25</v>
+        <v>0.77</v>
       </c>
       <c r="H111" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.01</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>7.313</v>
+        <v>1.19</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>6.969</v>
+        <v>1.302</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5507,28 +5507,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1098300</v>
+        <v>1468000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.38</v>
+        <v>1.72</v>
       </c>
       <c r="H112" t="n">
-        <v>29.83</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.527</v>
+        <v>0.331</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5552,28 +5552,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0014</v>
+        <v>5.11</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0.002</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1076000</v>
+        <v>1467900</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H113" t="n">
-        <v>41.58</v>
+        <v>52.9</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>7.405</v>
+        <v>5.064</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>7.796</v>
+        <v>5.036</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5597,39 +5597,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0</v>
+        <v>5.73</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1029200</v>
+        <v>1406700</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.7</v>
+        <v>0.17</v>
       </c>
       <c r="H114" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.28</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.323</v>
+        <v>5.815</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.332</v>
+        <v>6.069</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5642,39 +5642,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0</v>
+        <v>2.72</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1028700</v>
+        <v>1358600</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="H115" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.02</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.175</v>
+        <v>2.822</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.164</v>
+        <v>2.959</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5687,28 +5687,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.285</v>
+        <v>0.61</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>0.0556</v>
+        <v>0.0167</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1023400</v>
+        <v>1345300</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.47</v>
+        <v>0.17</v>
       </c>
       <c r="H116" t="n">
-        <v>59.75</v>
+        <v>41.4</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.272</v>
+        <v>0.644</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.259</v>
+        <v>0.681</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5732,39 +5732,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.705</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1008100</v>
+        <v>1296200</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>1.36</v>
+        <v>0.12</v>
       </c>
       <c r="H117" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.61</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.598</v>
+        <v>0.732</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.649</v>
+        <v>0.724</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5777,28 +5777,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0073</v>
+        <v>0.505</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1007900</v>
+        <v>1265700</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H118" t="n">
-        <v>58.94</v>
+        <v>29.83</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.655</v>
+        <v>0.527</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.583</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5822,28 +5822,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>0.0121</v>
+        <v>0.215</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>978000</v>
+        <v>1246400</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.35</v>
+        <v>1.06</v>
       </c>
       <c r="H119" t="n">
-        <v>36.42</v>
+        <v>61.3</v>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.865</v>
+        <v>0.211</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.927</v>
+        <v>0.207</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5867,39 +5867,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>5.74</v>
+        <v>0.61</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0083</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>970300</v>
+        <v>1246300</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H120" t="n">
-        <v>41.04</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>5.816</v>
+        <v>0.549</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>6.07</v>
+        <v>0.489</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5912,39 +5912,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>0</v>
+        <v>7.52</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0.0358</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>965000</v>
+        <v>1243900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="H121" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I121" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.35</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.31</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>6.968</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5957,28 +5957,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>3.06</v>
+        <v>0.275</v>
       </c>
       <c r="E122" s="17" t="n">
-        <v>0.02</v>
+        <v>0.0185</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>938100</v>
+        <v>1184300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>64.25</v>
+        <v>38.81</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>2.847</v>
+        <v>0.295</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.378</v>
+        <v>0.32</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6002,28 +6002,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E123" s="15" t="n">
-        <v>0</v>
+        <v>7.34</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>924200</v>
+        <v>1181900</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H123" t="n">
-        <v>52.41</v>
+        <v>41.58</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>5.063</v>
+        <v>7.405</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>5.036</v>
+        <v>7.796</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6047,39 +6047,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0139</v>
+        <v>1.31</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>918300</v>
+        <v>1161100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.49</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.732</v>
+        <v>1.256</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.724</v>
+        <v>1.123</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6092,28 +6092,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0155</v>
+        <v>13.36</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0.006</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>911800</v>
+        <v>1151200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H125" t="n">
-        <v>57.51</v>
+        <v>61.41</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.944</v>
+        <v>13.109</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.895</v>
+        <v>13.298</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6137,39 +6137,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>904900</v>
+        <v>1099500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H126" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.256</v>
+        <v>0.865</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.123</v>
+        <v>0.927</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6182,28 +6182,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="E127" s="17" t="n">
-        <v>0.0806</v>
+        <v>0.0077</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>880700</v>
+        <v>1087300</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>1.2</v>
+        <v>0.18</v>
       </c>
       <c r="H127" t="n">
-        <v>57.71</v>
+        <v>46.93</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.564</v>
+        <v>2.647</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.523</v>
+        <v>2.826</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6227,28 +6227,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.205</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>852100</v>
+        <v>1064100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.42</v>
+        <v>0.6</v>
       </c>
       <c r="H128" t="n">
-        <v>51.43</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.641</v>
+        <v>0.175</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.629</v>
+        <v>0.164</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6272,39 +6272,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0</v>
+        <v>0.68</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>800500</v>
+        <v>1046300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H129" t="n">
-        <v>46.05</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.645</v>
+        <v>0.655</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.825</v>
+        <v>0.583</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6317,28 +6317,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.02</v>
+        <v>0.285</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>0.02</v>
+        <v>0.0556</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>776000</v>
+        <v>1040800</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="H130" t="n">
-        <v>50.79</v>
+        <v>59.75</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6346,10 +6346,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.025</v>
+        <v>0.272</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.979</v>
+        <v>0.259</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6362,28 +6362,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0203</v>
+        <v>0.32</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>775800</v>
+        <v>1030000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="H131" t="n">
-        <v>47.42</v>
+        <v>46.79</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>6.801</v>
+        <v>0.323</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>6.819</v>
+        <v>0.332</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6407,39 +6407,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.95</v>
+        <v>6.76</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>-0.0155</v>
+        <v>-0.0189</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>736300</v>
+        <v>1025300</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="H132" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.95</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.93</v>
+        <v>6.802</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.009</v>
+        <v>6.82</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6452,28 +6452,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>13.3</v>
+        <v>1.64</v>
       </c>
       <c r="E133" s="17" t="n">
-        <v>0.0015</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>723800</v>
+        <v>1024300</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.12</v>
+        <v>1.38</v>
       </c>
       <c r="H133" t="n">
-        <v>59.15</v>
+        <v>52.69</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>13.104</v>
+        <v>1.598</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>13.297</v>
+        <v>1.649</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6497,39 +6497,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0</v>
+        <v>3.05</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>717900</v>
+        <v>1013000</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H134" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.93</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>2.846</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.78</v>
+        <v>2.378</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6542,28 +6542,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.35</v>
+        <v>2.14</v>
       </c>
       <c r="E135" s="17" t="n">
-        <v>0.0227</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>701000</v>
+        <v>981300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="H135" t="n">
-        <v>55.48</v>
+        <v>71.13</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.296</v>
+        <v>1.984</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.247</v>
+        <v>1.965</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6587,39 +6587,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>GASMSIA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>5.31</v>
+        <v>5.45</v>
       </c>
       <c r="E136" s="17" t="n">
-        <v>0.0019</v>
+        <v>0.0302</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>693500</v>
+        <v>950500</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="H136" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>5.451</v>
+        <v>5.173</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>5.726</v>
+        <v>5.029</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6632,39 +6632,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>0</v>
+        <v>4.45</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>677300</v>
+        <v>944300</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H137" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.57</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.124</v>
+        <v>4.549</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.249</v>
+        <v>4.642</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6677,28 +6677,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.96</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>667600</v>
+        <v>923800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H138" t="n">
-        <v>48.65</v>
+        <v>59.52</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>7.555</v>
+        <v>0.945</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>7.694</v>
+        <v>0.895</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6722,39 +6722,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>2.14</v>
+        <v>1.23</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>657300</v>
+        <v>918300</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H139" t="n">
-        <v>71.13</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.68</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.984</v>
+        <v>1.183</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.965</v>
+        <v>1.152</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6767,28 +6767,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>0</v>
+        <v>2.68</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>645000</v>
+        <v>913600</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.62</v>
+        <v>1.24</v>
       </c>
       <c r="H140" t="n">
-        <v>63.09</v>
+        <v>57.71</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6796,10 +6796,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.634</v>
+        <v>2.564</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.633</v>
+        <v>2.523</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6812,28 +6812,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>1.14</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0.0459</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>637200</v>
+        <v>905600</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.39</v>
+        <v>0.27</v>
       </c>
       <c r="H141" t="n">
-        <v>30.6</v>
+        <v>56.84</v>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.921</v>
+        <v>1.102</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.981</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6857,28 +6857,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>4.45</v>
+        <v>0.95</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0155</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>603400</v>
+        <v>888800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H142" t="n">
-        <v>36.57</v>
+        <v>51.21</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>4.549</v>
+        <v>0.93</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>4.642</v>
+        <v>1.009</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6902,39 +6902,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>1.79</v>
+        <v>0.64</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>602300</v>
+        <v>879400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H143" t="n">
-        <v>43.46</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.43</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>1.824</v>
+        <v>0.641</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>1.83</v>
+        <v>0.629</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6947,28 +6947,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.39</v>
+        <v>7.55</v>
       </c>
       <c r="E144" s="17" t="n">
-        <v>0.0127</v>
+        <v>0.0013</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>593000</v>
+        <v>877000</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="H144" t="n">
-        <v>60.2</v>
+        <v>48.65</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6976,10 +6976,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.294</v>
+        <v>7.555</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.214</v>
+        <v>7.694</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6992,28 +6992,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0.02</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>582500</v>
+        <v>871500</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H145" t="n">
-        <v>57.42</v>
+        <v>50.79</v>
       </c>
       <c r="I145" s="16" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.182</v>
+        <v>1.025</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.152</v>
+        <v>0.979</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7037,28 +7037,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>-0.0071</v>
+        <v>2.38</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>564300</v>
+        <v>858400</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H146" t="n">
-        <v>41.04</v>
+        <v>59.55</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.711</v>
+        <v>2.293</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.766</v>
+        <v>2.214</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7082,28 +7082,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>0</v>
+        <v>1.37</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>0.0379</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>558400</v>
+        <v>835000</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="H147" t="n">
-        <v>55.77</v>
+        <v>56.83</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>4.438</v>
+        <v>1.298</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>4.44</v>
+        <v>1.247</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7127,28 +7127,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GASMSIA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>5.45</v>
+        <v>4.58</v>
       </c>
       <c r="E148" s="17" t="n">
-        <v>0.0302</v>
+        <v>0.0022</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>556200</v>
+        <v>818900</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="H148" t="n">
-        <v>67.76000000000001</v>
+        <v>56.12</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>5.173</v>
+        <v>4.439</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>5.029</v>
+        <v>4.441</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7181,19 +7181,19 @@
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.625</v>
+        <v>0.635</v>
       </c>
       <c r="E149" s="17" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0242</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>548900</v>
+        <v>811400</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H149" t="n">
-        <v>47.6</v>
+        <v>51.45</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.633</v>
+        <v>0.634</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>0.623</v>
@@ -7217,28 +7217,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>-0.0417</v>
+        <v>0.55</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>548900</v>
+        <v>794300</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.74</v>
+        <v>0.53</v>
       </c>
       <c r="H150" t="n">
-        <v>34.59</v>
+        <v>40.89</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.711</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.766</v>
+        <v>0.575</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7262,39 +7262,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>0.0106</v>
+        <v>5.3</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>541800</v>
+        <v>789300</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H151" t="n">
-        <v>59.59</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.95</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>2.739</v>
+        <v>5.45</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>2.382</v>
+        <v>5.725</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7307,39 +7307,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.715</v>
+        <v>0.885</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>-0.0338</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>535100</v>
+        <v>773800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.91</v>
+        <v>0.48</v>
       </c>
       <c r="H152" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.6</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.651</v>
+        <v>0.921</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.617</v>
+        <v>0.981</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7352,39 +7352,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>4.23</v>
+        <v>1.59</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.0024</v>
+        <v>-0.0536</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>527500</v>
+        <v>763500</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.12</v>
+        <v>1.03</v>
       </c>
       <c r="H153" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.02</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>4.323</v>
+        <v>1.709</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>4.605</v>
+        <v>1.766</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7397,28 +7397,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E154" s="17" t="n">
-        <v>0.0089</v>
+        <v>1.07</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>515700</v>
+        <v>703300</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H154" t="n">
-        <v>31.07</v>
+        <v>40.39</v>
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.191</v>
+        <v>1.124</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.302</v>
+        <v>1.249</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7442,39 +7442,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E155" s="17" t="n">
-        <v>0.031</v>
+        <v>2.81</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>515500</v>
+        <v>698700</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="H155" t="n">
-        <v>53.68</v>
-      </c>
-      <c r="I155" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.71</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>1.298</v>
+        <v>2.735</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.305</v>
+        <v>2.381</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7487,28 +7487,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>0.0345</v>
+        <v>4.2</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>513700</v>
+        <v>685900</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1.63</v>
+        <v>0.16</v>
       </c>
       <c r="H156" t="n">
-        <v>59.21</v>
+        <v>36.6</v>
       </c>
       <c r="I156" s="16" t="inlineStr">
         <is>
@@ -7516,10 +7516,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.55</v>
+        <v>4.604</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7532,45 +7532,585 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>0.0221</v>
+        <v>0.64</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>513500</v>
+        <v>685000</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H157" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I157" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.471</v>
+        <v>0.634</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.597</v>
+        <v>0.633</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>675200</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H158" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>4.202</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>661500</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H159" t="n">
+        <v>52.67</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AXREIT</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>612100</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H160" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="I160" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>1.825</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>603200</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>0.0189</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>588900</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H162" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>584300</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H163" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>564200</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H164" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>549800</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H165" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>2.005</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5307</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AMEREIT</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>542600</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="H166" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>535600</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H167" t="n">
+        <v>41.21</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H168" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>518700</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H169" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M157"/>
+  <autoFilter ref="A1:M169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0708</v>
+        <v>0.0619</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4240800</v>
+        <v>4380300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.71</v>
+        <v>59.98</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.605高于50日均线0.529，RSI 60.71未超买，技术面信号可靠性较高。</t>
+          <t>SAR转多信号，现价0.60高于50日均线0.529，RSI 59.98处中性偏上区间，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0667</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4482300</v>
+        <v>4830100</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>59.01</v>
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.07629999999999999</v>
+        <v>0.0593</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3294900</v>
+        <v>3355800</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.88</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1.109</v>
+        <v>1.107</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.974</v>
@@ -704,54 +704,62 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 67.88接近超买区，现价高于50日均线约30%，信号可靠性中等。</t>
+          <t>SAR转多信号，现价1.25高于50日均线0.974约28%，RSI 66.74接近超买区，信号可靠性中等。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>54613500</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H5" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1092500</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="J5" s="3" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 55.48处中性区间，现价高于50日均线约8.3%，技术面信号可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -761,31 +769,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>30872000</v>
-      </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
+        <v>57215200</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.247</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
     </row>
@@ -797,28 +814,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0.1026</v>
+        <v>0.96</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0323</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>28185700</v>
+        <v>39324700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>5.5</v>
+        <v>0.53</v>
       </c>
       <c r="H7" t="n">
-        <v>89.11</v>
+        <v>69.28</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -826,10 +843,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.129</v>
+        <v>0.87</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.118</v>
+        <v>0.769</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -842,40 +859,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>0.0316</v>
+        <v>0.005</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>22201800</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>74.78</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.326</v>
-      </c>
+        <v>30872000</v>
+      </c>
+      <c r="G8" s="12" t="n"/>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -887,39 +895,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.495</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.0421</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>21499800</v>
+        <v>29878300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.25</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.45</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.319</v>
+        <v>0.427</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.269</v>
+        <v>0.326</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -932,28 +940,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.0161</v>
+        <v>0.215</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0.1026</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>19115300</v>
+        <v>29793800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.26</v>
+        <v>5.82</v>
       </c>
       <c r="H10" t="n">
-        <v>67.73</v>
+        <v>89.11</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -961,10 +969,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.868</v>
+        <v>0.129</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.769</v>
+        <v>0.118</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -977,39 +985,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.155</v>
+        <v>0.35</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>16369500</v>
+        <v>22514100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H11" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.2</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.156</v>
+        <v>0.319</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.156</v>
+        <v>0.269</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1022,28 +1030,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>0.0333</v>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14756200</v>
+        <v>17149500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H12" t="n">
-        <v>49.17</v>
+        <v>47.73</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1051,10 +1059,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.159</v>
+        <v>0.156</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.148</v>
+        <v>0.156</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1067,39 +1075,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.485</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14611300</v>
+        <v>15579400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>3.98</v>
+        <v>0.76</v>
       </c>
       <c r="H13" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+        <v>65.62</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.055</v>
+        <v>0.439</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.057</v>
+        <v>0.39</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1123,19 +1131,19 @@
       <c r="D14" s="9" t="n">
         <v>2.17</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="15" t="n">
         <v>0.0483</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13921200</v>
+        <v>15300300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>63.51</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1157,28 +1165,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.0068</v>
+        <v>0.155</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13619000</v>
+        <v>15024000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>81.18000000000001</v>
+        <v>49.17</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1186,10 +1194,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.667</v>
+        <v>0.159</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.569</v>
+        <v>0.148</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1202,39 +1210,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13179400</v>
+        <v>14627300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.67</v>
+        <v>3.99</v>
       </c>
       <c r="H16" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
+        <v>41.01</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.185</v>
+        <v>0.055</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.187</v>
+        <v>0.057</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1247,39 +1255,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0.0282</v>
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.1111</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12911100</v>
+        <v>14198800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.86</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
+        <v>37.48</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>5.369</v>
+        <v>0.06</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>5.515</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1292,39 +1300,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>12555700</v>
+        <v>13707000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.2</v>
+        <v>0.57</v>
       </c>
       <c r="H18" t="n">
-        <v>30.77</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.62</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.059</v>
+        <v>0.667</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1337,39 +1345,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.305</v>
+        <v>5.1</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0</v>
+        <v>0.0282</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10644300</v>
+        <v>13407100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="H19" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
+        <v>39.18</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.307</v>
+        <v>5.369</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.303</v>
+        <v>5.515</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1382,39 +1390,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0.0105</v>
+        <v>0.18</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9478900</v>
+        <v>13179400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="H20" t="n">
-        <v>64.70999999999999</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
+        <v>44.11</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.438</v>
+        <v>0.185</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.389</v>
+        <v>0.187</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1427,39 +1435,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E21" s="15" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E21" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9374000</v>
+        <v>12209300</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.41</v>
+        <v>0.63</v>
       </c>
       <c r="H21" t="n">
-        <v>72.56999999999999</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.079</v>
+        <v>0.307</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.076</v>
+        <v>0.303</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1472,39 +1480,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0.1</v>
+        <v>0.44</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8438900</v>
+        <v>10453500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.7</v>
+        <v>0.29</v>
       </c>
       <c r="H22" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
+        <v>44.39</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.454</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.637</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1517,28 +1525,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8175600</v>
+        <v>10082700</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="H23" t="n">
-        <v>50.65</v>
+        <v>54.27</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1546,10 +1554,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.776</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1562,39 +1570,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0.0238</v>
+        <v>1.2</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8079100</v>
+        <v>9999000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.23</v>
+        <v>1.08</v>
       </c>
       <c r="H24" t="n">
-        <v>41.09</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.18000000000001</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.453</v>
+        <v>1.103</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.473</v>
+        <v>1.06</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1607,28 +1615,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.82</v>
+        <v>0.775</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7909700</v>
+        <v>9740600</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="H25" t="n">
-        <v>54.27</v>
+        <v>50.65</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1636,10 +1644,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.776</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1652,39 +1660,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.08</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7683400</v>
+        <v>9394000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.38</v>
+        <v>2.41</v>
       </c>
       <c r="H26" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.22</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.571</v>
+        <v>0.078</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.548</v>
+        <v>0.076</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1697,36 +1705,40 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.22</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>-0.0222</v>
+        <v>-0.0053</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7551300</v>
+        <v>9169800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="H27" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
+        <v>40.81</v>
+      </c>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.985</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
     </row>
@@ -1738,39 +1750,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0</v>
+        <v>0.1071</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7547900</v>
+        <v>8522300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>38.22</v>
+        <v>1.72</v>
       </c>
       <c r="H28" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
+        <v>49.68</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.074</v>
+        <v>0.637</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1783,39 +1795,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.265</v>
+        <v>0.595</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>0</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7081100</v>
+        <v>8258700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="H29" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
+        <v>55.89</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.284</v>
+        <v>0.571</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.279</v>
+        <v>0.548</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1828,33 +1840,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0.0588</v>
+        <v>0.195</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6925100</v>
+        <v>8028800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+        <v>0.47</v>
+      </c>
+      <c r="H30" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.227</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1866,28 +1885,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HARNLEN</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E31" s="15" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E31" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6870100</v>
+        <v>7720700</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>77.09</v>
+        <v>0.37</v>
       </c>
       <c r="H31" t="n">
-        <v>52.02</v>
+        <v>46.13</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -1895,10 +1914,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.459</v>
+        <v>0.868</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.478</v>
+        <v>0.869</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1911,39 +1930,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6794300</v>
+        <v>7659900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.62</v>
+        <v>38.79</v>
       </c>
       <c r="H32" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
+        <v>44.67</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.985</v>
+        <v>0.074</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1956,40 +1975,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0.0388</v>
+        <v>0.22</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6482400</v>
+        <v>7568400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.74</v>
+        <v>0.38</v>
       </c>
       <c r="H33" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0.438</v>
-      </c>
+        <v>48.42</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -2001,39 +2016,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.295</v>
+        <v>0.545</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0</v>
+        <v>0.0583</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6232500</v>
+        <v>7260100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="H34" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.26000000000001</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.295</v>
+        <v>0.459</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.295</v>
+        <v>0.439</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2046,39 +2061,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.865</v>
+        <v>2.03</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0</v>
+        <v>0.0357</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6140700</v>
+        <v>7229300</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H35" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.61</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.868</v>
+        <v>2.096</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.869</v>
+        <v>2.227</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2091,39 +2106,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0.002</v>
+        <v>0.265</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6041800</v>
+        <v>7167800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.26</v>
+        <v>0.65</v>
       </c>
       <c r="H36" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
+        <v>41.24</v>
+      </c>
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>4.877</v>
+        <v>0.284</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>4.772</v>
+        <v>0.279</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2136,40 +2151,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.415</v>
+        <v>0.725</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5924200</v>
+        <v>7153900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>56.17</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0.384</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2181,28 +2189,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0.04</v>
+        <v>0.47</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5897500</v>
+        <v>6870100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.52</v>
+        <v>77.09</v>
       </c>
       <c r="H38" t="n">
-        <v>31.45</v>
+        <v>52.02</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2210,10 +2218,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.577</v>
+        <v>0.478</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2226,39 +2234,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0.027</v>
+        <v>2.57</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.0198</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5667700</v>
+        <v>6766300</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.85</v>
+        <v>0.39</v>
       </c>
       <c r="H39" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.62</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.373</v>
+        <v>2.593</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.37</v>
+        <v>2.563</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2271,39 +2279,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.025</v>
+        <v>4.89</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.002</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5591500</v>
+        <v>6463400</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H40" t="n">
-        <v>39.09</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
+        <v>52.01</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.208</v>
+        <v>4.877</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.227</v>
+        <v>4.772</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2316,39 +2324,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0.0255</v>
+        <v>0.415</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5587800</v>
+        <v>6448200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H41" t="n">
-        <v>38.18</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.17</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.094</v>
+        <v>0.403</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.227</v>
+        <v>0.384</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2361,39 +2369,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>FITTERS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0.0217</v>
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.2</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5366800</v>
+        <v>6378400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2.42</v>
+        <v>4.81</v>
       </c>
       <c r="H42" t="n">
-        <v>57.31</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.454</v>
+        <v>0.022</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.45</v>
+        <v>0.022</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2406,39 +2414,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0.0541</v>
+        <v>0.295</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5329800</v>
+        <v>6232500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.6</v>
+        <v>1.86</v>
       </c>
       <c r="H43" t="n">
-        <v>45.17</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
+        <v>49.06</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.606</v>
+        <v>0.295</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.617</v>
+        <v>0.295</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2451,39 +2459,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.15</v>
+        <v>0.39</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5115800</v>
+        <v>6216300</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="H44" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.45</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.199</v>
+        <v>0.461</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.284</v>
+        <v>0.577</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2507,14 +2515,14 @@
       <c r="D45" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="E45" s="17" t="n">
+      <c r="E45" s="15" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>5085600</v>
+        <v>6096200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="H45" t="n">
         <v>63.72</v>
@@ -2541,39 +2549,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.125</v>
+        <v>0.38</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.027</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5082500</v>
+        <v>5744700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.35</v>
+        <v>0.86</v>
       </c>
       <c r="H46" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.17</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.037</v>
+        <v>0.373</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.034</v>
+        <v>0.37</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2586,39 +2594,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0.0198</v>
+        <v>0.59</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>0.06309999999999999</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5059600</v>
+        <v>5731000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="H47" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
+        <v>46.06</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.593</v>
+        <v>0.607</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.563</v>
+        <v>0.617</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2631,39 +2639,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0.0174</v>
+        <v>1.15</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4869500</v>
+        <v>5437800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="H48" t="n">
-        <v>61.28</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.75</v>
+      </c>
+      <c r="I48" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.1</v>
+        <v>1.199</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.059</v>
+        <v>1.284</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2676,28 +2684,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0.1351</v>
+        <v>0.47</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4426700</v>
+        <v>5366800</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>14.44</v>
+        <v>2.42</v>
       </c>
       <c r="H49" t="n">
-        <v>74.02</v>
+        <v>57.31</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2705,10 +2713,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.185</v>
+        <v>0.454</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.192</v>
+        <v>0.45</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2721,39 +2729,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INNATURE</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.035</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.125</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4310600</v>
+        <v>5082500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>32.52</v>
+        <v>0.35</v>
       </c>
       <c r="H50" t="n">
-        <v>68.03</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.22</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.131</v>
+        <v>0.037</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.137</v>
+        <v>0.034</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2766,39 +2774,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4260600</v>
+        <v>4662200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="H51" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.3</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.28</v>
+        <v>2.104</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.282</v>
+        <v>2.111</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2811,28 +2819,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0.027</v>
+        <v>0.21</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.1351</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3989100</v>
+        <v>4465400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.71</v>
+        <v>14.56</v>
       </c>
       <c r="H52" t="n">
-        <v>63.49</v>
+        <v>74.02</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2840,9 +2848,11 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="K52" s="9" t="n"/>
+        <v>0.185</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.192</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
     </row>
@@ -2854,39 +2864,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0086</v>
+        <v>0.14</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3865300</v>
+        <v>4310600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.6</v>
+        <v>32.52</v>
       </c>
       <c r="H53" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.03</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.288</v>
+        <v>0.131</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1.49</v>
+        <v>0.137</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2899,39 +2909,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0048</v>
+        <v>0.26</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3810300</v>
+        <v>4304600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.36</v>
+        <v>0.63</v>
       </c>
       <c r="H54" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>2.104</v>
+        <v>0.28</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2.111</v>
+        <v>0.282</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2955,14 +2965,14 @@
       <c r="D55" s="9" t="n">
         <v>0.865</v>
       </c>
-      <c r="E55" s="17" t="n">
+      <c r="E55" s="15" t="n">
         <v>0.0117</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3809200</v>
+        <v>4061200</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H55" t="n">
         <v>47.14</v>
@@ -2989,39 +2999,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E56" s="15" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3798700</v>
+        <v>4027400</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H56" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
+        <v>44.57</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.401</v>
+        <v>6.339</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.367</v>
+        <v>6.626</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3034,40 +3044,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0.0417</v>
+        <v>0.38</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.027</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3509000</v>
+        <v>4017300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.91</v>
+        <v>0.71</v>
       </c>
       <c r="H57" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.49</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="K57" s="9" t="n">
-        <v>0.123</v>
-      </c>
+        <v>0.341</v>
+      </c>
+      <c r="K57" s="9" t="n"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
@@ -3079,39 +3087,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0.013</v>
+        <v>0.425</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3430800</v>
+        <v>3957200</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>0.63</v>
       </c>
       <c r="H58" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
+        <v>57.47</v>
+      </c>
+      <c r="I58" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.745</v>
+        <v>0.401</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.367</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3124,39 +3132,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0.0206</v>
+        <v>1.15</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3381300</v>
+        <v>3950100</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.98</v>
+        <v>0.61</v>
       </c>
       <c r="H59" t="n">
-        <v>56.72</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.33</v>
+      </c>
+      <c r="I59" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>3.827</v>
+        <v>1.288</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>3.755</v>
+        <v>1.49</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3169,39 +3177,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>6.3</v>
+        <v>3.96</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0</v>
+        <v>0.0206</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3140700</v>
+        <v>3756100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.43</v>
+        <v>1.09</v>
       </c>
       <c r="H60" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.72</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>6.339</v>
+        <v>3.827</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>6.626</v>
+        <v>3.755</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3214,39 +3222,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0.0805</v>
+        <v>0.775</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3087100</v>
+        <v>3749300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
+        <v>56.83</v>
+      </c>
+      <c r="I61" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.014</v>
+        <v>0.745</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.872</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3268,19 +3276,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>0.0303</v>
+        <v>0.165</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3087000</v>
+        <v>3587000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H62" t="n">
-        <v>42.77</v>
+        <v>34.48</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3304,39 +3312,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0.014</v>
+        <v>0.125</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3082900</v>
+        <v>3509000</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.22</v>
+        <v>0.91</v>
       </c>
       <c r="H63" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.74</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.566</v>
+        <v>0.122</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.852</v>
+        <v>0.123</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3349,28 +3357,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.435</v>
+        <v>1.46</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2908700</v>
+        <v>3445100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>52.42</v>
+        <v>33.62</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3378,10 +3386,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.43</v>
+        <v>1.567</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.417</v>
+        <v>1.852</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3394,39 +3402,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.865</v>
+        <v>1.26</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2877000</v>
+        <v>3239900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="H65" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.33</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.865</v>
+        <v>1.273</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.861</v>
+        <v>1.317</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3439,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.46</v>
+        <v>3.22</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0</v>
+        <v>0.0805</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2875700</v>
+        <v>3239900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.32</v>
+        <v>1.21</v>
       </c>
       <c r="H66" t="n">
-        <v>44.37</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
+        <v>60.33</v>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.49</v>
+        <v>3.014</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.47</v>
+        <v>2.872</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3484,39 +3492,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0.0061</v>
+        <v>0.75</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2817700</v>
+        <v>3101500</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.35</v>
+        <v>1.01</v>
       </c>
       <c r="H67" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.85</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.63</v>
+        <v>0.744</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.673</v>
+        <v>0.708</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3529,28 +3537,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2778700</v>
+        <v>3003100</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.57</v>
+        <v>0.74</v>
       </c>
       <c r="H68" t="n">
-        <v>48.68</v>
+        <v>39.36</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3558,10 +3566,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.904</v>
+        <v>0.951</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.895</v>
+        <v>1.03</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3574,28 +3582,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0.001</v>
+        <v>1.66</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2761700</v>
+        <v>2987100</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="H69" t="n">
-        <v>48.1</v>
+        <v>53.47</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3603,10 +3611,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>9.994</v>
+        <v>1.63</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>10.106</v>
+        <v>1.673</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3619,39 +3627,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0316</v>
+        <v>0.44</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2743400</v>
+        <v>2986900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="H70" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.494</v>
+        <v>0.43</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.514</v>
+        <v>0.417</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3664,39 +3672,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.0067</v>
+        <v>0.895</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2656000</v>
+        <v>2981200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.87</v>
+        <v>1.69</v>
       </c>
       <c r="H71" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.68</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.744</v>
+        <v>0.904</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.708</v>
+        <v>0.895</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3709,39 +3717,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0063</v>
+        <v>9.99</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2623800</v>
+        <v>2974000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>37.28</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.1</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.65</v>
+        <v>9.994</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.737</v>
+        <v>10.106</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3754,28 +3762,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0</v>
+        <v>4.11</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0284</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2596500</v>
+        <v>2948200</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H73" t="n">
-        <v>39.36</v>
+        <v>56.15</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3783,10 +3791,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.951</v>
+        <v>3.997</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.03</v>
+        <v>3.662</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3799,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.555</v>
+        <v>0.465</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2549400</v>
+        <v>2907500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.25</v>
+        <v>0.32</v>
       </c>
       <c r="H74" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
+        <v>45.37</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3844,39 +3852,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0236</v>
+        <v>0.865</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2410900</v>
+        <v>2877000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.44</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>3.999</v>
+        <v>0.865</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>3.663</v>
+        <v>0.861</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3889,39 +3897,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0.0233</v>
+        <v>6.78</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2358600</v>
+        <v>2867900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
+        <v>37.17</v>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>2.601</v>
+        <v>7.023</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2.603</v>
+        <v>7.47</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3934,39 +3942,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>0.008</v>
+        <v>0.49</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0316</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2341600</v>
+        <v>2847400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.66</v>
+        <v>0.38</v>
       </c>
       <c r="H77" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.06</v>
+      </c>
+      <c r="I77" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.621</v>
+        <v>0.494</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.611</v>
+        <v>0.514</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3979,39 +3987,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0.0391</v>
+        <v>0.555</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2308700</v>
+        <v>2778300</v>
       </c>
       <c r="G78" s="12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H78" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H78" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J78" s="9" t="n">
-        <v>5.531</v>
-      </c>
       <c r="K78" s="9" t="n">
-        <v>5.389</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4024,39 +4032,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>-0.0021</v>
+        <v>5.83</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.0374</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2299300</v>
+        <v>2716500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="H79" t="n">
-        <v>47.78</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.04</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>4.728</v>
+        <v>5.53</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>4.805</v>
+        <v>5.389</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4069,39 +4077,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0.0229</v>
+        <v>0.265</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2244300</v>
+        <v>2678000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.45</v>
+        <v>0.31</v>
       </c>
       <c r="H80" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.08</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.712</v>
+        <v>0.269</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.291</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4114,39 +4122,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>-0.0152</v>
+        <v>1.59</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2183800</v>
+        <v>2669600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="H81" t="n">
-        <v>45.66</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+        <v>39.61</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.337</v>
+        <v>1.652</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.337</v>
+        <v>1.737</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4159,39 +4167,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>0.0354</v>
+        <v>0.265</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2174800</v>
+        <v>2611100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.59</v>
+        <v>0.44</v>
       </c>
       <c r="H82" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.26</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>10.532</v>
+        <v>0.267</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>9.907999999999999</v>
+        <v>0.269</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4204,39 +4212,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.25</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2106900</v>
+        <v>2605900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>41.32</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
+        <v>60.99</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.427</v>
+        <v>1.184</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.417</v>
+        <v>1.153</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4249,39 +4257,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>0.0167</v>
+        <v>2.37</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2105900</v>
+        <v>2593900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.32</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.32</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.314</v>
+        <v>2.427</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.357</v>
+        <v>2.417</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4294,28 +4302,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>0.007800000000000001</v>
+        <v>11.08</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0336</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2033300</v>
+        <v>2558900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H85" t="n">
-        <v>61.31</v>
+        <v>62.55</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4323,10 +4331,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.236</v>
+        <v>10.53</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.209</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4339,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0.0117</v>
+        <v>2.64</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2029200</v>
+        <v>2509500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
       <c r="H86" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I86" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>3.085</v>
+        <v>2.601</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.611</v>
+        <v>2.603</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4384,28 +4392,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E87" s="15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E87" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2020900</v>
+        <v>2459900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H87" t="n">
-        <v>44.58</v>
+        <v>69.69</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4413,10 +4421,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.272</v>
+        <v>1.982</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.317</v>
+        <v>1.965</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4429,39 +4437,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.435</v>
+        <v>4.72</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>-0.0114</v>
+        <v>-0.0021</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2007400</v>
+        <v>2452900</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="H88" t="n">
-        <v>28.69</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.78</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.476</v>
+        <v>4.728</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.607</v>
+        <v>4.805</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4474,39 +4482,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>0.0345</v>
+        <v>2.02</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2004600</v>
+        <v>2374200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>3.62</v>
+        <v>0.57</v>
       </c>
       <c r="H89" t="n">
-        <v>54.53</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
+        <v>44.59</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.291</v>
+        <v>2.037</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.295</v>
+        <v>2.062</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4519,28 +4527,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0.0451</v>
+        <v>5.74</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1973200</v>
+        <v>2367500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="H90" t="n">
-        <v>61.74</v>
+        <v>41.04</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4548,10 +4556,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>6.372</v>
+        <v>5.816</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>6.027</v>
+        <v>6.07</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4564,39 +4572,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.63</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.008</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1942300</v>
+        <v>2341600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.66</v>
       </c>
       <c r="H91" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.48999999999999</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.347</v>
+        <v>0.621</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.33</v>
+        <v>0.611</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4609,38 +4617,40 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0.0217</v>
+        <v>0.67</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0229</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1937200</v>
+        <v>2318100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="H92" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
+        <v>44.16</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>0.712</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4652,39 +4662,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0.0044</v>
+        <v>0.325</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1914600</v>
+        <v>2236400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H93" t="n">
-        <v>37.17</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
+        <v>45.66</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>7.023</v>
+        <v>0.337</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>7.47</v>
+        <v>0.337</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4697,39 +4707,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.335</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1910700</v>
+        <v>2201200</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="H94" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
+        <v>45.4</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>2.037</v>
+        <v>0.347</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>2.062</v>
+        <v>0.33</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4742,28 +4752,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E95" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1880000</v>
+        <v>2139100</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H95" t="n">
-        <v>48.12</v>
+        <v>38.96</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -4771,10 +4781,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.898</v>
+        <v>0.313</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.956</v>
+        <v>0.357</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4787,39 +4797,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0.0034</v>
+        <v>1.14</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1836800</v>
+        <v>2137000</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.24</v>
+        <v>1.11</v>
       </c>
       <c r="H96" t="n">
-        <v>57.54</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.88</v>
+      </c>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.808</v>
+        <v>1.192</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.699</v>
+        <v>1.302</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4832,28 +4842,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0145</v>
+        <v>6.88</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.0346</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1817000</v>
+        <v>2130900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.96</v>
+        <v>0.36</v>
       </c>
       <c r="H97" t="n">
-        <v>46.29</v>
+        <v>60.86</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4861,10 +4871,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.365</v>
+        <v>6.366</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.435</v>
+        <v>6.025</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4877,39 +4887,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0.04</v>
+        <v>1.3</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1763900</v>
+        <v>2129000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H98" t="n">
-        <v>46.39</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.31</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.264</v>
+        <v>1.236</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.282</v>
+        <v>1.209</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4922,39 +4932,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0185</v>
+        <v>0.44</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1740600</v>
+        <v>2108300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="H99" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
+        <v>29.53</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.267</v>
+        <v>0.476</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.269</v>
+        <v>0.607</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4967,28 +4977,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0169</v>
+        <v>3.46</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1728500</v>
+        <v>2037200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.23</v>
+        <v>0.64</v>
       </c>
       <c r="H100" t="n">
-        <v>61.54</v>
+        <v>89.75</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4996,10 +5006,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>3.821</v>
+        <v>3.085</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>3.293</v>
+        <v>2.611</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5012,39 +5022,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0.031</v>
+        <v>2.9</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1703000</v>
+        <v>2019500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.65</v>
+        <v>0.26</v>
       </c>
       <c r="H101" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
+        <v>57.06</v>
+      </c>
+      <c r="I101" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.274</v>
+        <v>2.807</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.19</v>
+        <v>2.698</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5057,39 +5067,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0.0276</v>
+        <v>0.3</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1694600</v>
+        <v>2005900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.71</v>
+        <v>3.62</v>
       </c>
       <c r="H102" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.53</v>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.128</v>
+        <v>0.291</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.082</v>
+        <v>0.295</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5102,28 +5112,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.46</v>
+        <v>1.36</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0108</v>
+        <v>-0.0145</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1647800</v>
+        <v>1996600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.23</v>
+        <v>1.05</v>
       </c>
       <c r="H103" t="n">
-        <v>36.51</v>
+        <v>46.29</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5131,10 +5141,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.48</v>
+        <v>1.365</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.536</v>
+        <v>1.435</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5147,39 +5157,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0.0038</v>
+        <v>4.07</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1634600</v>
+        <v>1972400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H104" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.92</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2.726</v>
+        <v>3.822</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.747</v>
+        <v>3.293</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5192,40 +5202,38 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0.0167</v>
+        <v>0.235</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1627700</v>
+        <v>1937300</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.25</v>
+        <v>0.73</v>
       </c>
       <c r="H105" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
+        <v>18.87</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="K105" s="9" t="n">
-        <v>0.489</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5237,39 +5245,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0.0132</v>
+        <v>0.83</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1626800</v>
+        <v>1919200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
       <c r="H106" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.69</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.768</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.771</v>
+        <v>0.78</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5282,39 +5290,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>0.0115</v>
+        <v>0.905</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1623600</v>
+        <v>1880000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H107" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.835</v>
+        <v>0.898</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.802</v>
+        <v>0.956</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5327,39 +5335,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1608200</v>
+        <v>1878300</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H108" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.03</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.78</v>
+        <v>0.732</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5372,39 +5380,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0234</v>
+        <v>7.1</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1578900</v>
+        <v>1865200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.51</v>
+        <v>0.11</v>
       </c>
       <c r="H109" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
+        <v>31.47</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.677</v>
+        <v>7.335</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.732</v>
+        <v>7.611</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5417,39 +5425,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>0.0014</v>
+        <v>5.11</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0.002</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1553800</v>
+        <v>1850600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="H110" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.336</v>
+        <v>5.064</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.612</v>
+        <v>5.036</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5462,39 +5470,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1488800</v>
+        <v>1795600</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H111" t="n">
-        <v>28.01</v>
-      </c>
-      <c r="I111" s="16" t="inlineStr">
+        <v>57.1</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="K111" s="9" t="n">
         <v>1.19</v>
-      </c>
-      <c r="K111" s="9" t="n">
-        <v>1.302</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5507,39 +5515,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0.0147</v>
+        <v>0.61</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1468000</v>
+        <v>1783400</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>1.72</v>
+        <v>0.28</v>
       </c>
       <c r="H112" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
+        <v>57.18</v>
+      </c>
+      <c r="I112" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.331</v>
+        <v>0.58</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.317</v>
+        <v>0.489</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5552,39 +5560,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0.002</v>
+        <v>0.255</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1467900</v>
+        <v>1764800</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H113" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.93</v>
+      </c>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>5.064</v>
+        <v>0.264</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>5.036</v>
+        <v>0.282</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5597,28 +5605,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.465</v>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1406700</v>
+        <v>1750900</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H114" t="n">
-        <v>40.28</v>
+        <v>38.02</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5626,10 +5634,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>5.815</v>
+        <v>0.481</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>6.069</v>
+        <v>0.536</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5642,39 +5650,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0.0074</v>
+        <v>0.875</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1358600</v>
+        <v>1734400</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H115" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
+        <v>59.65</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.822</v>
+        <v>0.835</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.959</v>
+        <v>0.802</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5687,39 +5695,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0.0167</v>
+        <v>2.67</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1345300</v>
+        <v>1710200</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H116" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
+        <v>44.52</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.644</v>
+        <v>2.726</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.681</v>
+        <v>2.747</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5732,39 +5740,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.705</v>
+        <v>1.3</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>-0.0208</v>
+        <v>-0.0076</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1296200</v>
+        <v>1708400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="H117" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.52</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.732</v>
+        <v>1.255</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.724</v>
+        <v>1.123</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5777,39 +5785,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.505</v>
+        <v>2.24</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>0</v>
+        <v>0.0323</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1265700</v>
+        <v>1707800</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="H118" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.14</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.527</v>
+        <v>2.128</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>2.082</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5822,39 +5830,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1246400</v>
+        <v>1631700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>1.06</v>
+        <v>0.15</v>
       </c>
       <c r="H119" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
+        <v>45.61</v>
+      </c>
+      <c r="I119" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.211</v>
+        <v>0.732</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.207</v>
+        <v>0.724</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5867,39 +5875,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>0.0083</v>
+        <v>0.77</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1246300</v>
+        <v>1627400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="H120" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
+        <v>50.46</v>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.549</v>
+        <v>0.768</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.489</v>
+        <v>0.771</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5912,39 +5920,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0.0358</v>
+        <v>4.42</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1243900</v>
+        <v>1557500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="H121" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.42</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>7.31</v>
+        <v>4.546</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>6.968</v>
+        <v>4.641</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5957,39 +5965,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0.0185</v>
+        <v>0.21</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1184300</v>
+        <v>1528300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.18</v>
+        <v>1.3</v>
       </c>
       <c r="H122" t="n">
-        <v>38.81</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
+        <v>50.03</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.295</v>
+        <v>0.211</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.32</v>
+        <v>0.207</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6017,10 +6025,10 @@
         <v>-0.0014</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1181900</v>
+        <v>1527800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H123" t="n">
         <v>41.58</v>
@@ -6047,28 +6055,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.31</v>
+        <v>7.55</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1161100</v>
+        <v>1469700</v>
       </c>
       <c r="G124" s="12" t="n">
         <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>57.49</v>
+        <v>56.9</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6076,10 +6084,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.256</v>
+        <v>7.313</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.123</v>
+        <v>6.969</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6092,39 +6100,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0.006</v>
+        <v>0.345</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1151200</v>
+        <v>1468000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.19</v>
+        <v>1.72</v>
       </c>
       <c r="H125" t="n">
-        <v>61.41</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.54000000000001</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>13.109</v>
+        <v>0.331</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>13.298</v>
+        <v>0.317</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6137,39 +6145,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0.0121</v>
+        <v>0.21</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1099500</v>
+        <v>1445400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.39</v>
+        <v>0.82</v>
       </c>
       <c r="H126" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.86</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.865</v>
+        <v>0.176</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.927</v>
+        <v>0.164</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6182,39 +6190,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>0.0077</v>
+        <v>0.61</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0167</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1087300</v>
+        <v>1422300</v>
       </c>
       <c r="G127" s="12" t="n">
         <v>0.18</v>
       </c>
       <c r="H127" t="n">
-        <v>46.93</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.647</v>
+        <v>0.644</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.826</v>
+        <v>0.681</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6227,39 +6235,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.205</v>
+        <v>2.72</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0</v>
+        <v>0.0074</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1064100</v>
+        <v>1394100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H128" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.02</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.175</v>
+        <v>2.822</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.164</v>
+        <v>2.959</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6272,39 +6280,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>-0.0073</v>
+        <v>2.61</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1046300</v>
+        <v>1361100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.4</v>
+        <v>0.23</v>
       </c>
       <c r="H129" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.655</v>
+        <v>2.646</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.583</v>
+        <v>2.825</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6317,39 +6325,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0.0556</v>
+        <v>4.6</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1040800</v>
+        <v>1360600</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="H130" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.8</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.272</v>
+        <v>4.441</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.259</v>
+        <v>4.441</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6362,39 +6370,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0</v>
+        <v>6.76</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1030000</v>
+        <v>1342800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="H131" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
+        <v>47.95</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.323</v>
+        <v>6.802</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.332</v>
+        <v>6.82</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6407,39 +6415,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0.505</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1025300</v>
+        <v>1317100</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="H132" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
+        <v>29.83</v>
+      </c>
+      <c r="I132" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>6.802</v>
+        <v>0.527</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>6.82</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6452,28 +6460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0.07190000000000001</v>
+        <v>13.36</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0.006</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1024300</v>
+        <v>1309800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>1.38</v>
+        <v>0.21</v>
       </c>
       <c r="H133" t="n">
-        <v>52.69</v>
+        <v>61.41</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6481,10 +6489,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.598</v>
+        <v>13.109</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.649</v>
+        <v>13.298</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6497,39 +6505,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>GASMSIA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0.0167</v>
+        <v>5.45</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0302</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1013000</v>
+        <v>1293700</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.26</v>
+        <v>1.43</v>
       </c>
       <c r="H134" t="n">
-        <v>63.93</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>2.846</v>
+        <v>5.173</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>2.378</v>
+        <v>5.029</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6542,39 +6550,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>0.009399999999999999</v>
+        <v>3.03</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.01</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>981300</v>
+        <v>1278500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H135" t="n">
-        <v>71.13</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.27</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.984</v>
+        <v>2.844</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.965</v>
+        <v>2.378</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6587,39 +6595,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GASMSIA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E136" s="17" t="n">
-        <v>0.0302</v>
+        <v>0.61</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>950500</v>
+        <v>1259600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1.05</v>
+        <v>0.26</v>
       </c>
       <c r="H136" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.48999999999999</v>
+      </c>
+      <c r="I136" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>5.173</v>
+        <v>0.549</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>5.029</v>
+        <v>0.489</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6632,39 +6640,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0.835</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>944300</v>
+        <v>1245500</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="H137" t="n">
-        <v>36.57</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>4.549</v>
+        <v>0.865</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>4.642</v>
+        <v>0.927</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6677,39 +6685,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.0103</v>
+        <v>1.13</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.0367</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>923800</v>
+        <v>1239300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.22</v>
+        <v>0.36</v>
       </c>
       <c r="H138" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.96</v>
+      </c>
+      <c r="I138" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.945</v>
+        <v>1.101</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.895</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6722,39 +6730,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.28</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>918300</v>
+        <v>1197300</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H139" t="n">
-        <v>58.68</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
+        <v>41.19</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.183</v>
+        <v>0.295</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.152</v>
+        <v>0.32</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6767,39 +6775,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>AMEREIT</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0.0806</v>
+        <v>1.6</v>
+      </c>
+      <c r="E140" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>913600</v>
+        <v>1152200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>1.24</v>
+        <v>13.57</v>
       </c>
       <c r="H140" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.9</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>2.564</v>
+        <v>1.56</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>2.523</v>
+        <v>1.543</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6812,39 +6820,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>0.0459</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>905600</v>
+        <v>1089200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="H141" t="n">
-        <v>56.84</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
+        <v>60.26</v>
+      </c>
+      <c r="I141" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.102</v>
+        <v>0.655</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6857,39 +6865,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>-0.0155</v>
+        <v>5.3</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>888800</v>
+        <v>1076700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.77</v>
+        <v>0.41</v>
       </c>
       <c r="H142" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.95</v>
+      </c>
+      <c r="I142" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>0.93</v>
+        <v>5.45</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.009</v>
+        <v>5.725</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6902,39 +6910,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E143" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.32</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>879400</v>
+        <v>1050000</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.43</v>
+        <v>0.71</v>
       </c>
       <c r="H143" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.79</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.641</v>
+        <v>0.323</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.629</v>
+        <v>0.332</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6947,28 +6955,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>0.0013</v>
+        <v>1.64</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>0.07190000000000001</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>877000</v>
+        <v>1046100</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.31</v>
+        <v>1.41</v>
       </c>
       <c r="H144" t="n">
-        <v>48.65</v>
+        <v>52.69</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6976,10 +6984,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>7.555</v>
+        <v>1.598</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>7.694</v>
+        <v>1.649</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6992,39 +7000,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0.02</v>
+        <v>7.53</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>871500</v>
+        <v>1045900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="H145" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.6</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.025</v>
+        <v>7.553</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.979</v>
+        <v>7.693</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7037,39 +7045,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.285</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0556</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>858400</v>
+        <v>1040900</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="H146" t="n">
-        <v>59.55</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>2.293</v>
+        <v>0.272</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>2.214</v>
+        <v>0.259</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7082,28 +7090,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E147" s="17" t="n">
-        <v>0.0379</v>
+        <v>2.66</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0.0726</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>835000</v>
+        <v>981500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.28</v>
+        <v>1.34</v>
       </c>
       <c r="H147" t="n">
-        <v>56.83</v>
+        <v>56.76</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7111,10 +7119,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>1.298</v>
+        <v>2.562</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>1.247</v>
+        <v>2.522</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7127,28 +7135,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>0.0022</v>
+        <v>0.95</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>818900</v>
+        <v>959900</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.16</v>
+        <v>0.83</v>
       </c>
       <c r="H148" t="n">
-        <v>56.12</v>
+        <v>51.21</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7156,10 +7164,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>4.439</v>
+        <v>0.93</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>4.441</v>
+        <v>1.009</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7172,39 +7180,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>0.0242</v>
+        <v>0.955</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>811400</v>
+        <v>958000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H149" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I149" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.51</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.634</v>
+        <v>0.944</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.623</v>
+        <v>0.895</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7217,39 +7225,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>0.55</v>
+        <v>1.02</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>794300</v>
+        <v>953700</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="H150" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.79</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>1.025</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.575</v>
+        <v>0.979</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7262,39 +7270,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>0</v>
+        <v>1.61</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>789300</v>
+        <v>909100</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.3</v>
+        <v>1.22</v>
       </c>
       <c r="H151" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.59</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>5.45</v>
+        <v>1.711</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>5.725</v>
+        <v>1.766</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7307,39 +7315,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>2.38</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>773800</v>
+        <v>888200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
       <c r="H152" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.55</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.921</v>
+        <v>2.293</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.981</v>
+        <v>2.214</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7352,28 +7360,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.0536</v>
+        <v>-0.0098</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>763500</v>
+        <v>887700</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="H153" t="n">
-        <v>33.02</v>
+        <v>51.74</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7381,10 +7389,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.709</v>
+        <v>1.011</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.766</v>
+        <v>0.99</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7397,39 +7405,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E154" s="15" t="n">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>703300</v>
+        <v>884800</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H154" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.43</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.124</v>
+        <v>0.641</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.249</v>
+        <v>0.629</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7442,39 +7450,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.0035</v>
+        <v>4.25</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>698700</v>
+        <v>884000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H155" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I155" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.735</v>
+        <v>4.324</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.381</v>
+        <v>4.605</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7487,39 +7495,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E156" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.91</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>685900</v>
+        <v>869300</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.16</v>
+        <v>0.52</v>
       </c>
       <c r="H156" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="I156" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>4.32</v>
+        <v>0.893</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>4.604</v>
+        <v>0.903</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7532,28 +7540,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E157" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E157" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>685000</v>
+        <v>818800</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.66</v>
+        <v>0.54</v>
       </c>
       <c r="H157" t="n">
-        <v>63.09</v>
+        <v>40.89</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7561,10 +7569,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.634</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.633</v>
+        <v>0.575</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7577,39 +7585,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>0.0048</v>
+        <v>2.14</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>675200</v>
+        <v>813200</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H158" t="n">
-        <v>46.64</v>
-      </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.37</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>4.202</v>
+        <v>2.084</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>4.284</v>
+        <v>2.004</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7622,39 +7630,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>0.0233</v>
+        <v>0.635</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>661500</v>
+        <v>811400</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H159" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="I159" s="16" t="inlineStr">
+        <v>51.45</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.297</v>
+        <v>0.634</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.305</v>
+        <v>0.623</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7667,39 +7675,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E160" s="15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E160" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>612100</v>
+        <v>800800</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.75</v>
+        <v>0.49</v>
       </c>
       <c r="H160" t="n">
-        <v>45.01</v>
-      </c>
-      <c r="I160" s="16" t="inlineStr">
+        <v>31.78</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>1.825</v>
+        <v>0.922</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>1.83</v>
+        <v>0.981</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7712,28 +7720,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>-0.0071</v>
+        <v>2.83</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>603200</v>
+        <v>762300</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="H161" t="n">
-        <v>41.04</v>
+        <v>58.75</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7741,10 +7749,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.711</v>
+        <v>2.737</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.766</v>
+        <v>2.382</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7757,39 +7765,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E162" s="17" t="n">
-        <v>0.0189</v>
+        <v>1.07</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>588900</v>
+        <v>758100</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="H162" t="n">
-        <v>58.81</v>
-      </c>
-      <c r="I162" s="16" t="inlineStr">
+        <v>40.39</v>
+      </c>
+      <c r="I162" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.659</v>
+        <v>1.124</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.5</v>
+        <v>1.249</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7802,39 +7810,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>0.005600000000000001</v>
+        <v>4.14</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>584300</v>
+        <v>737800</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="H163" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.21</v>
+      </c>
+      <c r="I163" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.801</v>
+        <v>4.201</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.914</v>
+        <v>4.284</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7847,39 +7855,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>-0.0338</v>
+        <v>8.51</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>564200</v>
+        <v>697100</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.96</v>
+        <v>0.29</v>
       </c>
       <c r="H164" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.33</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>0.651</v>
+        <v>8.552</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>0.617</v>
+        <v>8.664</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7892,39 +7900,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>0.004699999999999999</v>
+        <v>1.32</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>549800</v>
+        <v>690600</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H165" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.67</v>
+      </c>
+      <c r="I165" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>2.085</v>
+        <v>1.297</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>2.005</v>
+        <v>1.305</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7937,39 +7945,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AMEREIT</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E166" s="15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E166" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>542600</v>
+        <v>685000</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>6.39</v>
+        <v>0.66</v>
       </c>
       <c r="H166" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.09</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.56</v>
+        <v>0.634</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.543</v>
+        <v>0.633</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7982,39 +7990,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E167" s="15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E167" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>535600</v>
+        <v>678100</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.23</v>
+        <v>1.13</v>
       </c>
       <c r="H167" t="n">
-        <v>41.21</v>
-      </c>
-      <c r="I167" s="16" t="inlineStr">
+        <v>41.31</v>
+      </c>
+      <c r="I167" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.753</v>
+        <v>1.181</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.767</v>
+        <v>1.203</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8027,39 +8035,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E168" s="17" t="n">
-        <v>0.0147</v>
+        <v>1.61</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>528500</v>
+        <v>677400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H168" t="n">
-        <v>34.54</v>
-      </c>
-      <c r="I168" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.47</v>
+        <v>1.641</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.597</v>
+        <v>1.711</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8072,45 +8080,765 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E169" s="17" t="n">
-        <v>0.0345</v>
+        <v>2.48</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>518700</v>
+        <v>665200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>1.64</v>
+        <v>0.25</v>
       </c>
       <c r="H169" t="n">
-        <v>59.21</v>
-      </c>
-      <c r="I169" s="16" t="inlineStr">
+        <v>41.47</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.521</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.55</v>
+        <v>2.638</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>0.0151</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>643200</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H170" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AXREIT</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>641200</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H171" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="I171" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>1.824</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>611400</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H172" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="I172" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>611400</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H173" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>1.914</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>609700</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H174" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>608600</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H175" t="n">
+        <v>38.55</v>
+      </c>
+      <c r="I175" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>607300</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>596400</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H177" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>3.543</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>3.577</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>-0.0338</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>564200</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H178" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>6033</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>PETGAS</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>554100</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H179" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="I179" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>17.283</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>17.329</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>534900</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H180" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="I180" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.122</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>528500</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H181" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>518700</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H182" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>515300</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H183" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>2.228</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>514300</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H184" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="I184" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E185" s="15" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>502600</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H185" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>1.683</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M169"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
+++ b/docs/downloads/2026-10-27/bursa-report-2026-10-27.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-27" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-27'!$A$1:$M$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.605</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0619</v>
+        <v>0.0708</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4380300</v>
+        <v>4496700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>59.98</v>
+        <v>60.71</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.60高于50日均线0.529，RSI 59.98处中性偏上区间，未超买，信号技术面较可靠。</t>
+          <t>SAR转多信号，RSI 60.71未超买，现价高于50日均线约14%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.64</v>
+        <v>0.635</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0667</v>
+        <v>0.0583</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4830100</v>
+        <v>4861100</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1.23</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.01</v>
+        <v>58.24</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 59.01未超买，现价高于50日均线约9.4%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，现价0.635高于50日均线0.585，RSI 58.24处中性偏上，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>0.0593</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>3355800</v>
+        <v>3528500</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>66.73999999999999</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价1.25高于50日均线0.974约28%，RSI 66.74接近超买区，信号可靠性中等。</t>
+          <t>SAR转多信号，RSI 66.74接近超买区，现价高于50日均线约28%，信号可靠性中等。</t>
         </is>
       </c>
     </row>
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0227</v>
+        <v>0.0303</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1092500</v>
+        <v>1238100</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>55.48</v>
+        <v>56.17</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.296</v>
+        <v>1.297</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.247</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 55.48处中性区间，现价高于50日均线约8.3%，技术面信号可靠性尚可。</t>
+          <t>现价1.36高于50日均线1.247，SAR转多信号获均线支撑；RSI 56.17处中性区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
         <v>-0.0667</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>57215200</v>
+        <v>59608000</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>0.16</v>
@@ -823,19 +823,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.96</v>
+        <v>0.965</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.03759999999999999</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>39324700</v>
+        <v>42310600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.53</v>
+        <v>0.57</v>
       </c>
       <c r="H7" t="n">
-        <v>69.28</v>
+        <v>69.77</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -859,31 +859,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0597</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>30872000</v>
-      </c>
-      <c r="G8" s="12" t="n"/>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+        <v>35934200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H8" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.269</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
     </row>
@@ -895,28 +904,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.495</v>
+        <v>0.215</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.0421</v>
+        <v>0.1026</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>29878300</v>
+        <v>31938500</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>6.23</v>
       </c>
       <c r="H9" t="n">
-        <v>75.45</v>
+        <v>89.11</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -924,10 +933,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.427</v>
+        <v>0.129</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.326</v>
+        <v>0.118</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -940,28 +949,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.215</v>
+        <v>0.495</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.1026</v>
+        <v>0.0421</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>29793800</v>
+        <v>31890300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>5.82</v>
+        <v>0.86</v>
       </c>
       <c r="H10" t="n">
-        <v>89.11</v>
+        <v>75.45</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -969,10 +978,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.129</v>
+        <v>0.427</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.118</v>
+        <v>0.326</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -985,40 +994,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.005</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>22514100</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H11" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>0.269</v>
-      </c>
+        <v>30872000</v>
+      </c>
+      <c r="G11" s="12" t="n"/>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
     </row>
@@ -1041,14 +1041,14 @@
       <c r="D12" s="9" t="n">
         <v>0.155</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17149500</v>
+        <v>20189500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="H12" t="n">
         <v>47.73</v>
@@ -1075,39 +1075,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.485</v>
+        <v>2.17</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.0483</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>15579400</v>
+        <v>17542200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="H13" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
+        <v>63.51</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.439</v>
+        <v>1.991</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.39</v>
+        <v>1.808</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1120,39 +1120,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2.17</v>
+        <v>0.485</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.0483</v>
+        <v>0.0211</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>15300300</v>
+        <v>17078800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H14" t="n">
-        <v>63.51</v>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
+        <v>65.62</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1.991</v>
+        <v>0.439</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.808</v>
+        <v>0.39</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         <v>0.0333</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>15024000</v>
+        <v>15711400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
         <v>49.17</v>
@@ -1210,39 +1210,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.045</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>14627300</v>
+        <v>15698800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3.99</v>
+        <v>1.49</v>
       </c>
       <c r="H16" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
+        <v>30.77</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.055</v>
+        <v>0.059</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1255,39 +1255,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.1111</v>
+        <v>0.305</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>14198800</v>
+        <v>15109400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.35</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="n">
-        <v>37.48</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
+        <v>47.42</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.06</v>
+        <v>0.307</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.303</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1300,39 +1300,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0135</v>
+        <v>5.11</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0302</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>13707000</v>
+        <v>14848200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.57</v>
+        <v>0.99</v>
       </c>
       <c r="H18" t="n">
-        <v>78.62</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.59</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.667</v>
+        <v>5.37</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>5.515</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1345,39 +1345,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.0282</v>
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>-0.09089999999999999</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>13407100</v>
+        <v>14628700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.89</v>
+        <v>3.99</v>
       </c>
       <c r="H19" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
+        <v>41.01</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>5.369</v>
+        <v>0.055</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>5.515</v>
+        <v>0.057</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1390,39 +1390,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>0.735</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>13179400</v>
+        <v>14180800</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.18000000000001</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.185</v>
+        <v>0.667</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.187</v>
+        <v>0.569</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1435,39 +1435,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>12209300</v>
+        <v>13184400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
+        <v>48.98</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.307</v>
+        <v>0.185</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.303</v>
+        <v>0.187</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1495,15 +1495,15 @@
         <v>0.0476</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10453500</v>
+        <v>13040700</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H22" t="n">
         <v>44.39</v>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1525,28 +1525,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.0522</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10082700</v>
+        <v>11453500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.63</v>
+        <v>1.24</v>
       </c>
       <c r="H23" t="n">
-        <v>54.27</v>
+        <v>65.05</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.8179999999999999</v>
+        <v>1.104</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1570,28 +1570,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.2</v>
+        <v>0.775</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.0435</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>9999000</v>
+        <v>10993200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1.08</v>
+        <v>0.71</v>
       </c>
       <c r="H24" t="n">
-        <v>64.18000000000001</v>
+        <v>50.65</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.103</v>
+        <v>0.774</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.06</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9740600</v>
+        <v>10403200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="H25" t="n">
-        <v>50.65</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.81</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.774</v>
+        <v>0.999</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.776</v>
+        <v>0.985</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1660,28 +1660,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0588</v>
+        <v>0.82</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9394000</v>
+        <v>10107800</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2.41</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
-        <v>56.22</v>
+        <v>54.27</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.078</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.076</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1705,39 +1705,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.825</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.1786</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9169800</v>
+        <v>10021700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.84</v>
+        <v>2.02</v>
       </c>
       <c r="H27" t="n">
-        <v>40.81</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
+        <v>52.6</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.999</v>
+        <v>0.821</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.985</v>
+        <v>0.638</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1750,39 +1750,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.1071</v>
+        <v>0.08</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8522300</v>
+        <v>9616000</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="H28" t="n">
-        <v>49.68</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.22</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.637</v>
+        <v>0.076</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1795,39 +1795,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8258700</v>
+        <v>9372300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="H29" t="n">
-        <v>55.89</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.571</v>
+        <v>0.868</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.548</v>
+        <v>0.869</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1855,15 +1855,15 @@
         <v>-0.025</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>8028800</v>
+        <v>8703000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="H30" t="n">
         <v>39.09</v>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1885,39 +1885,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.04389999999999999</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7720700</v>
+        <v>8557200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H31" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.89</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.868</v>
+        <v>0.571</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.869</v>
+        <v>0.548</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1930,39 +1930,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0189</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MATANG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7659900</v>
+        <v>8307600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>38.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>44.67</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
+        <v>41.75</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.07199999999999999</v>
+        <v>2.097</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.074</v>
+        <v>2.227</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1975,36 +1975,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.545</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0583</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7568400</v>
+        <v>8105300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.38</v>
+        <v>2.17</v>
       </c>
       <c r="H33" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+        <v>84.26000000000001</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.439</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -2016,39 +2020,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.545</v>
+        <v>2.58</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0583</v>
+        <v>0.0238</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>7260100</v>
+        <v>7715400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.95</v>
+        <v>0.44</v>
       </c>
       <c r="H34" t="n">
-        <v>84.26000000000001</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.25</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.459</v>
+        <v>2.594</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.439</v>
+        <v>2.563</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2061,39 +2065,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0189</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MATANG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7229300</v>
+        <v>7659900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.6</v>
+        <v>38.79</v>
       </c>
       <c r="H35" t="n">
-        <v>40.61</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
+        <v>44.67</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.096</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.227</v>
+        <v>0.074</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2106,40 +2110,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0</v>
+        <v>0.73</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0735</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>7167800</v>
+        <v>7634900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H36" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I36" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0.279</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2151,27 +2148,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.22</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7153900</v>
+        <v>7624400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
+        <v>0.38</v>
+      </c>
+      <c r="H37" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2189,28 +2189,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HARNLEN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E38" s="16" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E38" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>6870100</v>
+        <v>7388000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>77.09</v>
+        <v>0.62</v>
       </c>
       <c r="H38" t="n">
-        <v>52.02</v>
+        <v>56.17</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.459</v>
+        <v>0.403</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.478</v>
+        <v>0.384</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2234,39 +2234,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.0198</v>
+        <v>0.265</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>6766300</v>
+        <v>7265800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.39</v>
+        <v>0.66</v>
       </c>
       <c r="H39" t="n">
-        <v>48.62</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
+        <v>41.24</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.593</v>
+        <v>0.284</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.563</v>
+        <v>0.279</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2279,39 +2279,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>4.89</v>
+        <v>0.64</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.002</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>6463400</v>
+        <v>7181600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.27</v>
+        <v>0.7</v>
       </c>
       <c r="H40" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.72</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>4.877</v>
+        <v>0.626</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>4.772</v>
+        <v>0.619</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2324,28 +2324,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0667</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>6448200</v>
+        <v>7041800</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="H41" t="n">
-        <v>56.17</v>
+        <v>33.79</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.403</v>
+        <v>0.462</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.384</v>
+        <v>0.577</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2384,15 +2384,15 @@
         <v>-0.2</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>6378400</v>
+        <v>6991400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>4.81</v>
+        <v>5.27</v>
       </c>
       <c r="H42" t="n">
         <v>47.87</v>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2414,39 +2414,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0</v>
+        <v>4.9</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>6232500</v>
+        <v>6872100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.86</v>
+        <v>0.29</v>
       </c>
       <c r="H43" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
+        <v>52.61</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.295</v>
+        <v>4.878</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.295</v>
+        <v>4.772</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HARNLEN</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.04</v>
+        <v>0.47</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>6216300</v>
+        <v>6870100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.54</v>
+        <v>77.09</v>
       </c>
       <c r="H44" t="n">
-        <v>31.45</v>
+        <v>52.02</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.577</v>
+        <v>0.478</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2504,39 +2504,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.15</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>6096200</v>
+        <v>6384400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="H45" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.75</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.626</v>
+        <v>1.199</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.619</v>
+        <v>1.284</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2549,39 +2549,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.027</v>
+        <v>0.295</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>5744700</v>
+        <v>6232500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.86</v>
+        <v>1.86</v>
       </c>
       <c r="H46" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.06</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.373</v>
+        <v>0.295</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.37</v>
+        <v>0.295</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2603,27 +2603,27 @@
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.59</v>
+        <v>0.585</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>5731000</v>
+        <v>5973500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="H47" t="n">
-        <v>46.06</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
+        <v>45.17</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.607</v>
+        <v>0.606</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0.617</v>
@@ -2639,39 +2639,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E48" s="16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E48" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>5437800</v>
+        <v>5915900</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H48" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
+        <v>63.07</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.199</v>
+        <v>0.051</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.284</v>
+        <v>0.047</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2684,28 +2684,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.0217</v>
+        <v>0.027</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>5366800</v>
+        <v>5799700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>2.42</v>
+        <v>0.87</v>
       </c>
       <c r="H49" t="n">
-        <v>57.31</v>
+        <v>58.17</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.454</v>
+        <v>0.373</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2729,39 +2729,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.125</v>
+        <v>0.47</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>5082500</v>
+        <v>5475700</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.35</v>
+        <v>2.47</v>
       </c>
       <c r="H50" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.31</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.037</v>
+        <v>0.454</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.034</v>
+        <v>0.45</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2774,39 +2774,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.09</v>
+        <v>1.15</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>-0.0048</v>
+        <v>-0.0086</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4662200</v>
+        <v>5202500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="H51" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.33</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.104</v>
+        <v>1.288</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.111</v>
+        <v>1.49</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2819,39 +2819,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.1351</v>
+        <v>0.035</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.125</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4465400</v>
+        <v>5197500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>14.56</v>
+        <v>0.36</v>
       </c>
       <c r="H52" t="n">
-        <v>74.02</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.22</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.185</v>
+        <v>0.037</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.192</v>
+        <v>0.034</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2864,28 +2864,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INNATURE</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.14</v>
+        <v>1.66</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4310600</v>
+        <v>4936400</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>32.52</v>
+        <v>0.61</v>
       </c>
       <c r="H53" t="n">
-        <v>68.03</v>
+        <v>53.47</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.131</v>
+        <v>1.63</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.137</v>
+        <v>1.673</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2909,39 +2909,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E54" s="16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E54" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4304600</v>
+        <v>4902000</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H54" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
+        <v>44.57</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.28</v>
+        <v>6.339</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.282</v>
+        <v>6.626</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2954,28 +2954,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0117</v>
+        <v>2.09</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4061200</v>
+        <v>4698600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="H55" t="n">
-        <v>47.14</v>
+        <v>47.3</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.885</v>
+        <v>2.104</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.862</v>
+        <v>2.111</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2999,39 +2999,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E56" s="16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E56" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4027400</v>
+        <v>4533800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H56" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
+        <v>39.48</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>6.339</v>
+        <v>0.28</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>6.626</v>
+        <v>0.282</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3044,28 +3044,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0010</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>0.027</v>
+        <v>0.1351</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>4017300</v>
+        <v>4501400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.71</v>
+        <v>14.68</v>
       </c>
       <c r="H57" t="n">
-        <v>63.49</v>
+        <v>74.02</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3073,9 +3073,11 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="K57" s="9" t="n"/>
+        <v>0.185</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.192</v>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
@@ -3087,39 +3089,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.021</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3957200</v>
+        <v>4417400</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.63</v>
+        <v>0.32</v>
       </c>
       <c r="H58" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I58" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.62</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.401</v>
+        <v>1.567</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.367</v>
+        <v>1.852</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3132,39 +3134,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>INNATURE</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0086</v>
+        <v>0.14</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3950100</v>
+        <v>4331900</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.61</v>
+        <v>32.68</v>
       </c>
       <c r="H59" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="I59" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.03</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.288</v>
+        <v>0.131</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.49</v>
+        <v>0.137</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3177,28 +3179,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>3.96</v>
+        <v>0.385</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.0206</v>
+        <v>0.0405</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3756100</v>
+        <v>4278200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.09</v>
+        <v>0.76</v>
       </c>
       <c r="H60" t="n">
-        <v>56.72</v>
+        <v>64.52</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3206,11 +3208,9 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>3.827</v>
-      </c>
-      <c r="K60" s="9" t="n">
-        <v>3.755</v>
-      </c>
+        <v>0.342</v>
+      </c>
+      <c r="K60" s="9" t="n"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
     </row>
@@ -3222,39 +3222,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.775</v>
+        <v>0.87</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0175</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3749300</v>
+        <v>4125900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="H61" t="n">
-        <v>56.83</v>
-      </c>
-      <c r="I61" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.8</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.745</v>
+        <v>0.886</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3267,39 +3267,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3587000</v>
+        <v>4107500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H62" t="n">
-        <v>34.48</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.25</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.172</v>
+        <v>0.401</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.19</v>
+        <v>0.367</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3312,39 +3312,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ECONBHD</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.125</v>
+        <v>0.135</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.08</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3509000</v>
+        <v>4072800</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.91</v>
+        <v>0.38</v>
       </c>
       <c r="H63" t="n">
-        <v>54.74</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
+        <v>58.33</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.122</v>
+        <v>0.126</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.123</v>
+        <v>0.106</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3357,28 +3357,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>1.46</v>
+        <v>9.99</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>0.021</v>
+        <v>0.001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3445100</v>
+        <v>3983400</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>33.62</v>
+        <v>48.1</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1.567</v>
+        <v>9.994</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1.852</v>
+        <v>10.106</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3402,28 +3402,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.26</v>
+        <v>3.95</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>0.008</v>
+        <v>0.018</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3239900</v>
+        <v>3968100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.44</v>
+        <v>1.15</v>
       </c>
       <c r="H65" t="n">
-        <v>46.33</v>
+        <v>56.36</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.273</v>
+        <v>3.826</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.317</v>
+        <v>3.755</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3447,39 +3447,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>0.0805</v>
+        <v>0.77</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3239900</v>
+        <v>3948000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.21</v>
+        <v>0.73</v>
       </c>
       <c r="H66" t="n">
-        <v>60.33</v>
-      </c>
-      <c r="I66" s="17" t="inlineStr">
+        <v>56.13</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>3.014</v>
+        <v>0.744</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.872</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3492,39 +3492,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0</v>
+        <v>4.16</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3101500</v>
+        <v>3944600</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.01</v>
+        <v>0.42</v>
       </c>
       <c r="H67" t="n">
-        <v>52.85</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.12</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.744</v>
+        <v>4.002</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.708</v>
+        <v>3.663</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3537,28 +3537,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3003100</v>
+        <v>3589800</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H68" t="n">
-        <v>39.36</v>
+        <v>42.77</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.951</v>
+        <v>0.172</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.03</v>
+        <v>0.19</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3582,39 +3582,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>ECONBHD</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.66</v>
+        <v>0.125</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>0.0061</v>
+        <v>0.0417</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2987100</v>
+        <v>3578500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="H69" t="n">
-        <v>53.47</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.74</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.63</v>
+        <v>0.122</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.673</v>
+        <v>0.123</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3627,39 +3627,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.44</v>
+        <v>3.22</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.0115</v>
+        <v>0.0805</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2986900</v>
+        <v>3453500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.43</v>
+        <v>1.29</v>
       </c>
       <c r="H70" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.33</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.43</v>
+        <v>3.014</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.417</v>
+        <v>2.872</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3672,28 +3672,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.895</v>
+        <v>1.27</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2981200</v>
+        <v>3316700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.69</v>
+        <v>0.45</v>
       </c>
       <c r="H71" t="n">
-        <v>48.68</v>
+        <v>47.98</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3701,10 +3701,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.904</v>
+        <v>1.274</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.895</v>
+        <v>1.318</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3717,39 +3717,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>9.99</v>
+        <v>1.26</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.001</v>
+        <v>0.0328</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2974000</v>
+        <v>3223400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.24</v>
+        <v>0.49</v>
       </c>
       <c r="H72" t="n">
-        <v>48.1</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.05</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>9.994</v>
+        <v>1.185</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>10.106</v>
+        <v>1.153</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3762,39 +3762,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0284</v>
+        <v>0.47</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2948200</v>
+        <v>3194500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H73" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.34</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>3.997</v>
+        <v>0.49</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>3.662</v>
+        <v>0.47</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3807,39 +3807,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.465</v>
+        <v>0.755</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0067</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2907500</v>
+        <v>3123600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.32</v>
+        <v>1.02</v>
       </c>
       <c r="H74" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
+        <v>53.69</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.49</v>
+        <v>0.744</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.47</v>
+        <v>0.708</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3852,39 +3852,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>0</v>
+        <v>2.37</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2877000</v>
+        <v>3071100</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1</v>
+        <v>0.28</v>
       </c>
       <c r="H75" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
+        <v>41.32</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.865</v>
+        <v>2.427</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.861</v>
+        <v>2.417</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3897,39 +3897,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>6.78</v>
+        <v>5.8</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.0044</v>
+        <v>0.032</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2867900</v>
+        <v>3063900</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="H76" t="n">
-        <v>37.17</v>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
+        <v>58.41</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>7.023</v>
+        <v>5.527</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>7.47</v>
+        <v>5.388</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3942,39 +3942,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0316</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2847400</v>
+        <v>3058500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.38</v>
+        <v>0.76</v>
       </c>
       <c r="H77" t="n">
-        <v>47.06</v>
-      </c>
-      <c r="I77" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.36</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.494</v>
+        <v>0.951</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.514</v>
+        <v>1.03</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3987,39 +3987,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0</v>
+        <v>6.77</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2778300</v>
+        <v>3012300</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1.36</v>
+        <v>0.27</v>
       </c>
       <c r="H78" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
+        <v>36.73</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>7.022</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4032,39 +4032,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.0374</v>
+        <v>0.435</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2716500</v>
+        <v>3005600</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H79" t="n">
-        <v>59.04</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>5.53</v>
+        <v>0.43</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>5.389</v>
+        <v>0.417</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4077,39 +4077,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2678000</v>
+        <v>2995500</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.31</v>
+        <v>1.04</v>
       </c>
       <c r="H80" t="n">
-        <v>43.08</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.01</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.269</v>
+        <v>0.526</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.291</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.59</v>
+        <v>0.895</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>0.0063</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2669600</v>
+        <v>2981200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.43</v>
+        <v>1.69</v>
       </c>
       <c r="H81" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.68</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.652</v>
+        <v>0.904</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.737</v>
+        <v>0.895</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4167,39 +4167,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0185</v>
+        <v>5.74</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2611100</v>
+        <v>2968600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H82" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.04</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.267</v>
+        <v>5.816</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.269</v>
+        <v>6.07</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4212,39 +4212,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0246</v>
+        <v>0.26</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2605900</v>
+        <v>2967400</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
+        <v>41.98</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.184</v>
+        <v>0.267</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.153</v>
+        <v>0.269</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4257,39 +4257,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2593900</v>
+        <v>2877000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>41.32</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
+        <v>50.44</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>2.427</v>
+        <v>0.865</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.417</v>
+        <v>0.861</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4302,39 +4302,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>11.08</v>
+        <v>0.485</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>0.0336</v>
+        <v>0.0211</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2558900</v>
+        <v>2862000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H85" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.27</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>10.53</v>
+        <v>0.493</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>9.907999999999999</v>
+        <v>0.514</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4347,39 +4347,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.64</v>
+        <v>11.1</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.0354</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2509500</v>
+        <v>2858200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.47</v>
+        <v>0.77</v>
       </c>
       <c r="H86" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I86" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.601</v>
+        <v>10.532</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.603</v>
+        <v>9.907999999999999</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4392,28 +4392,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2459900</v>
+        <v>2841700</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="H87" t="n">
-        <v>69.69</v>
+        <v>40.03</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.982</v>
+        <v>0.268</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.965</v>
+        <v>0.291</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4446,19 +4446,19 @@
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0021</v>
+        <v>4.73</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2452900</v>
+        <v>2818400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H88" t="n">
-        <v>47.78</v>
+        <v>48.74</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.728</v>
+        <v>4.729</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>4.805</v>
@@ -4482,39 +4482,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.0098</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2374200</v>
+        <v>2780400</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.57</v>
+        <v>1.36</v>
       </c>
       <c r="H89" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
+        <v>49.47</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.037</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2.062</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>5.74</v>
+        <v>2.13</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2367500</v>
+        <v>2753500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.29</v>
+        <v>0.42</v>
       </c>
       <c r="H90" t="n">
-        <v>41.04</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>5.816</v>
+        <v>1.983</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>6.07</v>
+        <v>1.965</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4572,39 +4572,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.63</v>
+        <v>1.59</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>0.008</v>
+        <v>0.0063</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2341600</v>
+        <v>2697400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="H91" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.61</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.621</v>
+        <v>1.652</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.611</v>
+        <v>1.737</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4617,39 +4617,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.67</v>
+        <v>2.65</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0229</v>
+        <v>0.0271</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2318100</v>
+        <v>2690100</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>44.16</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+        <v>54.41</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.712</v>
+        <v>2.602</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.603</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4662,39 +4662,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.325</v>
+        <v>1.35</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.0217</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2236400</v>
+        <v>2526800</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.22</v>
+        <v>1.33</v>
       </c>
       <c r="H93" t="n">
-        <v>45.66</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.96</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.337</v>
+        <v>1.364</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.337</v>
+        <v>1.435</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4707,39 +4707,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0152</v>
+        <v>2.02</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2201200</v>
+        <v>2509700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="H94" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="I94" s="17" t="inlineStr">
+        <v>44.59</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.347</v>
+        <v>2.037</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.33</v>
+        <v>2.062</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0291</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2139100</v>
+        <v>2480300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.33</v>
+        <v>1.79</v>
       </c>
       <c r="H95" t="n">
-        <v>38.96</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.68</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.313</v>
+        <v>1.061</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.357</v>
+        <v>1.116</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4797,39 +4797,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.14</v>
+        <v>0.665</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0153</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2137000</v>
+        <v>2412200</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>1.11</v>
+        <v>0.48</v>
       </c>
       <c r="H96" t="n">
-        <v>33.88</v>
-      </c>
-      <c r="I96" s="17" t="inlineStr">
+        <v>43.42</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.192</v>
+        <v>0.711</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.302</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4842,28 +4842,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>6.88</v>
+        <v>0.63</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.0346</v>
+        <v>0.008</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2130900</v>
+        <v>2341600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.36</v>
+        <v>0.66</v>
       </c>
       <c r="H97" t="n">
-        <v>60.86</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>6.366</v>
+        <v>0.621</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>6.025</v>
+        <v>0.611</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4887,28 +4887,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>2129000</v>
+        <v>2289200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>61.31</v>
+        <v>48.12</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.236</v>
+        <v>0.898</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.209</v>
+        <v>0.956</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4932,39 +4932,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>2263000</v>
+      </c>
+      <c r="G99" s="12" t="n">
         <v>0.44</v>
       </c>
-      <c r="E99" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="11" t="n">
-        <v>2108300</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>0.13</v>
-      </c>
       <c r="H99" t="n">
-        <v>29.53</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.69</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.476</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.607</v>
+        <v>0.78</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4977,39 +4977,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>3.46</v>
+        <v>0.34</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.0117</v>
+        <v>0.0303</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>2037200</v>
+        <v>2247800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.64</v>
+        <v>0.28</v>
       </c>
       <c r="H100" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.53</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>3.085</v>
+        <v>0.348</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.611</v>
+        <v>0.33</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5022,39 +5022,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E101" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E101" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>2019500</v>
+        <v>2240700</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H101" t="n">
-        <v>57.06</v>
-      </c>
-      <c r="I101" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.96</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.807</v>
+        <v>0.313</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.698</v>
+        <v>0.357</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5067,39 +5067,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0113</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MMSV</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.325</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>2005900</v>
+        <v>2237400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>3.62</v>
+        <v>0.22</v>
       </c>
       <c r="H102" t="n">
-        <v>54.53</v>
-      </c>
-      <c r="I102" s="17" t="inlineStr">
+        <v>45.66</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.291</v>
+        <v>0.337</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.295</v>
+        <v>0.337</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5112,39 +5112,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>-0.0145</v>
+        <v>1.13</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1996600</v>
+        <v>2234300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="H103" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.07</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.365</v>
+        <v>1.191</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.435</v>
+        <v>1.302</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         <v>-0.0145</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1972400</v>
+        <v>2224600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H104" t="n">
         <v>61.92</v>
@@ -5202,38 +5202,40 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.235</v>
+        <v>1.3</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>0.0217</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1937300</v>
+        <v>2214800</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="H105" t="n">
-        <v>18.87</v>
-      </c>
-      <c r="I105" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.31</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="K105" s="9" t="n"/>
+        <v>1.236</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>1.209</v>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
     </row>
@@ -5245,28 +5247,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0</v>
+        <v>6.87</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0331</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1919200</v>
+        <v>2214200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H106" t="n">
-        <v>70.69</v>
+        <v>60.73</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5274,10 +5276,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>6.365</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.78</v>
+        <v>6.025</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5290,39 +5292,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E107" s="16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E107" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1880000</v>
+        <v>2205000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.46</v>
+        <v>0.14</v>
       </c>
       <c r="H107" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.53</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.898</v>
+        <v>0.476</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.956</v>
+        <v>0.607</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5335,39 +5337,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>-0.0156</v>
+        <v>5.1</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1878300</v>
+        <v>2191100</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H108" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.41</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.677</v>
+        <v>5.063</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.732</v>
+        <v>5.036</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5380,39 +5382,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E109" s="16" t="n">
-        <v>0</v>
+        <v>13.32</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1865200</v>
+        <v>2177200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H109" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="I109" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.93</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>7.335</v>
+        <v>13.106</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>7.611</v>
+        <v>13.298</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5425,39 +5427,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>5.11</v>
+        <v>7.11</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.002</v>
+        <v>0.0014</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1850600</v>
+        <v>2139100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="H110" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.25</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>5.064</v>
+        <v>7.336</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>5.036</v>
+        <v>7.612</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5470,39 +5472,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.33</v>
+        <v>2.93</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>0.031</v>
+        <v>0.0103</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1795600</v>
+        <v>2099100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H111" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
+        <v>58.47</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.274</v>
+        <v>2.81</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.19</v>
+        <v>2.699</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5530,15 +5532,15 @@
         <v>0.0167</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1783400</v>
+        <v>2084800</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H112" t="n">
         <v>57.18</v>
       </c>
-      <c r="I112" s="17" t="inlineStr">
+      <c r="I112" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5560,39 +5562,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.255</v>
+        <v>3.46</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0.02</v>
+        <v>0.0117</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1764800</v>
+        <v>2049700</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="H113" t="n">
-        <v>43.93</v>
-      </c>
-      <c r="I113" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.75</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.264</v>
+        <v>3.085</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.282</v>
+        <v>2.611</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5605,28 +5607,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E114" s="16" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1750900</v>
+        <v>2030300</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>38.02</v>
+        <v>56.52</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5634,10 +5636,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.481</v>
+        <v>1.255</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.536</v>
+        <v>1.123</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5650,39 +5652,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0113</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MMSV</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.875</v>
+        <v>0.3</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.0345</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1734400</v>
+        <v>2007900</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.44</v>
+        <v>3.62</v>
       </c>
       <c r="H115" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
+        <v>54.53</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.835</v>
+        <v>0.291</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.802</v>
+        <v>0.295</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5695,39 +5697,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.0038</v>
+        <v>0.625</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1710200</v>
+        <v>1971500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
       <c r="H116" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
+        <v>38.39</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>2.726</v>
+        <v>0.677</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>2.747</v>
+        <v>0.732</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5740,40 +5742,38 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0076</v>
+        <v>0.23</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1708400</v>
+        <v>1959400</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H117" t="n">
-        <v>56.52</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>14.67</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.255</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>1.123</v>
-      </c>
+        <v>0.255</v>
+      </c>
+      <c r="K117" s="9" t="n"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
     </row>
@@ -5785,28 +5785,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.0323</v>
+        <v>0.465</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1707800</v>
+        <v>1883400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.72</v>
+        <v>0.27</v>
       </c>
       <c r="H118" t="n">
-        <v>66.14</v>
+        <v>38.02</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>2.128</v>
+        <v>0.481</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.082</v>
+        <v>0.536</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5830,39 +5830,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.0208</v>
+        <v>0.875</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1631700</v>
+        <v>1835600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.15</v>
+        <v>0.47</v>
       </c>
       <c r="H119" t="n">
-        <v>45.61</v>
-      </c>
-      <c r="I119" s="17" t="inlineStr">
+        <v>59.65</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.732</v>
+        <v>0.835</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.724</v>
+        <v>0.802</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5875,39 +5875,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>1834200</v>
+      </c>
+      <c r="G120" s="12" t="n">
         <v>0.77</v>
       </c>
-      <c r="E120" s="15" t="n">
-        <v>0.0132</v>
-      </c>
-      <c r="F120" s="11" t="n">
-        <v>1627400</v>
-      </c>
-      <c r="G120" s="12" t="n">
-        <v>0.21</v>
-      </c>
       <c r="H120" t="n">
-        <v>50.46</v>
-      </c>
-      <c r="I120" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.3</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.768</v>
+        <v>2.128</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.771</v>
+        <v>2.082</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5929,27 +5929,27 @@
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>-0.0112</v>
+        <v>-0.0157</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1557500</v>
+        <v>1830300</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H121" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
+        <v>33.12</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>4.546</v>
+        <v>4.545</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>4.641</v>
@@ -5965,39 +5965,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0037</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>RGB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.0233</v>
+        <v>2.68</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1528300</v>
+        <v>1824800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.3</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
+        <v>45.46</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.211</v>
+        <v>2.727</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.207</v>
+        <v>2.748</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -6010,39 +6010,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0014</v>
+        <v>1.33</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.031</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1527800</v>
+        <v>1809500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H123" t="n">
-        <v>41.58</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.1</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>7.405</v>
+        <v>1.274</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>7.796</v>
+        <v>1.19</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6055,28 +6055,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>0.0399</v>
+        <v>7.35</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1469700</v>
+        <v>1809400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H124" t="n">
-        <v>56.9</v>
+        <v>42.06</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.313</v>
+        <v>7.406</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>6.969</v>
+        <v>7.796</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6100,39 +6100,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0206</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NADIBHD</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.345</v>
+        <v>0.615</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.0165</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1468000</v>
+        <v>1772500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>1.72</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>67.54000000000001</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
+        <v>66.12</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.331</v>
+        <v>0.549</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.317</v>
+        <v>0.489</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.04</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1445400</v>
+        <v>1766700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="H126" t="n">
-        <v>71.86</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.39</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.176</v>
+        <v>0.264</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.164</v>
+        <v>0.282</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6190,39 +6190,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.61</v>
+        <v>1.15</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0.0167</v>
+        <v>0.055</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1422300</v>
+        <v>1761800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.18</v>
+        <v>0.52</v>
       </c>
       <c r="H127" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
+        <v>57.69</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.644</v>
+        <v>1.103</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.681</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6235,39 +6235,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0.0074</v>
+        <v>0.705</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1394100</v>
+        <v>1720700</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.39</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
+        <v>45.61</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.822</v>
+        <v>0.732</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.959</v>
+        <v>0.724</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6280,39 +6280,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0.0038</v>
+        <v>6.78</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1361100</v>
+        <v>1712500</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H129" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.04</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>2.646</v>
+        <v>6.804</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>2.825</v>
+        <v>6.82</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6325,28 +6325,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.6</v>
+        <v>7.53</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>0.0066</v>
+        <v>0.0372</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1360600</v>
+        <v>1657200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H130" t="n">
-        <v>56.8</v>
+        <v>56.53</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.441</v>
+        <v>7.311</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.441</v>
+        <v>6.968</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6370,39 +6370,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0189</v>
+        <v>0.21</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1342800</v>
+        <v>1643300</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.27</v>
+        <v>0.93</v>
       </c>
       <c r="H131" t="n">
-        <v>47.95</v>
-      </c>
-      <c r="I131" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.86</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>6.802</v>
+        <v>0.176</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>6.82</v>
+        <v>0.164</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1317100</v>
+        <v>1628700</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H132" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="I132" s="17" t="inlineStr">
+        <v>50.46</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.527</v>
+        <v>0.768</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6460,28 +6460,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>0.006</v>
+        <v>2.6</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1309800</v>
+        <v>1605400</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H133" t="n">
-        <v>61.41</v>
+        <v>46.05</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>13.109</v>
+        <v>2.645</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>13.298</v>
+        <v>2.825</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6505,39 +6505,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>0037</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GASMSIA</t>
+          <t>RGB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0302</v>
+        <v>0.215</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1293700</v>
+        <v>1595300</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="H134" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.3</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>5.173</v>
+        <v>0.211</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>5.029</v>
+        <v>0.207</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6550,39 +6550,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>3.03</v>
+        <v>0.61</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>0.01</v>
+        <v>0.0167</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1278500</v>
+        <v>1588000</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H135" t="n">
-        <v>63.27</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
+        <v>41.4</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>2.844</v>
+        <v>0.644</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>2.378</v>
+        <v>0.681</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6595,39 +6595,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.61</v>
+        <v>4.6</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.0066</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1259600</v>
+        <v>1522000</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H136" t="n">
-        <v>65.48999999999999</v>
-      </c>
-      <c r="I136" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.8</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.549</v>
+        <v>4.441</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.489</v>
+        <v>4.441</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6640,39 +6640,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.835</v>
+        <v>2.71</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>0.0121</v>
+        <v>0.0037</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1245500</v>
+        <v>1496400</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H137" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
+        <v>38.06</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.865</v>
+        <v>2.821</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.927</v>
+        <v>2.959</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0206</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>NADIBHD</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.13</v>
+        <v>0.345</v>
       </c>
       <c r="E138" s="15" t="n">
-        <v>0.0367</v>
+        <v>0.0147</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1239300</v>
+        <v>1468000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.36</v>
+        <v>1.72</v>
       </c>
       <c r="H138" t="n">
-        <v>55.96</v>
-      </c>
-      <c r="I138" s="17" t="inlineStr">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.101</v>
+        <v>0.331</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6730,39 +6730,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.28</v>
+        <v>3.05</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0167</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1197300</v>
+        <v>1436600</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="H139" t="n">
-        <v>41.19</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
+        <v>63.93</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.295</v>
+        <v>2.846</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.32</v>
+        <v>2.378</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6775,39 +6775,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AMEREIT</t>
+          <t>GASMSIA</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E140" s="16" t="n">
-        <v>0</v>
+        <v>5.45</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0302</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1152200</v>
+        <v>1389400</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>13.57</v>
+        <v>1.53</v>
       </c>
       <c r="H140" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.56</v>
+        <v>5.173</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.543</v>
+        <v>5.029</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6820,39 +6820,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E141" s="16" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E141" s="15" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1089200</v>
+        <v>1387200</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="H141" t="n">
-        <v>60.26</v>
-      </c>
-      <c r="I141" s="17" t="inlineStr">
+        <v>36.42</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.655</v>
+        <v>0.865</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.583</v>
+        <v>0.927</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6865,39 +6865,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1076700</v>
+        <v>1335000</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H142" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="I142" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.82</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>5.45</v>
+        <v>2.295</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>5.725</v>
+        <v>2.214</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6910,39 +6910,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>1326600</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H143" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K143" s="9" t="n">
         <v>0.32</v>
-      </c>
-      <c r="E143" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="11" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="G143" s="12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H143" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J143" s="9" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="K143" s="9" t="n">
-        <v>0.332</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6955,39 +6955,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PIE</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>1.64</v>
+        <v>0.285</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1046100</v>
+        <v>1270400</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1.41</v>
+        <v>0.58</v>
       </c>
       <c r="H144" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>1.598</v>
+        <v>0.272</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>1.649</v>
+        <v>0.259</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -7000,39 +7000,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.0013</v>
+        <v>5.3</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1045900</v>
+        <v>1263900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="H145" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.95</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>7.553</v>
+        <v>5.45</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>7.693</v>
+        <v>5.725</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7045,39 +7045,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0.0556</v>
+        <v>1.01</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1040900</v>
+        <v>1262700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.47</v>
+        <v>2.05</v>
       </c>
       <c r="H146" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I146" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.74</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.272</v>
+        <v>1.011</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.259</v>
+        <v>0.99</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7090,28 +7090,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0392</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>KEEMING</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>0.0726</v>
+        <v>7.54</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>981500</v>
+        <v>1239100</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>1.34</v>
+        <v>0.44</v>
       </c>
       <c r="H147" t="n">
-        <v>56.76</v>
+        <v>48.11</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.562</v>
+        <v>7.554</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.522</v>
+        <v>7.694</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7135,39 +7135,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>AMEREIT</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>-0.0155</v>
+        <v>1.6</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>959900</v>
+        <v>1167100</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.83</v>
+        <v>13.74</v>
       </c>
       <c r="H148" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.9</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.93</v>
+        <v>1.56</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>1.009</v>
+        <v>1.543</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7180,28 +7180,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.955</v>
+        <v>0.95</v>
       </c>
       <c r="E149" s="10" t="n">
         <v>-0.0155</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>958000</v>
+        <v>1138400</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.22</v>
+        <v>0.99</v>
       </c>
       <c r="H149" t="n">
-        <v>57.51</v>
+        <v>51.21</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.944</v>
+        <v>0.93</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.895</v>
+        <v>1.009</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7225,39 +7225,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E150" s="15" t="n">
-        <v>0.02</v>
+        <v>1.74</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>953700</v>
+        <v>1127500</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H150" t="n">
-        <v>50.79</v>
-      </c>
-      <c r="I150" s="17" t="inlineStr">
+        <v>44.02</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.025</v>
+        <v>1.752</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.979</v>
+        <v>1.849</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>PIE</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>-0.0417</v>
+        <v>1.64</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.07190000000000001</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>909100</v>
+        <v>1123700</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="H151" t="n">
-        <v>34.59</v>
+        <v>52.69</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.711</v>
+        <v>1.598</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.766</v>
+        <v>1.649</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7315,39 +7315,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="E152" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>888200</v>
+        <v>1119300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H152" t="n">
-        <v>59.55</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.03</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.293</v>
+        <v>1.024</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.214</v>
+        <v>0.979</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7360,39 +7360,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.01</v>
+        <v>0.68</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.0073</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>887700</v>
+        <v>1093000</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>1.44</v>
+        <v>0.42</v>
       </c>
       <c r="H153" t="n">
-        <v>51.74</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.011</v>
+        <v>0.655</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.99</v>
+        <v>0.583</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7405,28 +7405,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0392</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>KEEMING</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.68</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0806</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>884800</v>
+        <v>1068800</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.43</v>
+        <v>1.46</v>
       </c>
       <c r="H154" t="n">
-        <v>51.43</v>
+        <v>57.71</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.641</v>
+        <v>2.564</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.629</v>
+        <v>2.523</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7450,39 +7450,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>0.0024</v>
+        <v>0.32</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>884000</v>
+        <v>1050000</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.21</v>
+        <v>0.71</v>
       </c>
       <c r="H155" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="I155" s="17" t="inlineStr">
+        <v>46.79</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>4.324</v>
+        <v>0.323</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>4.605</v>
+        <v>0.332</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7495,28 +7495,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E156" s="15" t="n">
-        <v>0.0225</v>
+        <v>0.305</v>
+      </c>
+      <c r="E156" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>869300</v>
+        <v>1008300</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.52</v>
+        <v>0.75</v>
       </c>
       <c r="H156" t="n">
-        <v>55.37</v>
+        <v>51.53</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.893</v>
+        <v>0.297</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.903</v>
+        <v>0.326</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7540,39 +7540,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>KRETAM</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E157" s="16" t="n">
-        <v>0</v>
+        <v>0.655</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>818800</v>
+        <v>1000400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.54</v>
+        <v>22.41</v>
       </c>
       <c r="H157" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.06</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.575</v>
+        <v>0.653</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7585,28 +7585,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>813200</v>
+        <v>999700</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H158" t="n">
-        <v>54.37</v>
+        <v>56.84</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>2.084</v>
+        <v>0.893</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>2.004</v>
+        <v>0.903</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7630,39 +7630,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E159" s="15" t="n">
-        <v>0.0242</v>
+        <v>0.955</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>811400</v>
+        <v>958000</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H159" t="n">
-        <v>51.45</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.51</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.634</v>
+        <v>0.944</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.623</v>
+        <v>0.895</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7675,39 +7675,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>0</v>
+        <v>4.25</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>800800</v>
+        <v>940000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.49</v>
+        <v>0.22</v>
       </c>
       <c r="H160" t="n">
-        <v>31.78</v>
-      </c>
-      <c r="I160" s="17" t="inlineStr">
+        <v>39.67</v>
+      </c>
+      <c r="I160" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.922</v>
+        <v>4.324</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.981</v>
+        <v>4.605</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7720,28 +7720,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E161" s="15" t="n">
-        <v>0.0035</v>
+        <v>1.61</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>762300</v>
+        <v>914100</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.27</v>
+        <v>1.23</v>
       </c>
       <c r="H161" t="n">
-        <v>58.75</v>
+        <v>34.59</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>2.737</v>
+        <v>1.711</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>2.382</v>
+        <v>1.766</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7765,39 +7765,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E162" s="16" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E162" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>758100</v>
+        <v>905100</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="H162" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I162" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.73</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>1.124</v>
+        <v>0.641</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>1.249</v>
+        <v>0.629</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7810,39 +7810,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E163" s="15" t="n">
-        <v>0.0024</v>
+        <v>2.13</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>737800</v>
+        <v>900700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H163" t="n">
-        <v>46.21</v>
-      </c>
-      <c r="I163" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.75</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>4.201</v>
+        <v>2.083</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>4.284</v>
+        <v>2.004</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7855,39 +7855,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>8.51</v>
+        <v>1.33</v>
       </c>
       <c r="E164" s="15" t="n">
-        <v>0.0131</v>
+        <v>0.031</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>697100</v>
+        <v>895600</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="H164" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="I164" s="17" t="inlineStr">
+        <v>53.68</v>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>8.552</v>
+        <v>1.298</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>8.664</v>
+        <v>1.305</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7900,39 +7900,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.32</v>
+        <v>2.49</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>0.0233</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>690600</v>
+        <v>883100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H165" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="I165" s="17" t="inlineStr">
+        <v>42.88</v>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.297</v>
+        <v>2.522</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.305</v>
+        <v>2.638</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7945,28 +7945,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E166" s="16" t="n">
-        <v>0</v>
+        <v>2.83</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>685000</v>
+        <v>865800</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.66</v>
+        <v>0.3</v>
       </c>
       <c r="H166" t="n">
-        <v>63.09</v>
+        <v>58.75</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.634</v>
+        <v>2.737</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.633</v>
+        <v>2.382</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7990,39 +7990,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E167" s="16" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E167" s="15" t="n">
+        <v>0.0242</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>678100</v>
+        <v>861800</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>1.13</v>
+        <v>0.3</v>
       </c>
       <c r="H167" t="n">
-        <v>41.31</v>
-      </c>
-      <c r="I167" s="17" t="inlineStr">
+        <v>51.45</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.181</v>
+        <v>0.634</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.203</v>
+        <v>0.623</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8035,39 +8035,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>1.61</v>
+        <v>1.1</v>
       </c>
       <c r="E168" s="15" t="n">
-        <v>0.0063</v>
+        <v>0.028</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>677400</v>
+        <v>848000</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="H168" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.01</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>1.641</v>
+        <v>1.127</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>1.711</v>
+        <v>1.249</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8080,39 +8080,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="E169" s="15" t="n">
-        <v>0.004</v>
+        <v>4.13</v>
+      </c>
+      <c r="E169" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>665200</v>
+        <v>822200</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.25</v>
+        <v>0.36</v>
       </c>
       <c r="H169" t="n">
-        <v>41.47</v>
-      </c>
-      <c r="I169" s="17" t="inlineStr">
+        <v>45.78</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>2.521</v>
+        <v>4.2</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>2.638</v>
+        <v>4.283</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8125,39 +8125,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E170" s="15" t="n">
-        <v>0.0151</v>
+        <v>0.55</v>
+      </c>
+      <c r="E170" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>643200</v>
+        <v>821900</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="H170" t="n">
-        <v>57.96</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.89</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>2.658</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>2.499</v>
+        <v>0.575</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8170,39 +8170,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.79</v>
+        <v>0.885</v>
       </c>
       <c r="E171" s="10" t="n">
         <v>-0.005600000000000001</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>641200</v>
+        <v>818300</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="H171" t="n">
-        <v>43.46</v>
-      </c>
-      <c r="I171" s="17" t="inlineStr">
+        <v>30.6</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.824</v>
+        <v>0.921</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.83</v>
+        <v>0.981</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8215,39 +8215,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>8.5</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>611400</v>
+        <v>778700</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H172" t="n">
-        <v>40.41</v>
-      </c>
-      <c r="I172" s="17" t="inlineStr">
+        <v>48.06</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.753</v>
+        <v>8.551</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>0.767</v>
+        <v>8.664</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8275,10 +8275,10 @@
         <v>0.005600000000000001</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>611400</v>
+        <v>758700</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H173" t="n">
         <v>42.75</v>
@@ -8305,39 +8305,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="E174" s="15" t="n">
-        <v>0.0255</v>
+        <v>2.35</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>609700</v>
+        <v>736200</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="H174" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.66</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>3.16</v>
+        <v>2.468</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>2.975</v>
+        <v>2.632</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8350,39 +8350,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E175" s="16" t="n">
-        <v>0</v>
+        <v>1.61</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>608600</v>
+        <v>716400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="H175" t="n">
-        <v>38.55</v>
-      </c>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>1.435</v>
+        <v>1.641</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>1.455</v>
+        <v>1.711</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8395,39 +8395,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.695</v>
+        <v>0.71</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>607300</v>
+        <v>687600</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H176" t="n">
-        <v>41.04</v>
-      </c>
-      <c r="I176" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.41</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.711</v>
+        <v>0.753</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8440,28 +8440,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="E177" s="15" t="n">
-        <v>0.014</v>
+        <v>0.64</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>596400</v>
+        <v>685000</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.42</v>
+        <v>0.66</v>
       </c>
       <c r="H177" t="n">
-        <v>60.48</v>
+        <v>63.09</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>3.543</v>
+        <v>0.634</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>3.577</v>
+        <v>0.633</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8485,39 +8485,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>-0.0338</v>
+        <v>2.69</v>
+      </c>
+      <c r="E178" s="15" t="n">
+        <v>0.0151</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>564200</v>
+        <v>683100</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="H178" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.96</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.651</v>
+        <v>2.658</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.617</v>
+        <v>2.499</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8530,39 +8530,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PETGAS</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>17.3</v>
+        <v>3.61</v>
       </c>
       <c r="E179" s="15" t="n">
-        <v>0.0023</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>554100</v>
+        <v>682800</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>1.08</v>
+        <v>0.48</v>
       </c>
       <c r="H179" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="I179" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.6</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>17.283</v>
+        <v>3.541</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>17.329</v>
+        <v>3.576</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8575,39 +8575,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>1.17</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>534900</v>
+        <v>679200</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.17</v>
+        <v>1.13</v>
       </c>
       <c r="H180" t="n">
-        <v>45.18</v>
-      </c>
-      <c r="I180" s="17" t="inlineStr">
+        <v>41.31</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>1.122</v>
+        <v>1.181</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>1.114</v>
+        <v>1.203</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8620,39 +8620,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E181" s="15" t="n">
-        <v>0.0147</v>
+        <v>1.79</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>528500</v>
+        <v>670200</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="H181" t="n">
-        <v>34.54</v>
-      </c>
-      <c r="I181" s="17" t="inlineStr">
+        <v>43.46</v>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>1.47</v>
+        <v>1.824</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>1.597</v>
+        <v>1.83</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8665,39 +8665,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.6</v>
+        <v>1.39</v>
       </c>
       <c r="E182" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.0072</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>518700</v>
+        <v>669000</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>1.64</v>
+        <v>0.33</v>
       </c>
       <c r="H182" t="n">
-        <v>59.21</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.3</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>1.369</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.55</v>
+        <v>1.348</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8710,28 +8710,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>2.17</v>
+        <v>3.22</v>
       </c>
       <c r="E183" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0255</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>515300</v>
+        <v>652100</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="H183" t="n">
-        <v>52.34</v>
+        <v>57.77</v>
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>2.124</v>
+        <v>3.16</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>2.228</v>
+        <v>2.975</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8755,39 +8755,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>PETGAS</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>-0.0185</v>
+        <v>17.3</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>514300</v>
+        <v>650800</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>0.14</v>
+        <v>1.27</v>
       </c>
       <c r="H184" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="I184" s="17" t="inlineStr">
+        <v>50.25</v>
+      </c>
+      <c r="I184" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>0.553</v>
+        <v>17.283</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>0.589</v>
+        <v>17.329</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8800,28 +8800,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0265</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>INFOM</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="E185" s="15" t="n">
-        <v>0.0272</v>
+        <v>0.695</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>502600</v>
+        <v>623400</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="H185" t="n">
-        <v>64.97</v>
+        <v>41.04</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -8829,16 +8829,646 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>1.802</v>
+        <v>0.711</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>1.683</v>
+        <v>0.766</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>620700</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H186" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>1.436</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>598100</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="H187" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>576100</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H188" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>5.356</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>KEYFIELD</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>572800</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H189" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="I189" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>1.372</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>549600</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H190" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="I190" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E191" s="10" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>549100</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H191" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>3.298</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>542800</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H192" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>2.228</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E193" s="15" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>541500</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H193" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="I193" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D194" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E194" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>539000</v>
+      </c>
+      <c r="G194" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H194" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J194" s="9" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="K194" s="9" t="n">
+        <v>1.114</v>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" s="14" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D195" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E195" s="15" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>518700</v>
+      </c>
+      <c r="G195" s="12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H195" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J195" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K195" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" s="14" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D196" s="9" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="E196" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>516000</v>
+      </c>
+      <c r="G196" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H196" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="I196" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J196" s="9" t="n">
+        <v>7.904</v>
+      </c>
+      <c r="K196" s="9" t="n">
+        <v>7.925</v>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" s="14" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>0265</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>INFOM</t>
+        </is>
+      </c>
+      <c r="D197" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E197" s="15" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>514200</v>
+      </c>
+      <c r="G197" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H197" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J197" s="9" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="K197" s="9" t="n">
+        <v>1.682</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" s="14" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D198" s="9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>511100</v>
+      </c>
+      <c r="G198" s="12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H198" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="I198" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J198" s="9" t="n">
+        <v>1.558</v>
+      </c>
+      <c r="K198" s="9" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" s="14" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>5299</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>IGBCR</t>
+        </is>
+      </c>
+      <c r="D199" s="9" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E199" s="10" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>510300</v>
+      </c>
+      <c r="G199" s="12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H199" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J199" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K199" s="9" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>